--- a/templates/Blank.xlsx
+++ b/templates/Blank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efinney\Desktop\Chat GPT\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54BDCFA-9255-47B7-A687-0C21C7C1353A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA36538-4C21-4204-91AE-7DC9CD03C42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1058,18 +1058,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1133,19 +1133,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1271,19 +1258,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1313,14 +1287,23 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1338,7 +1321,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1415,165 +1398,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="39" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1635,16 +1494,13 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="166" fontId="53" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1661,20 +1517,17 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1687,7 +1540,7 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="48" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="48" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1764,23 +1617,23 @@
     <xf numFmtId="4" fontId="39" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="7" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1788,16 +1641,13 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="7" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1820,15 +1670,15 @@
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="7" borderId="14" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="7" fillId="6" borderId="13" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1846,10 +1696,95 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1857,106 +1792,158 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="39" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -2344,7 +2331,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor theme="3" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:J1286"/>
+  <dimension ref="A1:W1286"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="7" customWidth="1"/>
@@ -2353,7 +2340,7 @@
     <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1" style="22" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="22" customWidth="1"/>
     <col min="8" max="8" width="11.140625" style="22" customWidth="1"/>
     <col min="9" max="9" width="7.5703125" style="21" customWidth="1"/>
     <col min="10" max="10" width="5.140625" style="21" customWidth="1"/>
@@ -2372,101 +2359,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A1" s="164" t="e" vm="1">
+      <c r="A1" s="112" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="28"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="146"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="12.6" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="28"/>
+      <c r="A2" s="112"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="146"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="28"/>
+      <c r="A3" s="112"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="112"/>
+      <c r="G3" s="146"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" ht="12.2" customHeight="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="28"/>
+      <c r="A4" s="112"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="146"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="37" t="s">
+      <c r="C5" s="52"/>
+      <c r="D5" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="28"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="146"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" ht="11.45" customHeight="1">
-      <c r="C6" s="91"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="38"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="147"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" ht="12.2" customHeight="1">
-      <c r="B7" s="86"/>
-      <c r="C7" s="98"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="23"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="28"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="146"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A8" s="99"/>
-      <c r="B8" s="100" t="s">
+      <c r="A8" s="65"/>
+      <c r="B8" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="166"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="29"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="148"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2475,702 +2462,702 @@
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="97"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="149"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:10" s="8" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="176"/>
-      <c r="C10" s="101" t="s">
+      <c r="B10" s="125"/>
+      <c r="C10" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="167" t="s">
+      <c r="D10" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="168"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="39"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="150"/>
     </row>
     <row r="11" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A11" s="177"/>
-      <c r="B11" s="178"/>
+      <c r="A11" s="126"/>
+      <c r="B11" s="127"/>
       <c r="C11" s="24"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="172"/>
-      <c r="G11" s="40"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="151"/>
     </row>
     <row r="12" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A12" s="162"/>
-      <c r="B12" s="180"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="157"/>
-      <c r="G12" s="41"/>
+      <c r="A12" s="129"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="152"/>
     </row>
     <row r="13" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A13" s="162"/>
-      <c r="B13" s="163"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="157"/>
-      <c r="G13" s="41"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="95"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="152"/>
     </row>
     <row r="14" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A14" s="162"/>
-      <c r="B14" s="163"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="159"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="40"/>
+      <c r="A14" s="129"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="151"/>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A15" s="162"/>
-      <c r="B15" s="163"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="40"/>
+      <c r="A15" s="129"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="151"/>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A16" s="162"/>
-      <c r="B16" s="163"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="155"/>
-      <c r="E16" s="156"/>
-      <c r="F16" s="157"/>
-      <c r="G16" s="42"/>
+      <c r="A16" s="129"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="153"/>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A17" s="162"/>
-      <c r="B17" s="163"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="155"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="42"/>
+      <c r="A17" s="129"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="153"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" hidden="1" customHeight="1">
-      <c r="A18" s="87"/>
+      <c r="A18" s="55"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="43"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="154"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A19" s="90"/>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="174"/>
-      <c r="G19" s="44"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="155"/>
     </row>
     <row r="20" spans="1:10" ht="4.7" customHeight="1">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="46"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="156"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" s="9" customFormat="1" ht="14.45" customHeight="1">
-      <c r="A21" s="102" t="s">
+      <c r="A21" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="102"/>
+      <c r="B21" s="68"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="30"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="157"/>
     </row>
     <row r="22" spans="1:10" ht="11.45" customHeight="1">
-      <c r="A22" s="154" t="s">
+      <c r="A22" s="132" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="154"/>
-      <c r="C22" s="179"/>
-      <c r="D22" s="179"/>
-      <c r="E22" s="179"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="26"/>
+      <c r="B22" s="132"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="158"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="11.45" customHeight="1">
-      <c r="A23" s="154" t="s">
+      <c r="A23" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="154"/>
-      <c r="C23" s="179"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="26"/>
+      <c r="B23" s="132"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="158"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="9" customHeight="1">
-      <c r="B24" s="47"/>
-      <c r="G24" s="26"/>
+      <c r="B24" s="28"/>
+      <c r="G24" s="158"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="93"/>
-      <c r="C25" s="161"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="27"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="159"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="62" t="s">
+      <c r="B26" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="63" t="s">
+      <c r="D26" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="64" t="s">
+      <c r="E26" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="66" t="s">
+      <c r="F26" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="48"/>
+      <c r="G26" s="160"/>
     </row>
     <row r="27" spans="1:10" s="10" customFormat="1" ht="1.5" hidden="1" customHeight="1">
-      <c r="A27" s="94">
+      <c r="A27" s="61">
         <v>0</v>
       </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="96"/>
-      <c r="E27" s="95"/>
-      <c r="F27" s="96"/>
-      <c r="G27" s="48"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="144"/>
+      <c r="G27" s="160"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="122">
+      <c r="A28" s="88">
         <f>+A27+1</f>
         <v>1</v>
       </c>
-      <c r="B28" s="123"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="128" t="str">
+      <c r="B28" s="89"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="145" t="str">
         <f>IF(D28&lt;&gt;"",D28*E28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G28" s="31"/>
+      <c r="G28" s="161"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="122">
+      <c r="A29" s="88">
         <f t="shared" ref="A29:A47" si="0">+A28+1</f>
         <v>2</v>
       </c>
-      <c r="B29" s="139"/>
-      <c r="C29" s="140"/>
-      <c r="D29" s="125"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="128" t="str">
+      <c r="B29" s="104"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="91"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="145" t="str">
         <f t="shared" ref="F29:F44" si="1">IF(D29&lt;&gt;"",D29*E29," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="161"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="122">
+      <c r="A30" s="88">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B30" s="139"/>
-      <c r="C30" s="140"/>
-      <c r="D30" s="125"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="128" t="str">
+      <c r="B30" s="104"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G30" s="31"/>
+      <c r="G30" s="161"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="122">
+      <c r="A31" s="88">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B31" s="139"/>
-      <c r="C31" s="140"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="128" t="str">
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G31" s="31"/>
+      <c r="G31" s="161"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="122">
+      <c r="A32" s="88">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B32" s="139"/>
-      <c r="C32" s="140"/>
-      <c r="D32" s="125"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="128" t="str">
+      <c r="B32" s="104"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="91"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G32" s="31"/>
+      <c r="G32" s="161"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="122">
+      <c r="A33" s="88">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B33" s="139"/>
-      <c r="C33" s="140"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="128" t="str">
+      <c r="B33" s="104"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G33" s="31"/>
+      <c r="G33" s="161"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="122">
+      <c r="A34" s="88">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B34" s="139"/>
-      <c r="C34" s="140"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="128" t="str">
+      <c r="B34" s="104"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="91"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G34" s="31"/>
+      <c r="G34" s="161"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="122">
+      <c r="A35" s="88">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B35" s="139"/>
-      <c r="C35" s="140"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="128" t="str">
+      <c r="B35" s="104"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G35" s="31"/>
+      <c r="G35" s="161"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="122">
+      <c r="A36" s="88">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B36" s="139"/>
-      <c r="C36" s="140"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="141"/>
-      <c r="F36" s="128" t="str">
+      <c r="B36" s="104"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G36" s="31"/>
+      <c r="G36" s="161"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="122">
+      <c r="A37" s="88">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B37" s="139"/>
-      <c r="C37" s="140"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="141"/>
-      <c r="F37" s="128" t="str">
+      <c r="B37" s="104"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G37" s="31"/>
+      <c r="G37" s="161"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="122">
+      <c r="A38" s="88">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B38" s="139"/>
-      <c r="C38" s="140"/>
-      <c r="D38" s="125"/>
-      <c r="E38" s="141"/>
-      <c r="F38" s="128" t="str">
+      <c r="B38" s="104"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="91"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G38" s="32"/>
+      <c r="G38" s="162"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="122">
+      <c r="A39" s="88">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B39" s="139"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="125"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="128" t="str">
+      <c r="B39" s="104"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G39" s="32"/>
+      <c r="G39" s="162"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10" ht="24.75" hidden="1" customHeight="1" thickBot="1">
-      <c r="A40" s="122">
+      <c r="A40" s="88">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B40" s="139"/>
-      <c r="C40" s="140"/>
-      <c r="D40" s="125"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="128" t="str">
+      <c r="B40" s="104"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G40" s="31"/>
+      <c r="G40" s="161"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="122">
+      <c r="A41" s="88">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B41" s="139"/>
-      <c r="C41" s="140"/>
-      <c r="D41" s="125"/>
-      <c r="E41" s="141"/>
-      <c r="F41" s="128" t="str">
+      <c r="B41" s="104"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G41" s="49"/>
+      <c r="G41" s="163"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="122">
+      <c r="A42" s="88">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B42" s="139"/>
-      <c r="C42" s="140"/>
-      <c r="D42" s="125"/>
-      <c r="E42" s="141"/>
-      <c r="F42" s="128" t="str">
+      <c r="B42" s="104"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="91"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G42" s="33"/>
+      <c r="G42" s="164"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A43" s="122">
+      <c r="A43" s="88">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B43" s="139"/>
-      <c r="C43" s="140"/>
-      <c r="D43" s="125"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="128" t="str">
+      <c r="B43" s="104"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G43" s="33"/>
+      <c r="G43" s="164"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="122">
+      <c r="A44" s="88">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B44" s="139"/>
-      <c r="C44" s="140"/>
-      <c r="D44" s="125"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="128" t="str">
+      <c r="B44" s="104"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="145" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G44" s="34"/>
+      <c r="G44" s="165"/>
       <c r="H44" s="14"/>
       <c r="I44" s="14"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="122">
+      <c r="A45" s="88">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B45" s="139"/>
-      <c r="C45" s="140"/>
-      <c r="D45" s="125"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="128" t="str">
+      <c r="B45" s="104"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="91"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="145" t="str">
         <f t="shared" ref="F45:F47" si="2">IF(D45&lt;&gt;"",D45*E45," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G45" s="33"/>
+      <c r="G45" s="164"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="122">
+      <c r="A46" s="88">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B46" s="139"/>
-      <c r="C46" s="140"/>
-      <c r="D46" s="125"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="128" t="str">
+      <c r="B46" s="104"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="145" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G46" s="33"/>
+      <c r="G46" s="164"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A47" s="122">
+      <c r="A47" s="88">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B47" s="139"/>
-      <c r="C47" s="140"/>
-      <c r="D47" s="125"/>
-      <c r="E47" s="141"/>
-      <c r="F47" s="128" t="str">
+      <c r="B47" s="104"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="145" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G47" s="51"/>
+      <c r="G47" s="166"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A48" s="127"/>
-      <c r="B48" s="117"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="120" t="s">
+      <c r="A48" s="93"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="84"/>
+      <c r="D48" s="85"/>
+      <c r="E48" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="121">
+      <c r="F48" s="87">
         <f>SUM(F28:F47)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="35"/>
+      <c r="G48" s="167"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A49" s="73"/>
-      <c r="B49" s="108"/>
-      <c r="C49" s="109"/>
-      <c r="E49" s="74" t="s">
+      <c r="A49" s="41"/>
+      <c r="B49" s="74"/>
+      <c r="C49" s="75"/>
+      <c r="E49" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="114"/>
-      <c r="G49" s="52"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="168"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" ht="12" customHeight="1">
-      <c r="A50" s="73"/>
-      <c r="B50" s="108"/>
-      <c r="C50" s="109"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="75"/>
       <c r="E50" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F50" s="114">
+      <c r="F50" s="80">
         <v>0</v>
       </c>
-      <c r="G50" s="26"/>
+      <c r="G50" s="158"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" s="19" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A51" s="73"/>
-      <c r="B51" s="108"/>
-      <c r="C51" s="110"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="74"/>
+      <c r="C51" s="76"/>
       <c r="D51" s="12"/>
       <c r="E51" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F51" s="138">
+      <c r="F51" s="103">
         <v>0</v>
       </c>
-      <c r="G51" s="53"/>
+      <c r="G51" s="169"/>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1">
-      <c r="A52" s="71"/>
-      <c r="B52" s="108"/>
-      <c r="C52" s="111"/>
+      <c r="A52" s="39"/>
+      <c r="B52" s="74"/>
+      <c r="C52" s="77"/>
       <c r="D52" s="12"/>
       <c r="E52" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="137">
+      <c r="F52" s="102">
         <v>0</v>
       </c>
-      <c r="G52" s="26"/>
+      <c r="G52" s="158"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" ht="18" customHeight="1" thickBot="1">
       <c r="A53" s="4"/>
-      <c r="B53" s="69"/>
-      <c r="C53" s="70"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="38"/>
       <c r="D53"/>
       <c r="E53" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F53" s="115"/>
-      <c r="G53" s="53"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="169"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A54" s="73"/>
-      <c r="B54" s="50"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="29"/>
       <c r="C54" s="16"/>
       <c r="D54" s="17"/>
       <c r="E54" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="112">
+      <c r="F54" s="78">
         <f>+F53+F52+F49+F48+F50</f>
         <v>0</v>
       </c>
-      <c r="G54" s="26"/>
+      <c r="G54" s="158"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" ht="5.25" customHeight="1">
-      <c r="A55" s="142"/>
-      <c r="B55" s="143"/>
-      <c r="C55" s="143"/>
-      <c r="D55" s="143"/>
-      <c r="E55" s="144"/>
-      <c r="F55" s="145"/>
-      <c r="G55" s="54"/>
+      <c r="A55" s="107"/>
+      <c r="B55" s="108"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="109"/>
+      <c r="F55" s="110"/>
+      <c r="G55" s="170"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10" ht="15">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="98" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="133"/>
-      <c r="C56" s="133"/>
-      <c r="D56" s="133"/>
-      <c r="E56" s="133"/>
-      <c r="F56" s="133"/>
-      <c r="G56" s="55"/>
+      <c r="B56" s="98"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="98"/>
+      <c r="F56" s="98"/>
+      <c r="G56" s="171"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3182,652 +3169,652 @@
       <c r="D57"/>
       <c r="E57"/>
       <c r="F57"/>
-      <c r="G57" s="55"/>
+      <c r="G57" s="171"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A58" s="75" t="s">
+      <c r="A58" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B58" s="147" t="s">
+      <c r="B58" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="C58" s="147"/>
-      <c r="D58" s="147"/>
-      <c r="E58" s="147"/>
-      <c r="F58" s="147"/>
-      <c r="G58" s="26"/>
+      <c r="C58" s="111"/>
+      <c r="D58" s="111"/>
+      <c r="E58" s="111"/>
+      <c r="F58" s="111"/>
+      <c r="G58" s="158"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="2.25" customHeight="1">
-      <c r="A59" s="75"/>
-      <c r="B59" s="75"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="105"/>
-      <c r="E59" s="105"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="71"/>
+      <c r="E59" s="71"/>
       <c r="F59"/>
-      <c r="G59" s="53"/>
+      <c r="G59" s="169"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A60" s="75" t="s">
+      <c r="A60" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B60" s="147" t="s">
+      <c r="B60" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="147"/>
-      <c r="D60" s="147"/>
-      <c r="E60" s="147"/>
-      <c r="F60" s="147"/>
-      <c r="G60" s="26"/>
+      <c r="C60" s="111"/>
+      <c r="D60" s="111"/>
+      <c r="E60" s="111"/>
+      <c r="F60" s="111"/>
+      <c r="G60" s="158"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10" ht="2.25" customHeight="1">
-      <c r="A61" s="75"/>
-      <c r="B61" s="75"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
+      <c r="A61" s="43"/>
+      <c r="B61" s="43"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
       <c r="F61"/>
-      <c r="G61" s="56"/>
+      <c r="G61" s="172"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" s="75" t="s">
+      <c r="A62" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="152" t="s">
+      <c r="B62" s="136" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="152"/>
-      <c r="D62" s="116">
+      <c r="C62" s="136"/>
+      <c r="D62" s="82">
         <v>0.5</v>
       </c>
-      <c r="E62" s="76" t="s">
+      <c r="E62" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="F62" s="77">
+      <c r="F62" s="45">
         <f>+F54*D62</f>
         <v>0</v>
       </c>
-      <c r="G62" s="56"/>
+      <c r="G62" s="172"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10" ht="3" customHeight="1">
-      <c r="A63" s="75"/>
-      <c r="B63" s="75"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="78"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="80"/>
-      <c r="G63" s="26"/>
+      <c r="A63" s="43"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="46"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="158"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10" ht="15" customHeight="1">
-      <c r="A64" s="75"/>
-      <c r="B64" s="151" t="s">
+      <c r="A64" s="43"/>
+      <c r="B64" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="151"/>
-      <c r="D64" s="151"/>
-      <c r="E64" s="151"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="53"/>
+      <c r="C64" s="135"/>
+      <c r="D64" s="135"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="169"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10" ht="8.4499999999999993" customHeight="1">
-      <c r="A65" s="75"/>
-      <c r="B65" s="75"/>
-      <c r="C65" s="105"/>
-      <c r="D65" s="105"/>
-      <c r="E65" s="105"/>
+      <c r="A65" s="43"/>
+      <c r="B65" s="43"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="71"/>
       <c r="F65"/>
-      <c r="G65" s="26"/>
+      <c r="G65" s="158"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10" ht="15" customHeight="1">
-      <c r="A66" s="75" t="s">
+      <c r="A66" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="147" t="s">
+      <c r="B66" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="147"/>
-      <c r="D66" s="147"/>
-      <c r="E66" s="147"/>
-      <c r="F66" s="147"/>
-      <c r="G66" s="57"/>
+      <c r="C66" s="111"/>
+      <c r="D66" s="111"/>
+      <c r="E66" s="111"/>
+      <c r="F66" s="111"/>
+      <c r="G66" s="173"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10" ht="8.4499999999999993" customHeight="1">
-      <c r="A67" s="75"/>
-      <c r="B67" s="75"/>
-      <c r="C67" s="105"/>
-      <c r="D67" s="105"/>
-      <c r="E67" s="105"/>
+      <c r="A67" s="43"/>
+      <c r="B67" s="43"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
       <c r="F67"/>
-      <c r="G67" s="26"/>
+      <c r="G67" s="158"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
     <row r="68" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="153" t="s">
+      <c r="B68" s="137" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="153"/>
-      <c r="D68" s="153"/>
-      <c r="E68" s="153"/>
-      <c r="F68" s="153"/>
-      <c r="G68" s="53"/>
+      <c r="C68" s="137"/>
+      <c r="D68" s="137"/>
+      <c r="E68" s="137"/>
+      <c r="F68" s="137"/>
+      <c r="G68" s="169"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A69" s="75"/>
-      <c r="B69" s="153" t="s">
+      <c r="A69" s="43"/>
+      <c r="B69" s="137" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="153"/>
-      <c r="D69" s="153"/>
-      <c r="E69" s="153"/>
-      <c r="F69" s="153"/>
-      <c r="G69" s="26"/>
+      <c r="C69" s="137"/>
+      <c r="D69" s="137"/>
+      <c r="E69" s="137"/>
+      <c r="F69" s="137"/>
+      <c r="G69" s="158"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10" ht="4.5" customHeight="1">
-      <c r="A70" s="75"/>
-      <c r="B70" s="75"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="81"/>
-      <c r="E70" s="81"/>
+      <c r="A70" s="43"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="49"/>
+      <c r="E70" s="49"/>
       <c r="F70"/>
-      <c r="G70" s="53"/>
+      <c r="G70" s="169"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10" ht="27" customHeight="1">
-      <c r="A71" s="75" t="s">
+      <c r="A71" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="147" t="s">
+      <c r="B71" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="147"/>
-      <c r="D71" s="147"/>
-      <c r="E71" s="147"/>
-      <c r="F71" s="147"/>
-      <c r="G71" s="26"/>
+      <c r="C71" s="111"/>
+      <c r="D71" s="111"/>
+      <c r="E71" s="111"/>
+      <c r="F71" s="111"/>
+      <c r="G71" s="158"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10" ht="4.5" customHeight="1">
-      <c r="A72" s="75"/>
-      <c r="B72" s="75"/>
-      <c r="C72" s="105"/>
-      <c r="D72" s="105"/>
-      <c r="E72" s="105"/>
+      <c r="A72" s="43"/>
+      <c r="B72" s="43"/>
+      <c r="C72" s="71"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="71"/>
       <c r="F72"/>
-      <c r="G72" s="53"/>
+      <c r="G72" s="169"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" ht="39" customHeight="1">
-      <c r="A73" s="75" t="s">
+      <c r="A73" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="150" t="s">
+      <c r="B73" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="C73" s="150"/>
-      <c r="D73" s="150"/>
-      <c r="E73" s="150"/>
-      <c r="F73" s="150"/>
-      <c r="G73" s="26"/>
+      <c r="C73" s="134"/>
+      <c r="D73" s="134"/>
+      <c r="E73" s="134"/>
+      <c r="F73" s="134"/>
+      <c r="G73" s="158"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10" ht="6" customHeight="1">
-      <c r="A74" s="75"/>
-      <c r="B74" s="75"/>
-      <c r="C74" s="106"/>
-      <c r="D74" s="106"/>
-      <c r="E74" s="106"/>
+      <c r="A74" s="43"/>
+      <c r="B74" s="43"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="72"/>
+      <c r="E74" s="72"/>
       <c r="F74"/>
-      <c r="G74" s="53"/>
+      <c r="G74" s="169"/>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10" ht="30" customHeight="1">
-      <c r="A75" s="75" t="s">
+      <c r="A75" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B75" s="147" t="s">
+      <c r="B75" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C75" s="147"/>
-      <c r="D75" s="147"/>
-      <c r="E75" s="147"/>
-      <c r="F75" s="147"/>
-      <c r="G75" s="26"/>
+      <c r="C75" s="111"/>
+      <c r="D75" s="111"/>
+      <c r="E75" s="111"/>
+      <c r="F75" s="111"/>
+      <c r="G75" s="158"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
     <row r="76" spans="1:10" ht="3" customHeight="1">
-      <c r="A76" s="75"/>
-      <c r="B76" s="75"/>
-      <c r="C76" s="105"/>
-      <c r="D76" s="105"/>
-      <c r="E76" s="105"/>
+      <c r="A76" s="43"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="71"/>
+      <c r="D76" s="71"/>
+      <c r="E76" s="71"/>
       <c r="F76"/>
-      <c r="G76" s="53"/>
+      <c r="G76" s="169"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
     </row>
     <row r="77" spans="1:10" ht="27" customHeight="1">
-      <c r="A77" s="75" t="s">
+      <c r="A77" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B77" s="147" t="s">
+      <c r="B77" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="147"/>
-      <c r="D77" s="147"/>
-      <c r="E77" s="147"/>
-      <c r="F77" s="147"/>
-      <c r="G77" s="26"/>
+      <c r="C77" s="111"/>
+      <c r="D77" s="111"/>
+      <c r="E77" s="111"/>
+      <c r="F77" s="111"/>
+      <c r="G77" s="158"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
     </row>
     <row r="78" spans="1:10" ht="5.25" customHeight="1">
-      <c r="A78" s="75"/>
-      <c r="B78" s="75"/>
-      <c r="C78" s="105"/>
-      <c r="D78" s="105"/>
-      <c r="E78" s="105"/>
+      <c r="A78" s="43"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="71"/>
+      <c r="E78" s="71"/>
       <c r="F78"/>
-      <c r="G78" s="53"/>
+      <c r="G78" s="169"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1"/>
     </row>
     <row r="79" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A79" s="75" t="s">
+      <c r="A79" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="B79" s="147" t="s">
+      <c r="B79" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="147"/>
-      <c r="D79" s="147"/>
-      <c r="E79" s="147"/>
-      <c r="F79" s="147"/>
-      <c r="G79" s="53"/>
+      <c r="C79" s="111"/>
+      <c r="D79" s="111"/>
+      <c r="E79" s="111"/>
+      <c r="F79" s="111"/>
+      <c r="G79" s="169"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
     </row>
     <row r="80" spans="1:10" ht="3" customHeight="1">
-      <c r="A80" s="75"/>
-      <c r="B80" s="75"/>
-      <c r="C80" s="105"/>
-      <c r="D80" s="105"/>
-      <c r="E80" s="105"/>
+      <c r="A80" s="43"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="71"/>
+      <c r="D80" s="71"/>
+      <c r="E80" s="71"/>
       <c r="F80"/>
-      <c r="G80" s="26"/>
+      <c r="G80" s="158"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
     </row>
     <row r="81" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A81" s="75" t="s">
+      <c r="A81" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="147" t="s">
+      <c r="B81" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="147"/>
-      <c r="D81" s="147"/>
-      <c r="E81" s="147"/>
-      <c r="F81" s="147"/>
-      <c r="G81" s="26"/>
+      <c r="C81" s="111"/>
+      <c r="D81" s="111"/>
+      <c r="E81" s="111"/>
+      <c r="F81" s="111"/>
+      <c r="G81" s="158"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
     </row>
     <row r="82" spans="1:10" ht="6" customHeight="1">
-      <c r="A82" s="75"/>
-      <c r="B82" s="75"/>
-      <c r="C82" s="105"/>
-      <c r="D82" s="105"/>
-      <c r="E82" s="105"/>
+      <c r="A82" s="43"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="71"/>
+      <c r="D82" s="71"/>
+      <c r="E82" s="71"/>
       <c r="F82"/>
-      <c r="G82" s="53"/>
+      <c r="G82" s="169"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
     </row>
     <row r="83" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A83" s="75" t="s">
+      <c r="A83" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="147" t="s">
+      <c r="B83" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="147"/>
-      <c r="D83" s="147"/>
-      <c r="E83" s="147"/>
-      <c r="F83" s="147"/>
-      <c r="G83" s="26"/>
+      <c r="C83" s="111"/>
+      <c r="D83" s="111"/>
+      <c r="E83" s="111"/>
+      <c r="F83" s="111"/>
+      <c r="G83" s="158"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A84" s="75"/>
-      <c r="B84" s="75"/>
-      <c r="C84" s="105"/>
-      <c r="D84" s="105"/>
-      <c r="E84" s="105"/>
+      <c r="A84" s="43"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="71"/>
+      <c r="E84" s="71"/>
       <c r="F84"/>
-      <c r="G84" s="26"/>
+      <c r="G84" s="158"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
       <c r="J84" s="1"/>
     </row>
     <row r="85" spans="1:10" ht="81" customHeight="1">
-      <c r="A85" s="75" t="s">
+      <c r="A85" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B85" s="147" t="s">
+      <c r="B85" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="147"/>
-      <c r="D85" s="147"/>
-      <c r="E85" s="147"/>
-      <c r="F85" s="147"/>
-      <c r="G85" s="26"/>
+      <c r="C85" s="111"/>
+      <c r="D85" s="111"/>
+      <c r="E85" s="111"/>
+      <c r="F85" s="111"/>
+      <c r="G85" s="158"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
       <c r="J85" s="1"/>
     </row>
     <row r="86" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A86" s="75"/>
-      <c r="B86" s="105"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="105"/>
-      <c r="E86" s="105"/>
-      <c r="F86" s="105"/>
-      <c r="G86" s="26"/>
+      <c r="A86" s="43"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="71"/>
+      <c r="D86" s="71"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="71"/>
+      <c r="G86" s="158"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
       <c r="J86" s="1"/>
     </row>
     <row r="87" spans="1:10" ht="88.5" customHeight="1">
-      <c r="A87" s="75" t="s">
+      <c r="A87" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="148" t="s">
+      <c r="B87" s="139" t="s">
         <v>67</v>
       </c>
-      <c r="C87" s="148"/>
-      <c r="D87" s="148"/>
-      <c r="E87" s="148"/>
+      <c r="C87" s="139"/>
+      <c r="D87" s="139"/>
+      <c r="E87" s="139"/>
       <c r="F87"/>
-      <c r="G87" s="26"/>
+      <c r="G87" s="158"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
     </row>
     <row r="88" spans="1:10" ht="6" customHeight="1">
-      <c r="A88" s="75"/>
-      <c r="B88" s="148"/>
-      <c r="C88" s="148"/>
-      <c r="D88" s="148"/>
-      <c r="E88" s="148"/>
+      <c r="A88" s="43"/>
+      <c r="B88" s="139"/>
+      <c r="C88" s="139"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="139"/>
       <c r="F88"/>
-      <c r="G88" s="53"/>
+      <c r="G88" s="169"/>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
       <c r="J88" s="1"/>
     </row>
     <row r="89" spans="1:10" ht="18" customHeight="1">
-      <c r="A89" s="75" t="s">
+      <c r="A89" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="147" t="s">
+      <c r="B89" s="111" t="s">
         <v>59</v>
       </c>
-      <c r="C89" s="147"/>
-      <c r="D89" s="147"/>
-      <c r="E89" s="147"/>
-      <c r="F89" s="147"/>
-      <c r="G89" s="53"/>
+      <c r="C89" s="111"/>
+      <c r="D89" s="111"/>
+      <c r="E89" s="111"/>
+      <c r="F89" s="111"/>
+      <c r="G89" s="169"/>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
     </row>
     <row r="90" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A90" s="75"/>
-      <c r="B90" s="75"/>
-      <c r="C90" s="105"/>
-      <c r="D90" s="105"/>
-      <c r="E90" s="105"/>
+      <c r="A90" s="43"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="71"/>
+      <c r="D90" s="71"/>
+      <c r="E90" s="71"/>
       <c r="F90"/>
-      <c r="G90" s="53"/>
+      <c r="G90" s="169"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1"/>
     </row>
     <row r="91" spans="1:10" ht="67.5" customHeight="1">
-      <c r="A91" s="75" t="s">
+      <c r="A91" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="B91" s="147" t="s">
+      <c r="B91" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="147"/>
-      <c r="D91" s="147"/>
-      <c r="E91" s="147"/>
+      <c r="C91" s="111"/>
+      <c r="D91" s="111"/>
+      <c r="E91" s="111"/>
       <c r="F91"/>
-      <c r="G91" s="36"/>
+      <c r="G91" s="174"/>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
       <c r="J91" s="1"/>
     </row>
     <row r="92" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A92" s="75"/>
-      <c r="B92" s="113"/>
-      <c r="C92" s="113"/>
-      <c r="D92" s="113"/>
-      <c r="E92" s="113"/>
+      <c r="A92" s="43"/>
+      <c r="B92" s="79"/>
+      <c r="C92" s="79"/>
+      <c r="D92" s="79"/>
+      <c r="E92" s="79"/>
       <c r="F92"/>
-      <c r="G92" s="53"/>
+      <c r="G92" s="169"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1"/>
     </row>
     <row r="93" spans="1:10" ht="54.75" customHeight="1">
-      <c r="A93" s="75" t="s">
+      <c r="A93" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="147" t="s">
+      <c r="B93" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="147"/>
-      <c r="D93" s="147"/>
-      <c r="E93" s="147"/>
+      <c r="C93" s="111"/>
+      <c r="D93" s="111"/>
+      <c r="E93" s="111"/>
       <c r="F93"/>
-      <c r="G93" s="53"/>
+      <c r="G93" s="169"/>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
       <c r="J93" s="1"/>
     </row>
     <row r="94" spans="1:10" ht="7.5" customHeight="1">
-      <c r="A94" s="75"/>
-      <c r="B94" s="113"/>
-      <c r="C94" s="113"/>
-      <c r="D94" s="113"/>
-      <c r="E94" s="113"/>
+      <c r="A94" s="43"/>
+      <c r="B94" s="79"/>
+      <c r="C94" s="79"/>
+      <c r="D94" s="79"/>
+      <c r="E94" s="79"/>
       <c r="F94"/>
-      <c r="G94" s="53"/>
+      <c r="G94" s="169"/>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
       <c r="J94" s="1"/>
     </row>
     <row r="95" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B95" s="147" t="s">
+      <c r="B95" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="C95" s="147"/>
-      <c r="D95" s="147"/>
-      <c r="E95" s="147"/>
-      <c r="F95" s="147"/>
-      <c r="G95" s="53"/>
+      <c r="C95" s="111"/>
+      <c r="D95" s="111"/>
+      <c r="E95" s="111"/>
+      <c r="F95" s="111"/>
+      <c r="G95" s="169"/>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
       <c r="J95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A96" s="75"/>
-      <c r="B96" s="105"/>
-      <c r="C96" s="105"/>
-      <c r="D96" s="105"/>
-      <c r="E96" s="105"/>
-      <c r="F96" s="105"/>
-      <c r="G96" s="53"/>
+      <c r="A96" s="43"/>
+      <c r="B96" s="71"/>
+      <c r="C96" s="71"/>
+      <c r="D96" s="71"/>
+      <c r="E96" s="71"/>
+      <c r="F96" s="71"/>
+      <c r="G96" s="169"/>
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
       <c r="J96" s="1"/>
     </row>
     <row r="97" spans="1:10" ht="132.75" customHeight="1">
-      <c r="A97" s="75" t="s">
+      <c r="A97" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="B97" s="147" t="s">
+      <c r="B97" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="C97" s="147"/>
-      <c r="D97" s="147"/>
-      <c r="E97" s="147"/>
-      <c r="F97" s="147"/>
-      <c r="G97" s="58"/>
+      <c r="C97" s="111"/>
+      <c r="D97" s="111"/>
+      <c r="E97" s="111"/>
+      <c r="F97" s="111"/>
+      <c r="G97" s="175"/>
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
     </row>
     <row r="98" spans="1:10" ht="12.75" customHeight="1">
       <c r="A98" s="4"/>
-      <c r="B98" s="75"/>
-      <c r="C98" s="105"/>
-      <c r="D98" s="105"/>
-      <c r="E98" s="105"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="71"/>
+      <c r="D98" s="71"/>
+      <c r="E98" s="71"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="59"/>
+      <c r="G98" s="176"/>
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
       <c r="J98" s="1"/>
     </row>
     <row r="99" spans="1:10" ht="41.25" customHeight="1">
       <c r="A99" s="4"/>
-      <c r="B99" s="149" t="s">
+      <c r="B99" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="C99" s="149"/>
-      <c r="D99" s="149"/>
-      <c r="E99" s="149"/>
-      <c r="F99" s="105"/>
-      <c r="G99" s="58"/>
+      <c r="C99" s="140"/>
+      <c r="D99" s="140"/>
+      <c r="E99" s="140"/>
+      <c r="F99" s="71"/>
+      <c r="G99" s="175"/>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
       <c r="J99" s="1"/>
     </row>
     <row r="100" spans="1:10" ht="9" customHeight="1">
       <c r="A100" s="4"/>
-      <c r="B100" s="105"/>
-      <c r="C100" s="105"/>
-      <c r="D100" s="105"/>
-      <c r="E100" s="105"/>
-      <c r="F100" s="105"/>
-      <c r="G100" s="58"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="71"/>
+      <c r="D100" s="71"/>
+      <c r="E100" s="71"/>
+      <c r="F100" s="71"/>
+      <c r="G100" s="175"/>
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
     </row>
     <row r="101" spans="1:10" ht="39.75" customHeight="1">
       <c r="A101" s="4"/>
-      <c r="B101" s="149" t="s">
+      <c r="B101" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="C101" s="149"/>
-      <c r="D101" s="149"/>
-      <c r="E101" s="149"/>
-      <c r="F101" s="105"/>
-      <c r="G101" s="60"/>
+      <c r="C101" s="140"/>
+      <c r="D101" s="140"/>
+      <c r="E101" s="140"/>
+      <c r="F101" s="71"/>
+      <c r="G101" s="177"/>
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
       <c r="J101" s="1"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="4"/>
-      <c r="B102" s="105"/>
-      <c r="C102" s="105"/>
-      <c r="D102" s="105"/>
-      <c r="E102" s="105"/>
-      <c r="F102" s="105"/>
-      <c r="G102" s="58"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="71"/>
+      <c r="D102" s="71"/>
+      <c r="E102" s="71"/>
+      <c r="F102" s="71"/>
+      <c r="G102" s="175"/>
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
     </row>
     <row r="103" spans="1:10" ht="29.25" customHeight="1">
       <c r="A103" s="4"/>
-      <c r="B103" s="149" t="s">
+      <c r="B103" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="C103" s="149"/>
-      <c r="D103" s="149"/>
-      <c r="E103" s="149"/>
-      <c r="F103" s="105"/>
-      <c r="G103" s="58"/>
+      <c r="C103" s="140"/>
+      <c r="D103" s="140"/>
+      <c r="E103" s="140"/>
+      <c r="F103" s="71"/>
+      <c r="G103" s="175"/>
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
       <c r="J103" s="1"/>
@@ -3839,21 +3826,21 @@
       <c r="D104" s="25"/>
       <c r="E104" s="25"/>
       <c r="F104" s="25"/>
-      <c r="G104" s="26"/>
+      <c r="G104" s="158"/>
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
       <c r="J104" s="1"/>
     </row>
     <row r="105" spans="1:10" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
-      <c r="B105" s="149" t="s">
+      <c r="B105" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="149"/>
-      <c r="D105" s="149"/>
-      <c r="E105" s="149"/>
-      <c r="F105" s="149"/>
-      <c r="G105" s="58"/>
+      <c r="C105" s="140"/>
+      <c r="D105" s="140"/>
+      <c r="E105" s="140"/>
+      <c r="F105" s="140"/>
+      <c r="G105" s="175"/>
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
       <c r="J105" s="1"/>
@@ -3865,7 +3852,7 @@
       <c r="D106" s="25"/>
       <c r="E106" s="25"/>
       <c r="F106" s="25"/>
-      <c r="G106" s="26"/>
+      <c r="G106" s="158"/>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -3877,20 +3864,20 @@
       <c r="D107" s="25"/>
       <c r="E107" s="25"/>
       <c r="F107" s="25"/>
-      <c r="G107" s="26"/>
+      <c r="G107" s="158"/>
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
       <c r="J107" s="1"/>
     </row>
     <row r="108" spans="1:10" ht="31.5">
-      <c r="B108" s="107" t="s">
+      <c r="B108" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="C108" s="107"/>
-      <c r="D108" s="107"/>
-      <c r="E108" s="107"/>
-      <c r="F108" s="107"/>
-      <c r="G108" s="26"/>
+      <c r="C108" s="73"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="73"/>
+      <c r="F108" s="73"/>
+      <c r="G108" s="158"/>
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
       <c r="J108" s="1"/>
@@ -3901,20 +3888,20 @@
       <c r="D109" s="25"/>
       <c r="E109" s="25"/>
       <c r="F109" s="25"/>
-      <c r="G109" s="26"/>
+      <c r="G109" s="158"/>
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
       <c r="J109" s="1"/>
     </row>
     <row r="110" spans="1:10" ht="12.75" customHeight="1">
-      <c r="B110" s="146" t="s">
+      <c r="B110" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="146"/>
-      <c r="D110" s="146"/>
-      <c r="E110" s="146"/>
-      <c r="F110" s="146"/>
-      <c r="G110" s="26"/>
+      <c r="C110" s="138"/>
+      <c r="D110" s="138"/>
+      <c r="E110" s="138"/>
+      <c r="F110" s="138"/>
+      <c r="G110" s="158"/>
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
@@ -3925,71 +3912,110 @@
       <c r="D111"/>
       <c r="E111"/>
       <c r="F111"/>
-      <c r="G111" s="26"/>
+      <c r="G111" s="158"/>
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
     </row>
     <row r="112" spans="1:10" ht="17.25" customHeight="1">
-      <c r="B112" s="146" t="s">
+      <c r="B112" s="138" t="s">
         <v>52</v>
       </c>
-      <c r="C112" s="146"/>
-      <c r="D112" s="146"/>
-      <c r="E112" s="146"/>
-      <c r="F112" s="146"/>
-      <c r="G112" s="26"/>
+      <c r="C112" s="138"/>
+      <c r="D112" s="138"/>
+      <c r="E112" s="138"/>
+      <c r="F112" s="138"/>
+      <c r="G112" s="158"/>
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
     </row>
-    <row r="113" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="113" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="B113" s="6"/>
       <c r="C113"/>
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113"/>
-      <c r="G113" s="26"/>
+      <c r="G113" s="158"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10" ht="18.75" customHeight="1">
+    <row r="114" spans="1:23" ht="18.75" customHeight="1">
       <c r="B114" s="6"/>
       <c r="C114"/>
       <c r="D114"/>
       <c r="E114"/>
       <c r="F114"/>
-      <c r="G114" s="26"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1">
-      <c r="B115" s="82" t="s">
+      <c r="G114" s="158"/>
+      <c r="H114" s="178"/>
+      <c r="I114" s="178"/>
+      <c r="J114" s="178"/>
+      <c r="K114" s="178"/>
+      <c r="L114" s="178"/>
+      <c r="M114" s="178"/>
+      <c r="N114" s="178"/>
+      <c r="O114" s="178"/>
+      <c r="P114" s="178"/>
+      <c r="Q114" s="178"/>
+      <c r="R114" s="178"/>
+      <c r="S114" s="178"/>
+      <c r="T114" s="178"/>
+      <c r="U114" s="178"/>
+      <c r="V114" s="178"/>
+      <c r="W114" s="178"/>
+    </row>
+    <row r="115" spans="1:23" ht="15" customHeight="1">
+      <c r="B115" s="50" t="s">
         <v>34</v>
       </c>
       <c r="C115"/>
       <c r="D115"/>
       <c r="E115"/>
       <c r="F115"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" ht="0.75" customHeight="1">
+      <c r="G115" s="158"/>
+      <c r="H115" s="178"/>
+      <c r="I115" s="178"/>
+      <c r="J115" s="178"/>
+      <c r="K115" s="178"/>
+      <c r="L115" s="178"/>
+      <c r="M115" s="178"/>
+      <c r="N115" s="178"/>
+      <c r="O115" s="178"/>
+      <c r="P115" s="178"/>
+      <c r="Q115" s="178"/>
+      <c r="R115" s="178"/>
+      <c r="S115" s="178"/>
+      <c r="T115" s="178"/>
+      <c r="U115" s="178"/>
+      <c r="V115" s="178"/>
+      <c r="W115" s="178"/>
+    </row>
+    <row r="116" spans="1:23" ht="0.75" customHeight="1">
       <c r="B116" s="6"/>
       <c r="C116"/>
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116"/>
-      <c r="G116" s="26"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="16.5" customHeight="1">
+      <c r="G116" s="158"/>
+      <c r="H116" s="178"/>
+      <c r="I116" s="178"/>
+      <c r="J116" s="178"/>
+      <c r="K116" s="178"/>
+      <c r="L116" s="178"/>
+      <c r="M116" s="178"/>
+      <c r="N116" s="178"/>
+      <c r="O116" s="178"/>
+      <c r="P116" s="178"/>
+      <c r="Q116" s="178"/>
+      <c r="R116" s="178"/>
+      <c r="S116" s="178"/>
+      <c r="T116" s="178"/>
+      <c r="U116" s="178"/>
+      <c r="V116" s="178"/>
+      <c r="W116" s="178"/>
+    </row>
+    <row r="117" spans="1:23" ht="16.5" customHeight="1">
       <c r="B117" s="6"/>
       <c r="C117"/>
       <c r="D117"/>
@@ -3997,37 +4023,93 @@
         <v>73</v>
       </c>
       <c r="F117" s="3"/>
-      <c r="G117" s="26"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="9.9499999999999993" customHeight="1">
+      <c r="G117" s="158"/>
+      <c r="H117" s="178"/>
+      <c r="I117" s="178"/>
+      <c r="J117" s="178"/>
+      <c r="K117" s="178"/>
+      <c r="L117" s="178"/>
+      <c r="M117" s="178"/>
+      <c r="N117" s="178"/>
+      <c r="O117" s="178"/>
+      <c r="P117" s="178"/>
+      <c r="Q117" s="178"/>
+      <c r="R117" s="178"/>
+      <c r="S117" s="178"/>
+      <c r="T117" s="178"/>
+      <c r="U117" s="178"/>
+      <c r="V117" s="178"/>
+      <c r="W117" s="178"/>
+    </row>
+    <row r="118" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A118" s="1"/>
       <c r="B118" s="20"/>
-      <c r="C118" s="67"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="9.9499999999999993" customHeight="1">
-      <c r="A119" s="1"/>
-      <c r="B119" s="20"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="9.9499999999999993" customHeight="1">
+      <c r="C118" s="35"/>
+      <c r="G118" s="179"/>
+      <c r="H118" s="178"/>
+      <c r="I118" s="178"/>
+      <c r="J118" s="178"/>
+      <c r="K118" s="178"/>
+      <c r="L118" s="178"/>
+      <c r="M118" s="178"/>
+      <c r="N118" s="178"/>
+      <c r="O118" s="178"/>
+      <c r="P118" s="178"/>
+      <c r="Q118" s="178"/>
+      <c r="R118" s="178"/>
+      <c r="S118" s="178"/>
+      <c r="T118" s="178"/>
+      <c r="U118" s="178"/>
+      <c r="V118" s="178"/>
+      <c r="W118" s="178"/>
+    </row>
+    <row r="119" spans="1:23" ht="9.9499999999999993" customHeight="1">
+      <c r="A119" s="180"/>
+      <c r="B119" s="181"/>
+      <c r="C119" s="180"/>
+      <c r="D119" s="180"/>
+      <c r="E119" s="180"/>
+      <c r="F119" s="180"/>
+      <c r="G119" s="179"/>
+      <c r="H119" s="178"/>
+      <c r="I119" s="178"/>
+      <c r="J119" s="178"/>
+      <c r="K119" s="178"/>
+      <c r="L119" s="178"/>
+      <c r="M119" s="178"/>
+      <c r="N119" s="178"/>
+      <c r="O119" s="178"/>
+      <c r="P119" s="178"/>
+      <c r="Q119" s="178"/>
+      <c r="R119" s="178"/>
+      <c r="S119" s="178"/>
+      <c r="T119" s="178"/>
+      <c r="U119" s="178"/>
+      <c r="V119" s="178"/>
+      <c r="W119" s="178"/>
+    </row>
+    <row r="120" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A120" s="1"/>
       <c r="B120" s="20"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="9.9499999999999993" customHeight="1">
+      <c r="G120" s="178"/>
+      <c r="H120" s="178"/>
+      <c r="I120" s="178"/>
+      <c r="J120" s="178"/>
+      <c r="K120" s="178"/>
+      <c r="L120" s="178"/>
+      <c r="M120" s="178"/>
+      <c r="N120" s="178"/>
+      <c r="O120" s="178"/>
+      <c r="P120" s="178"/>
+      <c r="Q120" s="178"/>
+      <c r="R120" s="178"/>
+      <c r="S120" s="178"/>
+      <c r="T120" s="178"/>
+      <c r="U120" s="178"/>
+      <c r="V120" s="178"/>
+      <c r="W120" s="178"/>
+    </row>
+    <row r="121" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A121" s="1"/>
       <c r="B121" s="20"/>
       <c r="G121" s="1"/>
@@ -4035,7 +4117,7 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="122" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="20"/>
       <c r="G122" s="1"/>
@@ -4043,7 +4125,7 @@
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="123" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A123" s="1"/>
       <c r="B123" s="20"/>
       <c r="G123" s="1"/>
@@ -4051,7 +4133,7 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="124" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A124" s="1"/>
       <c r="B124" s="20"/>
       <c r="G124" s="1"/>
@@ -4059,7 +4141,7 @@
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="125" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A125" s="1"/>
       <c r="B125" s="20"/>
       <c r="G125" s="1"/>
@@ -4067,7 +4149,7 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="126" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A126" s="1"/>
       <c r="B126" s="20"/>
       <c r="G126" s="1"/>
@@ -4075,7 +4157,7 @@
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="127" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A127" s="1"/>
       <c r="B127" s="20"/>
       <c r="G127" s="1"/>
@@ -4083,7 +4165,7 @@
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" ht="9.9499999999999993" customHeight="1">
+    <row r="128" spans="1:23" ht="9.9499999999999993" customHeight="1">
       <c r="A128" s="1"/>
       <c r="B128" s="20"/>
       <c r="G128" s="1"/>
@@ -10007,6 +10089,43 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0"/>
   <dataConsolidate/>
   <mergeCells count="53">
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="A1:F4"/>
     <mergeCell ref="D17:F17"/>
@@ -10023,43 +10142,6 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B97:F97"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" display="www.BOYDSIGNSYSTEMS.com                                                                     " xr:uid="{00000000-0004-0000-0200-000000000000}"/>

--- a/templates/Blank.xlsx
+++ b/templates/Blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efinney\Desktop\Chat GPT\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA36538-4C21-4204-91AE-7DC9CD03C42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A7DACF-0F5F-4796-BF95-AED63C8A24D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proposal" sheetId="19" r:id="rId1"/>
@@ -1321,7 +1321,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1362,9 +1362,6 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
@@ -1695,25 +1692,203 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="39" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1755,194 +1930,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="39" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2331,7 +2340,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor theme="3" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:W1286"/>
+  <dimension ref="A1:K1286"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="7" customWidth="1"/>
@@ -2340,10 +2349,10 @@
     <col min="4" max="4" width="8.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="22" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" style="22" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" style="21" customWidth="1"/>
-    <col min="10" max="10" width="5.140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="5.140625" style="20" customWidth="1"/>
     <col min="11" max="11" width="58" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" style="1" customWidth="1"/>
@@ -2358,1664 +2367,1782 @@
     <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A1" s="112" t="e" vm="1">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1">
+      <c r="A1" s="164" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" ht="12.6" customHeight="1">
-      <c r="A2" s="112"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="112"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="146"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" ht="12.2" customHeight="1">
-      <c r="A4" s="112"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="B5" s="51" t="s">
+      <c r="B1" s="164"/>
+      <c r="C1" s="164"/>
+      <c r="D1" s="164"/>
+      <c r="E1" s="164"/>
+      <c r="F1" s="164"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+    </row>
+    <row r="2" spans="1:11" ht="12.6" customHeight="1">
+      <c r="A2" s="164"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="178"/>
+      <c r="I2" s="178"/>
+      <c r="J2" s="178"/>
+      <c r="K2" s="178"/>
+    </row>
+    <row r="3" spans="1:11" ht="17.100000000000001" customHeight="1">
+      <c r="A3" s="164"/>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="178"/>
+      <c r="I3" s="178"/>
+      <c r="J3" s="178"/>
+      <c r="K3" s="178"/>
+    </row>
+    <row r="4" spans="1:11" ht="12.2" customHeight="1">
+      <c r="A4" s="164"/>
+      <c r="B4" s="164"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="164"/>
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="114"/>
+      <c r="H4" s="178"/>
+      <c r="I4" s="178"/>
+      <c r="J4" s="178"/>
+      <c r="K4" s="178"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1">
+      <c r="B5" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="51"/>
+      <c r="D5" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" ht="11.45" customHeight="1">
-      <c r="C6" s="58"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" ht="12.2" customHeight="1">
-      <c r="B7" s="54"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66" t="s">
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
+    </row>
+    <row r="6" spans="1:11" ht="11.45" customHeight="1">
+      <c r="C6" s="57"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="178"/>
+      <c r="I6" s="178"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
+    </row>
+    <row r="7" spans="1:11" ht="12.2" customHeight="1">
+      <c r="B7" s="53"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="178"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" customHeight="1">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" customFormat="1" ht="18.75" hidden="1" customHeight="1">
+      <c r="C8" s="65"/>
+      <c r="D8" s="166"/>
+      <c r="E8" s="166"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="178"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="178"/>
+      <c r="K8" s="178"/>
+    </row>
+    <row r="9" spans="1:11" customFormat="1" ht="18.75" hidden="1" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" s="8" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="124" t="s">
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="179"/>
+      <c r="J9" s="179"/>
+      <c r="K9" s="179"/>
+    </row>
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="67" t="s">
+      <c r="B10" s="173"/>
+      <c r="C10" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="119" t="s">
+      <c r="D10" s="167" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="150"/>
-    </row>
-    <row r="11" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A11" s="126"/>
-      <c r="B11" s="127"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="151"/>
-    </row>
-    <row r="12" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A12" s="129"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="152"/>
-    </row>
-    <row r="13" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A13" s="129"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="114"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="152"/>
-    </row>
-    <row r="14" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A14" s="129"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="151"/>
-    </row>
-    <row r="15" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A15" s="129"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="151"/>
-    </row>
-    <row r="16" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A16" s="129"/>
-      <c r="B16" s="131"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="141"/>
-      <c r="G16" s="153"/>
-    </row>
-    <row r="17" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A17" s="129"/>
-      <c r="B17" s="131"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="114"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="153"/>
-    </row>
-    <row r="18" spans="1:10" ht="12.75" hidden="1" customHeight="1">
-      <c r="A18" s="55"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="168"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="180"/>
+      <c r="I10" s="180"/>
+      <c r="J10" s="180"/>
+      <c r="K10" s="180"/>
+    </row>
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A11" s="174"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="170"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="180"/>
+      <c r="J11" s="180"/>
+      <c r="K11" s="180"/>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A12" s="162"/>
+      <c r="B12" s="177"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="158"/>
+      <c r="F12" s="158"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="180"/>
+      <c r="J12" s="180"/>
+      <c r="K12" s="180"/>
+    </row>
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A13" s="162"/>
+      <c r="B13" s="163"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="158"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="180"/>
+      <c r="J13" s="180"/>
+      <c r="K13" s="180"/>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A14" s="162"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="180"/>
+      <c r="J14" s="180"/>
+      <c r="K14" s="180"/>
+    </row>
+    <row r="15" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A15" s="162"/>
+      <c r="B15" s="163"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="159"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="180"/>
+      <c r="I15" s="180"/>
+      <c r="J15" s="180"/>
+      <c r="K15" s="180"/>
+    </row>
+    <row r="16" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A16" s="162"/>
+      <c r="B16" s="163"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="180"/>
+      <c r="I16" s="180"/>
+      <c r="J16" s="180"/>
+      <c r="K16" s="180"/>
+    </row>
+    <row r="17" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A17" s="162"/>
+      <c r="B17" s="163"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="180"/>
+      <c r="J17" s="180"/>
+      <c r="K17" s="180"/>
+    </row>
+    <row r="18" spans="1:11" ht="12.75" hidden="1" customHeight="1">
+      <c r="A18" s="54"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="154"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A19" s="57"/>
-      <c r="B19" s="123"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="155"/>
-    </row>
-    <row r="20" spans="1:10" ht="4.7" customHeight="1">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" s="9" customFormat="1" ht="14.45" customHeight="1">
-      <c r="A21" s="68" t="s">
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="178"/>
+      <c r="I18" s="178"/>
+      <c r="J18" s="178"/>
+      <c r="K18" s="178"/>
+    </row>
+    <row r="19" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A19" s="56"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="171"/>
+      <c r="D19" s="171"/>
+      <c r="E19" s="171"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="180"/>
+      <c r="I19" s="180"/>
+      <c r="J19" s="180"/>
+      <c r="K19" s="180"/>
+    </row>
+    <row r="20" spans="1:11" ht="4.7" customHeight="1">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="178"/>
+      <c r="J20" s="178"/>
+      <c r="K20" s="178"/>
+    </row>
+    <row r="21" spans="1:11" s="9" customFormat="1" ht="14.45" customHeight="1">
+      <c r="A21" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="68"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="157"/>
-    </row>
-    <row r="22" spans="1:10" ht="11.45" customHeight="1">
-      <c r="A22" s="132" t="s">
+      <c r="E21" s="68"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="181"/>
+    </row>
+    <row r="22" spans="1:11" ht="11.45" customHeight="1">
+      <c r="A22" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="132"/>
-      <c r="C22" s="128"/>
-      <c r="D22" s="128"/>
-      <c r="E22" s="128"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="158"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" ht="11.45" customHeight="1">
-      <c r="A23" s="132" t="s">
+      <c r="B22" s="156"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="176"/>
+      <c r="F22" s="176"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="178"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="178"/>
+      <c r="K22" s="178"/>
+    </row>
+    <row r="23" spans="1:11" ht="11.45" customHeight="1">
+      <c r="A23" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="132"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="158"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="9" customHeight="1">
-      <c r="B24" s="28"/>
-      <c r="G24" s="158"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="70" t="s">
+      <c r="B23" s="156"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="176"/>
+      <c r="F23" s="176"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="178"/>
+      <c r="I23" s="178"/>
+      <c r="J23" s="178"/>
+      <c r="K23" s="178"/>
+    </row>
+    <row r="24" spans="1:11" ht="9" customHeight="1">
+      <c r="B24" s="27"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="178"/>
+      <c r="I24" s="178"/>
+      <c r="J24" s="178"/>
+      <c r="K24" s="178"/>
+    </row>
+    <row r="25" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A25" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="60"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10" s="10" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="B25" s="59"/>
+      <c r="C25" s="161"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="178"/>
+      <c r="J25" s="178"/>
+      <c r="K25" s="178"/>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A26" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="F26" s="143" t="s">
+      <c r="F26" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="160"/>
-    </row>
-    <row r="27" spans="1:10" s="10" customFormat="1" ht="1.5" hidden="1" customHeight="1">
-      <c r="A27" s="61">
+      <c r="G26" s="128"/>
+      <c r="H26" s="182"/>
+      <c r="I26" s="182"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="182"/>
+    </row>
+    <row r="27" spans="1:11" s="10" customFormat="1" ht="1.5" hidden="1" customHeight="1">
+      <c r="A27" s="60">
         <v>0</v>
       </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="160"/>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="88">
+      <c r="B27" s="61"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="182"/>
+      <c r="I27" s="182"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="182"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="87">
         <f>+A27+1</f>
         <v>1</v>
       </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="145" t="str">
+      <c r="B28" s="88"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="113" t="str">
         <f>IF(D28&lt;&gt;"",D28*E28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G28" s="161"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="88">
+      <c r="G28" s="129"/>
+      <c r="H28" s="178"/>
+      <c r="I28" s="178"/>
+      <c r="J28" s="178"/>
+      <c r="K28" s="178"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="87">
         <f t="shared" ref="A29:A47" si="0">+A28+1</f>
         <v>2</v>
       </c>
-      <c r="B29" s="104"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="91"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="145" t="str">
+      <c r="B29" s="103"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="90"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="113" t="str">
         <f t="shared" ref="F29:F44" si="1">IF(D29&lt;&gt;"",D29*E29," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G29" s="161"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="88">
+      <c r="G29" s="129"/>
+      <c r="H29" s="178"/>
+      <c r="I29" s="178"/>
+      <c r="J29" s="178"/>
+      <c r="K29" s="178"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="87">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B30" s="104"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="106"/>
-      <c r="F30" s="145" t="str">
+      <c r="B30" s="103"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G30" s="161"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="88">
+      <c r="G30" s="129"/>
+      <c r="H30" s="178"/>
+      <c r="I30" s="178"/>
+      <c r="J30" s="178"/>
+      <c r="K30" s="178"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="87">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B31" s="104"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="106"/>
-      <c r="F31" s="145" t="str">
+      <c r="B31" s="103"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G31" s="161"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="88">
+      <c r="G31" s="129"/>
+      <c r="H31" s="178"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="178"/>
+      <c r="K31" s="178"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="87">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B32" s="104"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="106"/>
-      <c r="F32" s="145" t="str">
+      <c r="B32" s="103"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G32" s="161"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="88">
+      <c r="G32" s="129"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="178"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="87">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B33" s="104"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="145" t="str">
+      <c r="B33" s="103"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="90"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G33" s="161"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="88">
+      <c r="G33" s="129"/>
+      <c r="H33" s="178"/>
+      <c r="I33" s="178"/>
+      <c r="J33" s="178"/>
+      <c r="K33" s="178"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="87">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B34" s="104"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="145" t="str">
+      <c r="B34" s="103"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G34" s="161"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="88">
+      <c r="G34" s="129"/>
+      <c r="H34" s="178"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="87">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B35" s="104"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="145" t="str">
+      <c r="B35" s="103"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G35" s="161"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="88">
+      <c r="G35" s="129"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="87">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B36" s="104"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="145" t="str">
+      <c r="B36" s="103"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G36" s="161"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="88">
+      <c r="G36" s="129"/>
+      <c r="H36" s="178"/>
+      <c r="I36" s="178"/>
+      <c r="J36" s="178"/>
+      <c r="K36" s="178"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="87">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B37" s="104"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="91"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="145" t="str">
+      <c r="B37" s="103"/>
+      <c r="C37" s="104"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G37" s="161"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="88">
+      <c r="G37" s="129"/>
+      <c r="H37" s="178"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="87">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B38" s="104"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="145" t="str">
+      <c r="B38" s="103"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G38" s="162"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="88">
+      <c r="G38" s="130"/>
+      <c r="H38" s="178"/>
+      <c r="I38" s="178"/>
+      <c r="J38" s="178"/>
+      <c r="K38" s="178"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="87">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B39" s="104"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="145" t="str">
+      <c r="B39" s="103"/>
+      <c r="C39" s="104"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G39" s="162"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-    </row>
-    <row r="40" spans="1:10" ht="24.75" hidden="1" customHeight="1" thickBot="1">
-      <c r="A40" s="88">
+      <c r="G39" s="130"/>
+      <c r="H39" s="178"/>
+      <c r="I39" s="178"/>
+      <c r="J39" s="178"/>
+      <c r="K39" s="178"/>
+    </row>
+    <row r="40" spans="1:11" ht="24.75" hidden="1" customHeight="1" thickBot="1">
+      <c r="A40" s="87">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B40" s="104"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="145" t="str">
+      <c r="B40" s="103"/>
+      <c r="C40" s="104"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G40" s="161"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-    </row>
-    <row r="41" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A41" s="88">
+      <c r="G40" s="129"/>
+      <c r="H40" s="178"/>
+      <c r="I40" s="178"/>
+      <c r="J40" s="178"/>
+      <c r="K40" s="178"/>
+    </row>
+    <row r="41" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A41" s="87">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B41" s="104"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="145" t="str">
+      <c r="B41" s="103"/>
+      <c r="C41" s="104"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G41" s="163"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A42" s="88">
+      <c r="G41" s="131"/>
+      <c r="H41" s="178"/>
+      <c r="I41" s="178"/>
+      <c r="J41" s="178"/>
+      <c r="K41" s="178"/>
+    </row>
+    <row r="42" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A42" s="87">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B42" s="104"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="145" t="str">
+      <c r="B42" s="103"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G42" s="164"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A43" s="88">
+      <c r="G42" s="132"/>
+      <c r="H42" s="178"/>
+      <c r="I42" s="178"/>
+      <c r="J42" s="178"/>
+      <c r="K42" s="178"/>
+    </row>
+    <row r="43" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A43" s="87">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B43" s="104"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="145" t="str">
+      <c r="B43" s="103"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G43" s="164"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A44" s="88">
+      <c r="G43" s="132"/>
+      <c r="H43" s="178"/>
+      <c r="I43" s="178"/>
+      <c r="J43" s="178"/>
+      <c r="K43" s="178"/>
+    </row>
+    <row r="44" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A44" s="87">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B44" s="104"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="145" t="str">
+      <c r="B44" s="103"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G44" s="165"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A45" s="88">
+      <c r="G44" s="133"/>
+      <c r="H44" s="183"/>
+      <c r="I44" s="183"/>
+      <c r="J44" s="178"/>
+      <c r="K44" s="178"/>
+    </row>
+    <row r="45" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A45" s="87">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B45" s="104"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="145" t="str">
+      <c r="B45" s="103"/>
+      <c r="C45" s="104"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="113" t="str">
         <f t="shared" ref="F45:F47" si="2">IF(D45&lt;&gt;"",D45*E45," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G45" s="164"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A46" s="88">
+      <c r="G45" s="132"/>
+      <c r="H45" s="178"/>
+      <c r="I45" s="178"/>
+      <c r="J45" s="178"/>
+      <c r="K45" s="178"/>
+    </row>
+    <row r="46" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A46" s="87">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B46" s="104"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="145" t="str">
+      <c r="B46" s="103"/>
+      <c r="C46" s="104"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="113" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G46" s="164"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A47" s="88">
+      <c r="G46" s="132"/>
+      <c r="H46" s="178"/>
+      <c r="I46" s="178"/>
+      <c r="J46" s="178"/>
+      <c r="K46" s="178"/>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A47" s="87">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="145" t="str">
+      <c r="B47" s="103"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="113" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G47" s="166"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A48" s="93"/>
-      <c r="B48" s="83"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="86" t="s">
+      <c r="G47" s="134"/>
+      <c r="H47" s="178"/>
+      <c r="I47" s="178"/>
+      <c r="J47" s="178"/>
+      <c r="K47" s="178"/>
+    </row>
+    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A48" s="92"/>
+      <c r="B48" s="82"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="87">
+      <c r="F48" s="86">
         <f>SUM(F28:F47)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="167"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" ht="16.149999999999999" customHeight="1">
-      <c r="A49" s="41"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="75"/>
-      <c r="E49" s="42" t="s">
+      <c r="G48" s="135"/>
+      <c r="H48" s="178"/>
+      <c r="I48" s="178"/>
+      <c r="J48" s="178"/>
+      <c r="K48" s="178"/>
+    </row>
+    <row r="49" spans="1:11" ht="16.149999999999999" customHeight="1">
+      <c r="A49" s="40"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="74"/>
+      <c r="E49" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="80"/>
-      <c r="G49" s="168"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" ht="12" customHeight="1">
-      <c r="A50" s="41"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="75"/>
+      <c r="F49" s="79"/>
+      <c r="G49" s="136"/>
+      <c r="H49" s="178"/>
+      <c r="I49" s="178"/>
+      <c r="J49" s="178"/>
+      <c r="K49" s="178"/>
+    </row>
+    <row r="50" spans="1:11" ht="12" customHeight="1">
+      <c r="A50" s="40"/>
+      <c r="B50" s="73"/>
+      <c r="C50" s="74"/>
       <c r="E50" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F50" s="80">
+      <c r="F50" s="79">
         <v>0</v>
       </c>
-      <c r="G50" s="158"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" s="19" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A51" s="41"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="76"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="178"/>
+      <c r="I50" s="178"/>
+      <c r="J50" s="178"/>
+      <c r="K50" s="178"/>
+    </row>
+    <row r="51" spans="1:11" s="18" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A51" s="40"/>
+      <c r="B51" s="73"/>
+      <c r="C51" s="75"/>
       <c r="D51" s="12"/>
       <c r="E51" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F51" s="103">
+      <c r="F51" s="102">
         <v>0</v>
       </c>
-      <c r="G51" s="169"/>
-    </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1">
-      <c r="A52" s="39"/>
-      <c r="B52" s="74"/>
-      <c r="C52" s="77"/>
+      <c r="G51" s="137"/>
+      <c r="H51" s="184"/>
+      <c r="I51" s="184"/>
+      <c r="J51" s="184"/>
+      <c r="K51" s="184"/>
+    </row>
+    <row r="52" spans="1:11" ht="15" customHeight="1">
+      <c r="A52" s="38"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="76"/>
       <c r="D52" s="12"/>
       <c r="E52" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="F52" s="102">
+      <c r="F52" s="101">
         <v>0</v>
       </c>
-      <c r="G52" s="158"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-    </row>
-    <row r="53" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="G52" s="126"/>
+      <c r="H52" s="178"/>
+      <c r="I52" s="178"/>
+      <c r="J52" s="178"/>
+      <c r="K52" s="178"/>
+    </row>
+    <row r="53" spans="1:11" ht="18" customHeight="1" thickBot="1">
       <c r="A53" s="4"/>
-      <c r="B53" s="37"/>
-      <c r="C53" s="38"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
       <c r="D53"/>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F53" s="81"/>
-      <c r="G53" s="169"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-    </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A54" s="41"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="18" t="s">
+      <c r="F53" s="80"/>
+      <c r="G53" s="137"/>
+      <c r="H53" s="178"/>
+      <c r="I53" s="178"/>
+      <c r="J53" s="178"/>
+      <c r="K53" s="178"/>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A54" s="40"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="F54" s="78">
+      <c r="F54" s="77">
         <f>+F53+F52+F49+F48+F50</f>
         <v>0</v>
       </c>
-      <c r="G54" s="158"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="5.25" customHeight="1">
-      <c r="A55" s="107"/>
-      <c r="B55" s="108"/>
-      <c r="C55" s="108"/>
-      <c r="D55" s="108"/>
-      <c r="E55" s="109"/>
-      <c r="F55" s="110"/>
-      <c r="G55" s="170"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" ht="15">
-      <c r="A56" s="98" t="s">
+      <c r="G54" s="126"/>
+      <c r="H54" s="178"/>
+      <c r="I54" s="178"/>
+      <c r="J54" s="178"/>
+      <c r="K54" s="178"/>
+    </row>
+    <row r="55" spans="1:11" ht="5.25" customHeight="1">
+      <c r="A55" s="106"/>
+      <c r="B55" s="107"/>
+      <c r="C55" s="107"/>
+      <c r="D55" s="107"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="109"/>
+      <c r="G55" s="138"/>
+      <c r="H55" s="178"/>
+      <c r="I55" s="178"/>
+      <c r="J55" s="178"/>
+      <c r="K55" s="178"/>
+    </row>
+    <row r="56" spans="1:11" ht="15">
+      <c r="A56" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="98"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="98"/>
-      <c r="E56" s="98"/>
-      <c r="F56" s="98"/>
-      <c r="G56" s="171"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1">
+      <c r="B56" s="97"/>
+      <c r="C56" s="97"/>
+      <c r="D56" s="97"/>
+      <c r="E56" s="97"/>
+      <c r="F56" s="97"/>
+      <c r="G56" s="139"/>
+      <c r="H56" s="178"/>
+      <c r="I56" s="178"/>
+      <c r="J56" s="178"/>
+      <c r="K56" s="178"/>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
       <c r="F57"/>
-      <c r="G57" s="171"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A58" s="43" t="s">
+      <c r="G57" s="139"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="178"/>
+      <c r="J57" s="178"/>
+      <c r="K57" s="178"/>
+    </row>
+    <row r="58" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A58" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B58" s="111" t="s">
+      <c r="B58" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="C58" s="111"/>
-      <c r="D58" s="111"/>
-      <c r="E58" s="111"/>
-      <c r="F58" s="111"/>
-      <c r="G58" s="158"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" ht="2.25" customHeight="1">
-      <c r="A59" s="43"/>
-      <c r="B59" s="43"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="71"/>
-      <c r="E59" s="71"/>
+      <c r="C58" s="149"/>
+      <c r="D58" s="149"/>
+      <c r="E58" s="149"/>
+      <c r="F58" s="149"/>
+      <c r="G58" s="126"/>
+      <c r="H58" s="178"/>
+      <c r="I58" s="178"/>
+      <c r="J58" s="178"/>
+      <c r="K58" s="178"/>
+    </row>
+    <row r="59" spans="1:11" ht="2.25" customHeight="1">
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
       <c r="F59"/>
-      <c r="G59" s="169"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-    </row>
-    <row r="60" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A60" s="43" t="s">
+      <c r="G59" s="137"/>
+      <c r="H59" s="178"/>
+      <c r="I59" s="178"/>
+      <c r="J59" s="178"/>
+      <c r="K59" s="178"/>
+    </row>
+    <row r="60" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A60" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B60" s="111" t="s">
+      <c r="B60" s="149" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="111"/>
-      <c r="D60" s="111"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="111"/>
-      <c r="G60" s="158"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" ht="2.25" customHeight="1">
-      <c r="A61" s="43"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
+      <c r="C60" s="149"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
+      <c r="G60" s="126"/>
+      <c r="H60" s="178"/>
+      <c r="I60" s="178"/>
+      <c r="J60" s="178"/>
+      <c r="K60" s="178"/>
+    </row>
+    <row r="61" spans="1:11" ht="2.25" customHeight="1">
+      <c r="A61" s="42"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
       <c r="F61"/>
-      <c r="G61" s="172"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A62" s="43" t="s">
+      <c r="G61" s="140"/>
+      <c r="H61" s="178"/>
+      <c r="I61" s="178"/>
+      <c r="J61" s="178"/>
+      <c r="K61" s="178"/>
+    </row>
+    <row r="62" spans="1:11" ht="13.5" customHeight="1">
+      <c r="A62" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="136" t="s">
+      <c r="B62" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="136"/>
-      <c r="D62" s="82">
+      <c r="C62" s="154"/>
+      <c r="D62" s="81">
         <v>0.5</v>
       </c>
-      <c r="E62" s="44" t="s">
+      <c r="E62" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="F62" s="45">
+      <c r="F62" s="44">
         <f>+F54*D62</f>
         <v>0</v>
       </c>
-      <c r="G62" s="172"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-    </row>
-    <row r="63" spans="1:10" ht="3" customHeight="1">
-      <c r="A63" s="43"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="49"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="158"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-    </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1">
-      <c r="A64" s="43"/>
-      <c r="B64" s="135" t="s">
+      <c r="G62" s="140"/>
+      <c r="H62" s="178"/>
+      <c r="I62" s="178"/>
+      <c r="J62" s="178"/>
+      <c r="K62" s="178"/>
+    </row>
+    <row r="63" spans="1:11" ht="3" customHeight="1">
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="48"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="47"/>
+      <c r="G63" s="126"/>
+      <c r="H63" s="178"/>
+      <c r="I63" s="178"/>
+      <c r="J63" s="178"/>
+      <c r="K63" s="178"/>
+    </row>
+    <row r="64" spans="1:11" ht="15" customHeight="1">
+      <c r="A64" s="42"/>
+      <c r="B64" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="135"/>
-      <c r="D64" s="135"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="169"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-    </row>
-    <row r="65" spans="1:10" ht="8.4499999999999993" customHeight="1">
-      <c r="A65" s="43"/>
-      <c r="B65" s="43"/>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="71"/>
+      <c r="C64" s="153"/>
+      <c r="D64" s="153"/>
+      <c r="E64" s="153"/>
+      <c r="F64" s="47"/>
+      <c r="G64" s="137"/>
+      <c r="H64" s="178"/>
+      <c r="I64" s="178"/>
+      <c r="J64" s="178"/>
+      <c r="K64" s="178"/>
+    </row>
+    <row r="65" spans="1:11" ht="8.4499999999999993" customHeight="1">
+      <c r="A65" s="42"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="70"/>
+      <c r="D65" s="70"/>
+      <c r="E65" s="70"/>
       <c r="F65"/>
-      <c r="G65" s="158"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-    </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1">
-      <c r="A66" s="43" t="s">
+      <c r="G65" s="126"/>
+      <c r="H65" s="178"/>
+      <c r="I65" s="178"/>
+      <c r="J65" s="178"/>
+      <c r="K65" s="178"/>
+    </row>
+    <row r="66" spans="1:11" ht="15" customHeight="1">
+      <c r="A66" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="111" t="s">
+      <c r="B66" s="149" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="111"/>
-      <c r="D66" s="111"/>
-      <c r="E66" s="111"/>
-      <c r="F66" s="111"/>
-      <c r="G66" s="173"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-    </row>
-    <row r="67" spans="1:10" ht="8.4499999999999993" customHeight="1">
-      <c r="A67" s="43"/>
-      <c r="B67" s="43"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
+      <c r="C66" s="149"/>
+      <c r="D66" s="149"/>
+      <c r="E66" s="149"/>
+      <c r="F66" s="149"/>
+      <c r="G66" s="141"/>
+      <c r="H66" s="178"/>
+      <c r="I66" s="178"/>
+      <c r="J66" s="178"/>
+      <c r="K66" s="178"/>
+    </row>
+    <row r="67" spans="1:11" ht="8.4499999999999993" customHeight="1">
+      <c r="A67" s="42"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
       <c r="F67"/>
-      <c r="G67" s="158"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-    </row>
-    <row r="68" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A68" s="43" t="s">
+      <c r="G67" s="126"/>
+      <c r="H67" s="178"/>
+      <c r="I67" s="178"/>
+      <c r="J67" s="178"/>
+      <c r="K67" s="178"/>
+    </row>
+    <row r="68" spans="1:11" ht="70.5" customHeight="1">
+      <c r="A68" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="137" t="s">
+      <c r="B68" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="137"/>
-      <c r="D68" s="137"/>
-      <c r="E68" s="137"/>
-      <c r="F68" s="137"/>
-      <c r="G68" s="169"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="69" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A69" s="43"/>
-      <c r="B69" s="137" t="s">
+      <c r="C68" s="155"/>
+      <c r="D68" s="155"/>
+      <c r="E68" s="155"/>
+      <c r="F68" s="155"/>
+      <c r="G68" s="137"/>
+      <c r="H68" s="178"/>
+      <c r="I68" s="178"/>
+      <c r="J68" s="178"/>
+      <c r="K68" s="178"/>
+    </row>
+    <row r="69" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A69" s="42"/>
+      <c r="B69" s="155" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="137"/>
-      <c r="D69" s="137"/>
-      <c r="E69" s="137"/>
-      <c r="F69" s="137"/>
-      <c r="G69" s="158"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-    </row>
-    <row r="70" spans="1:10" ht="4.5" customHeight="1">
-      <c r="A70" s="43"/>
-      <c r="B70" s="43"/>
-      <c r="C70" s="49"/>
-      <c r="D70" s="49"/>
-      <c r="E70" s="49"/>
+      <c r="C69" s="155"/>
+      <c r="D69" s="155"/>
+      <c r="E69" s="155"/>
+      <c r="F69" s="155"/>
+      <c r="G69" s="126"/>
+      <c r="H69" s="178"/>
+      <c r="I69" s="178"/>
+      <c r="J69" s="178"/>
+      <c r="K69" s="178"/>
+    </row>
+    <row r="70" spans="1:11" ht="4.5" customHeight="1">
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
       <c r="F70"/>
-      <c r="G70" s="169"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" spans="1:10" ht="27" customHeight="1">
-      <c r="A71" s="43" t="s">
+      <c r="G70" s="137"/>
+      <c r="H70" s="178"/>
+      <c r="I70" s="178"/>
+      <c r="J70" s="178"/>
+      <c r="K70" s="178"/>
+    </row>
+    <row r="71" spans="1:11" ht="27" customHeight="1">
+      <c r="A71" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="111" t="s">
+      <c r="B71" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="111"/>
-      <c r="D71" s="111"/>
-      <c r="E71" s="111"/>
-      <c r="F71" s="111"/>
-      <c r="G71" s="158"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-    </row>
-    <row r="72" spans="1:10" ht="4.5" customHeight="1">
-      <c r="A72" s="43"/>
-      <c r="B72" s="43"/>
-      <c r="C72" s="71"/>
-      <c r="D72" s="71"/>
-      <c r="E72" s="71"/>
+      <c r="C71" s="149"/>
+      <c r="D71" s="149"/>
+      <c r="E71" s="149"/>
+      <c r="F71" s="149"/>
+      <c r="G71" s="126"/>
+      <c r="H71" s="178"/>
+      <c r="I71" s="178"/>
+      <c r="J71" s="178"/>
+      <c r="K71" s="178"/>
+    </row>
+    <row r="72" spans="1:11" ht="4.5" customHeight="1">
+      <c r="A72" s="42"/>
+      <c r="B72" s="42"/>
+      <c r="C72" s="70"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="70"/>
       <c r="F72"/>
-      <c r="G72" s="169"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-    </row>
-    <row r="73" spans="1:10" ht="39" customHeight="1">
-      <c r="A73" s="43" t="s">
+      <c r="G72" s="137"/>
+      <c r="H72" s="178"/>
+      <c r="I72" s="178"/>
+      <c r="J72" s="178"/>
+      <c r="K72" s="178"/>
+    </row>
+    <row r="73" spans="1:11" ht="39" customHeight="1">
+      <c r="A73" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="134" t="s">
+      <c r="B73" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="C73" s="134"/>
-      <c r="D73" s="134"/>
-      <c r="E73" s="134"/>
-      <c r="F73" s="134"/>
-      <c r="G73" s="158"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" ht="6" customHeight="1">
-      <c r="A74" s="43"/>
-      <c r="B74" s="43"/>
-      <c r="C74" s="72"/>
-      <c r="D74" s="72"/>
-      <c r="E74" s="72"/>
+      <c r="C73" s="152"/>
+      <c r="D73" s="152"/>
+      <c r="E73" s="152"/>
+      <c r="F73" s="152"/>
+      <c r="G73" s="126"/>
+      <c r="H73" s="178"/>
+      <c r="I73" s="178"/>
+      <c r="J73" s="178"/>
+      <c r="K73" s="178"/>
+    </row>
+    <row r="74" spans="1:11" ht="6" customHeight="1">
+      <c r="A74" s="42"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="71"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="71"/>
       <c r="F74"/>
-      <c r="G74" s="169"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-    </row>
-    <row r="75" spans="1:10" ht="30" customHeight="1">
-      <c r="A75" s="43" t="s">
+      <c r="G74" s="137"/>
+      <c r="H74" s="178"/>
+      <c r="I74" s="178"/>
+      <c r="J74" s="178"/>
+      <c r="K74" s="178"/>
+    </row>
+    <row r="75" spans="1:11" ht="30" customHeight="1">
+      <c r="A75" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B75" s="111" t="s">
+      <c r="B75" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="C75" s="111"/>
-      <c r="D75" s="111"/>
-      <c r="E75" s="111"/>
-      <c r="F75" s="111"/>
-      <c r="G75" s="158"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" ht="3" customHeight="1">
-      <c r="A76" s="43"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="71"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="71"/>
+      <c r="C75" s="149"/>
+      <c r="D75" s="149"/>
+      <c r="E75" s="149"/>
+      <c r="F75" s="149"/>
+      <c r="G75" s="126"/>
+      <c r="H75" s="178"/>
+      <c r="I75" s="178"/>
+      <c r="J75" s="178"/>
+      <c r="K75" s="178"/>
+    </row>
+    <row r="76" spans="1:11" ht="3" customHeight="1">
+      <c r="A76" s="42"/>
+      <c r="B76" s="42"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
       <c r="F76"/>
-      <c r="G76" s="169"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-    </row>
-    <row r="77" spans="1:10" ht="27" customHeight="1">
-      <c r="A77" s="43" t="s">
+      <c r="G76" s="137"/>
+      <c r="H76" s="178"/>
+      <c r="I76" s="178"/>
+      <c r="J76" s="178"/>
+      <c r="K76" s="178"/>
+    </row>
+    <row r="77" spans="1:11" ht="27" customHeight="1">
+      <c r="A77" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B77" s="111" t="s">
+      <c r="B77" s="149" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="111"/>
-      <c r="D77" s="111"/>
-      <c r="E77" s="111"/>
-      <c r="F77" s="111"/>
-      <c r="G77" s="158"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-    </row>
-    <row r="78" spans="1:10" ht="5.25" customHeight="1">
-      <c r="A78" s="43"/>
-      <c r="B78" s="43"/>
-      <c r="C78" s="71"/>
-      <c r="D78" s="71"/>
-      <c r="E78" s="71"/>
+      <c r="C77" s="149"/>
+      <c r="D77" s="149"/>
+      <c r="E77" s="149"/>
+      <c r="F77" s="149"/>
+      <c r="G77" s="126"/>
+      <c r="H77" s="178"/>
+      <c r="I77" s="178"/>
+      <c r="J77" s="178"/>
+      <c r="K77" s="178"/>
+    </row>
+    <row r="78" spans="1:11" ht="5.25" customHeight="1">
+      <c r="A78" s="42"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
       <c r="F78"/>
-      <c r="G78" s="169"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" spans="1:10" ht="40.5" customHeight="1">
-      <c r="A79" s="43" t="s">
+      <c r="G78" s="137"/>
+      <c r="H78" s="178"/>
+      <c r="I78" s="178"/>
+      <c r="J78" s="178"/>
+      <c r="K78" s="178"/>
+    </row>
+    <row r="79" spans="1:11" ht="40.5" customHeight="1">
+      <c r="A79" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B79" s="111" t="s">
+      <c r="B79" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="111"/>
-      <c r="D79" s="111"/>
-      <c r="E79" s="111"/>
-      <c r="F79" s="111"/>
-      <c r="G79" s="169"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-    </row>
-    <row r="80" spans="1:10" ht="3" customHeight="1">
-      <c r="A80" s="43"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
+      <c r="C79" s="149"/>
+      <c r="D79" s="149"/>
+      <c r="E79" s="149"/>
+      <c r="F79" s="149"/>
+      <c r="G79" s="137"/>
+      <c r="H79" s="178"/>
+      <c r="I79" s="178"/>
+      <c r="J79" s="178"/>
+      <c r="K79" s="178"/>
+    </row>
+    <row r="80" spans="1:11" ht="3" customHeight="1">
+      <c r="A80" s="42"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
       <c r="F80"/>
-      <c r="G80" s="158"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A81" s="43" t="s">
+      <c r="G80" s="126"/>
+      <c r="H80" s="178"/>
+      <c r="I80" s="178"/>
+      <c r="J80" s="178"/>
+      <c r="K80" s="178"/>
+    </row>
+    <row r="81" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A81" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="111" t="s">
+      <c r="B81" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="111"/>
-      <c r="D81" s="111"/>
-      <c r="E81" s="111"/>
-      <c r="F81" s="111"/>
-      <c r="G81" s="158"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="6" customHeight="1">
-      <c r="A82" s="43"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="71"/>
+      <c r="C81" s="149"/>
+      <c r="D81" s="149"/>
+      <c r="E81" s="149"/>
+      <c r="F81" s="149"/>
+      <c r="G81" s="126"/>
+      <c r="H81" s="178"/>
+      <c r="I81" s="178"/>
+      <c r="J81" s="178"/>
+      <c r="K81" s="178"/>
+    </row>
+    <row r="82" spans="1:11" ht="6" customHeight="1">
+      <c r="A82" s="42"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="70"/>
       <c r="F82"/>
-      <c r="G82" s="169"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A83" s="43" t="s">
+      <c r="G82" s="137"/>
+      <c r="H82" s="178"/>
+      <c r="I82" s="178"/>
+      <c r="J82" s="178"/>
+      <c r="K82" s="178"/>
+    </row>
+    <row r="83" spans="1:11" ht="42.75" customHeight="1">
+      <c r="A83" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="111" t="s">
+      <c r="B83" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="111"/>
-      <c r="D83" s="111"/>
-      <c r="E83" s="111"/>
-      <c r="F83" s="111"/>
-      <c r="G83" s="158"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A84" s="43"/>
-      <c r="B84" s="43"/>
-      <c r="C84" s="71"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
+      <c r="C83" s="149"/>
+      <c r="D83" s="149"/>
+      <c r="E83" s="149"/>
+      <c r="F83" s="149"/>
+      <c r="G83" s="126"/>
+      <c r="H83" s="178"/>
+      <c r="I83" s="178"/>
+      <c r="J83" s="178"/>
+      <c r="K83" s="178"/>
+    </row>
+    <row r="84" spans="1:11" ht="6.75" customHeight="1">
+      <c r="A84" s="42"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="70"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="70"/>
       <c r="F84"/>
-      <c r="G84" s="158"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="81" customHeight="1">
-      <c r="A85" s="43" t="s">
+      <c r="G84" s="126"/>
+      <c r="H84" s="178"/>
+      <c r="I84" s="178"/>
+      <c r="J84" s="178"/>
+      <c r="K84" s="178"/>
+    </row>
+    <row r="85" spans="1:11" ht="81" customHeight="1">
+      <c r="A85" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B85" s="111" t="s">
+      <c r="B85" s="149" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="111"/>
-      <c r="D85" s="111"/>
-      <c r="E85" s="111"/>
-      <c r="F85" s="111"/>
-      <c r="G85" s="158"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A86" s="43"/>
-      <c r="B86" s="71"/>
-      <c r="C86" s="71"/>
-      <c r="D86" s="71"/>
-      <c r="E86" s="71"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="88.5" customHeight="1">
-      <c r="A87" s="43" t="s">
+      <c r="C85" s="149"/>
+      <c r="D85" s="149"/>
+      <c r="E85" s="149"/>
+      <c r="F85" s="149"/>
+      <c r="G85" s="126"/>
+      <c r="H85" s="178"/>
+      <c r="I85" s="178"/>
+      <c r="J85" s="178"/>
+      <c r="K85" s="178"/>
+    </row>
+    <row r="86" spans="1:11" ht="6.75" customHeight="1">
+      <c r="A86" s="42"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="70"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="70"/>
+      <c r="F86" s="70"/>
+      <c r="G86" s="126"/>
+      <c r="H86" s="178"/>
+      <c r="I86" s="178"/>
+      <c r="J86" s="178"/>
+      <c r="K86" s="178"/>
+    </row>
+    <row r="87" spans="1:11" ht="88.5" customHeight="1">
+      <c r="A87" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="139" t="s">
+      <c r="B87" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="C87" s="139"/>
-      <c r="D87" s="139"/>
-      <c r="E87" s="139"/>
+      <c r="C87" s="150"/>
+      <c r="D87" s="150"/>
+      <c r="E87" s="150"/>
       <c r="F87"/>
-      <c r="G87" s="158"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="6" customHeight="1">
-      <c r="A88" s="43"/>
-      <c r="B88" s="139"/>
-      <c r="C88" s="139"/>
-      <c r="D88" s="139"/>
-      <c r="E88" s="139"/>
+      <c r="G87" s="126"/>
+      <c r="H87" s="178"/>
+      <c r="I87" s="178"/>
+      <c r="J87" s="178"/>
+      <c r="K87" s="178"/>
+    </row>
+    <row r="88" spans="1:11" ht="6" customHeight="1">
+      <c r="A88" s="42"/>
+      <c r="B88" s="150"/>
+      <c r="C88" s="150"/>
+      <c r="D88" s="150"/>
+      <c r="E88" s="150"/>
       <c r="F88"/>
-      <c r="G88" s="169"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="18" customHeight="1">
-      <c r="A89" s="43" t="s">
+      <c r="G88" s="137"/>
+      <c r="H88" s="178"/>
+      <c r="I88" s="178"/>
+      <c r="J88" s="178"/>
+      <c r="K88" s="178"/>
+    </row>
+    <row r="89" spans="1:11" ht="18" customHeight="1">
+      <c r="A89" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="111" t="s">
+      <c r="B89" s="149" t="s">
         <v>59</v>
       </c>
-      <c r="C89" s="111"/>
-      <c r="D89" s="111"/>
-      <c r="E89" s="111"/>
-      <c r="F89" s="111"/>
-      <c r="G89" s="169"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A90" s="43"/>
-      <c r="B90" s="43"/>
-      <c r="C90" s="71"/>
-      <c r="D90" s="71"/>
-      <c r="E90" s="71"/>
+      <c r="C89" s="149"/>
+      <c r="D89" s="149"/>
+      <c r="E89" s="149"/>
+      <c r="F89" s="149"/>
+      <c r="G89" s="137"/>
+      <c r="H89" s="178"/>
+      <c r="I89" s="178"/>
+      <c r="J89" s="178"/>
+      <c r="K89" s="178"/>
+    </row>
+    <row r="90" spans="1:11" ht="6.75" customHeight="1">
+      <c r="A90" s="42"/>
+      <c r="B90" s="42"/>
+      <c r="C90" s="70"/>
+      <c r="D90" s="70"/>
+      <c r="E90" s="70"/>
       <c r="F90"/>
-      <c r="G90" s="169"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="67.5" customHeight="1">
-      <c r="A91" s="43" t="s">
+      <c r="G90" s="137"/>
+      <c r="H90" s="178"/>
+      <c r="I90" s="178"/>
+      <c r="J90" s="178"/>
+      <c r="K90" s="178"/>
+    </row>
+    <row r="91" spans="1:11" ht="67.5" customHeight="1">
+      <c r="A91" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B91" s="111" t="s">
+      <c r="B91" s="149" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="111"/>
-      <c r="D91" s="111"/>
-      <c r="E91" s="111"/>
+      <c r="C91" s="149"/>
+      <c r="D91" s="149"/>
+      <c r="E91" s="149"/>
       <c r="F91"/>
-      <c r="G91" s="174"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="9.75" customHeight="1">
-      <c r="A92" s="43"/>
-      <c r="B92" s="79"/>
-      <c r="C92" s="79"/>
-      <c r="D92" s="79"/>
-      <c r="E92" s="79"/>
+      <c r="G91" s="142"/>
+      <c r="H91" s="178"/>
+      <c r="I91" s="178"/>
+      <c r="J91" s="178"/>
+      <c r="K91" s="178"/>
+    </row>
+    <row r="92" spans="1:11" ht="9.75" customHeight="1">
+      <c r="A92" s="42"/>
+      <c r="B92" s="78"/>
+      <c r="C92" s="78"/>
+      <c r="D92" s="78"/>
+      <c r="E92" s="78"/>
       <c r="F92"/>
-      <c r="G92" s="169"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="54.75" customHeight="1">
-      <c r="A93" s="43" t="s">
+      <c r="G92" s="137"/>
+      <c r="H92" s="178"/>
+      <c r="I92" s="178"/>
+      <c r="J92" s="178"/>
+      <c r="K92" s="178"/>
+    </row>
+    <row r="93" spans="1:11" ht="54.75" customHeight="1">
+      <c r="A93" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="111" t="s">
+      <c r="B93" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="111"/>
-      <c r="D93" s="111"/>
-      <c r="E93" s="111"/>
+      <c r="C93" s="149"/>
+      <c r="D93" s="149"/>
+      <c r="E93" s="149"/>
       <c r="F93"/>
-      <c r="G93" s="169"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" ht="7.5" customHeight="1">
-      <c r="A94" s="43"/>
-      <c r="B94" s="79"/>
-      <c r="C94" s="79"/>
-      <c r="D94" s="79"/>
-      <c r="E94" s="79"/>
+      <c r="G93" s="137"/>
+      <c r="H93" s="178"/>
+      <c r="I93" s="178"/>
+      <c r="J93" s="178"/>
+      <c r="K93" s="178"/>
+    </row>
+    <row r="94" spans="1:11" ht="7.5" customHeight="1">
+      <c r="A94" s="42"/>
+      <c r="B94" s="78"/>
+      <c r="C94" s="78"/>
+      <c r="D94" s="78"/>
+      <c r="E94" s="78"/>
       <c r="F94"/>
-      <c r="G94" s="169"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A95" s="43" t="s">
+      <c r="G94" s="137"/>
+      <c r="H94" s="178"/>
+      <c r="I94" s="178"/>
+      <c r="J94" s="178"/>
+      <c r="K94" s="178"/>
+    </row>
+    <row r="95" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A95" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B95" s="111" t="s">
+      <c r="B95" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="C95" s="111"/>
-      <c r="D95" s="111"/>
-      <c r="E95" s="111"/>
-      <c r="F95" s="111"/>
-      <c r="G95" s="169"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="10.5" customHeight="1">
-      <c r="A96" s="43"/>
-      <c r="B96" s="71"/>
-      <c r="C96" s="71"/>
-      <c r="D96" s="71"/>
-      <c r="E96" s="71"/>
-      <c r="F96" s="71"/>
-      <c r="G96" s="169"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-    </row>
-    <row r="97" spans="1:10" ht="132.75" customHeight="1">
-      <c r="A97" s="43" t="s">
+      <c r="C95" s="149"/>
+      <c r="D95" s="149"/>
+      <c r="E95" s="149"/>
+      <c r="F95" s="149"/>
+      <c r="G95" s="137"/>
+      <c r="H95" s="178"/>
+      <c r="I95" s="178"/>
+      <c r="J95" s="178"/>
+      <c r="K95" s="178"/>
+    </row>
+    <row r="96" spans="1:11" ht="10.5" customHeight="1">
+      <c r="A96" s="42"/>
+      <c r="B96" s="70"/>
+      <c r="C96" s="70"/>
+      <c r="D96" s="70"/>
+      <c r="E96" s="70"/>
+      <c r="F96" s="70"/>
+      <c r="G96" s="137"/>
+      <c r="H96" s="178"/>
+      <c r="I96" s="178"/>
+      <c r="J96" s="178"/>
+      <c r="K96" s="178"/>
+    </row>
+    <row r="97" spans="1:11" ht="132.75" customHeight="1">
+      <c r="A97" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="B97" s="111" t="s">
+      <c r="B97" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="C97" s="111"/>
-      <c r="D97" s="111"/>
-      <c r="E97" s="111"/>
-      <c r="F97" s="111"/>
-      <c r="G97" s="175"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-    </row>
-    <row r="98" spans="1:10" ht="12.75" customHeight="1">
+      <c r="C97" s="149"/>
+      <c r="D97" s="149"/>
+      <c r="E97" s="149"/>
+      <c r="F97" s="149"/>
+      <c r="G97" s="143"/>
+      <c r="H97" s="178"/>
+      <c r="I97" s="178"/>
+      <c r="J97" s="178"/>
+      <c r="K97" s="178"/>
+    </row>
+    <row r="98" spans="1:11" ht="12.75" customHeight="1">
       <c r="A98" s="4"/>
-      <c r="B98" s="43"/>
-      <c r="C98" s="71"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
+      <c r="B98" s="42"/>
+      <c r="C98" s="70"/>
+      <c r="D98" s="70"/>
+      <c r="E98" s="70"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="176"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-    </row>
-    <row r="99" spans="1:10" ht="41.25" customHeight="1">
+      <c r="G98" s="144"/>
+      <c r="H98" s="178"/>
+      <c r="I98" s="178"/>
+      <c r="J98" s="178"/>
+      <c r="K98" s="178"/>
+    </row>
+    <row r="99" spans="1:11" ht="41.25" customHeight="1">
       <c r="A99" s="4"/>
-      <c r="B99" s="140" t="s">
+      <c r="B99" s="151" t="s">
         <v>33</v>
       </c>
-      <c r="C99" s="140"/>
-      <c r="D99" s="140"/>
-      <c r="E99" s="140"/>
-      <c r="F99" s="71"/>
-      <c r="G99" s="175"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" ht="9" customHeight="1">
+      <c r="C99" s="151"/>
+      <c r="D99" s="151"/>
+      <c r="E99" s="151"/>
+      <c r="F99" s="70"/>
+      <c r="G99" s="143"/>
+      <c r="H99" s="178"/>
+      <c r="I99" s="178"/>
+      <c r="J99" s="178"/>
+      <c r="K99" s="178"/>
+    </row>
+    <row r="100" spans="1:11" ht="9" customHeight="1">
       <c r="A100" s="4"/>
-      <c r="B100" s="71"/>
-      <c r="C100" s="71"/>
-      <c r="D100" s="71"/>
-      <c r="E100" s="71"/>
-      <c r="F100" s="71"/>
-      <c r="G100" s="175"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-    </row>
-    <row r="101" spans="1:10" ht="39.75" customHeight="1">
+      <c r="B100" s="70"/>
+      <c r="C100" s="70"/>
+      <c r="D100" s="70"/>
+      <c r="E100" s="70"/>
+      <c r="F100" s="70"/>
+      <c r="G100" s="143"/>
+      <c r="H100" s="178"/>
+      <c r="I100" s="178"/>
+      <c r="J100" s="178"/>
+      <c r="K100" s="178"/>
+    </row>
+    <row r="101" spans="1:11" ht="39.75" customHeight="1">
       <c r="A101" s="4"/>
-      <c r="B101" s="140" t="s">
+      <c r="B101" s="151" t="s">
         <v>46</v>
       </c>
-      <c r="C101" s="140"/>
-      <c r="D101" s="140"/>
-      <c r="E101" s="140"/>
-      <c r="F101" s="71"/>
-      <c r="G101" s="177"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-    </row>
-    <row r="102" spans="1:10">
+      <c r="C101" s="151"/>
+      <c r="D101" s="151"/>
+      <c r="E101" s="151"/>
+      <c r="F101" s="70"/>
+      <c r="G101" s="145"/>
+      <c r="H101" s="178"/>
+      <c r="I101" s="178"/>
+      <c r="J101" s="178"/>
+      <c r="K101" s="178"/>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102" s="4"/>
-      <c r="B102" s="71"/>
-      <c r="C102" s="71"/>
-      <c r="D102" s="71"/>
-      <c r="E102" s="71"/>
-      <c r="F102" s="71"/>
-      <c r="G102" s="175"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-    </row>
-    <row r="103" spans="1:10" ht="29.25" customHeight="1">
+      <c r="B102" s="70"/>
+      <c r="C102" s="70"/>
+      <c r="D102" s="70"/>
+      <c r="E102" s="70"/>
+      <c r="F102" s="70"/>
+      <c r="G102" s="143"/>
+      <c r="H102" s="178"/>
+      <c r="I102" s="178"/>
+      <c r="J102" s="178"/>
+      <c r="K102" s="178"/>
+    </row>
+    <row r="103" spans="1:11" ht="29.25" customHeight="1">
       <c r="A103" s="4"/>
-      <c r="B103" s="140" t="s">
+      <c r="B103" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="C103" s="140"/>
-      <c r="D103" s="140"/>
-      <c r="E103" s="140"/>
-      <c r="F103" s="71"/>
-      <c r="G103" s="175"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-    </row>
-    <row r="104" spans="1:10" ht="6.75" customHeight="1">
+      <c r="C103" s="151"/>
+      <c r="D103" s="151"/>
+      <c r="E103" s="151"/>
+      <c r="F103" s="70"/>
+      <c r="G103" s="143"/>
+      <c r="H103" s="178"/>
+      <c r="I103" s="178"/>
+      <c r="J103" s="178"/>
+      <c r="K103" s="178"/>
+    </row>
+    <row r="104" spans="1:11" ht="6.75" customHeight="1">
       <c r="A104" s="4"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="158"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-    </row>
-    <row r="105" spans="1:10" ht="15.75" customHeight="1">
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="126"/>
+      <c r="H104" s="178"/>
+      <c r="I104" s="178"/>
+      <c r="J104" s="178"/>
+      <c r="K104" s="178"/>
+    </row>
+    <row r="105" spans="1:11" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
-      <c r="B105" s="140" t="s">
+      <c r="B105" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="140"/>
-      <c r="D105" s="140"/>
-      <c r="E105" s="140"/>
-      <c r="F105" s="140"/>
-      <c r="G105" s="175"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-    </row>
-    <row r="106" spans="1:10">
+      <c r="C105" s="151"/>
+      <c r="D105" s="151"/>
+      <c r="E105" s="151"/>
+      <c r="F105" s="151"/>
+      <c r="G105" s="143"/>
+      <c r="H105" s="178"/>
+      <c r="I105" s="178"/>
+      <c r="J105" s="178"/>
+      <c r="K105" s="178"/>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106" s="4"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25"/>
-      <c r="G106" s="158"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-    </row>
-    <row r="107" spans="1:10">
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="126"/>
+      <c r="H106" s="178"/>
+      <c r="I106" s="178"/>
+      <c r="J106" s="178"/>
+      <c r="K106" s="178"/>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107" s="4"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="158"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-    </row>
-    <row r="108" spans="1:10" ht="31.5">
-      <c r="B108" s="73" t="s">
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="126"/>
+      <c r="H107" s="178"/>
+      <c r="I107" s="178"/>
+      <c r="J107" s="178"/>
+      <c r="K107" s="178"/>
+    </row>
+    <row r="108" spans="1:11" ht="31.5">
+      <c r="B108" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C108" s="73"/>
-      <c r="D108" s="73"/>
-      <c r="E108" s="73"/>
-      <c r="F108" s="73"/>
-      <c r="G108" s="158"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-    </row>
-    <row r="109" spans="1:10">
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="25"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="25"/>
-      <c r="G109" s="158"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
-    </row>
-    <row r="110" spans="1:10" ht="12.75" customHeight="1">
-      <c r="B110" s="138" t="s">
+      <c r="C108" s="72"/>
+      <c r="D108" s="72"/>
+      <c r="E108" s="72"/>
+      <c r="F108" s="72"/>
+      <c r="G108" s="126"/>
+      <c r="H108" s="178"/>
+      <c r="I108" s="178"/>
+      <c r="J108" s="178"/>
+      <c r="K108" s="178"/>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="126"/>
+      <c r="H109" s="178"/>
+      <c r="I109" s="178"/>
+      <c r="J109" s="178"/>
+      <c r="K109" s="178"/>
+    </row>
+    <row r="110" spans="1:11" ht="12.75" customHeight="1">
+      <c r="B110" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="138"/>
-      <c r="D110" s="138"/>
-      <c r="E110" s="138"/>
-      <c r="F110" s="138"/>
-      <c r="G110" s="158"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-    </row>
-    <row r="111" spans="1:10" ht="2.25" customHeight="1">
+      <c r="C110" s="148"/>
+      <c r="D110" s="148"/>
+      <c r="E110" s="148"/>
+      <c r="F110" s="148"/>
+      <c r="G110" s="126"/>
+      <c r="H110" s="178"/>
+      <c r="I110" s="178"/>
+      <c r="J110" s="178"/>
+      <c r="K110" s="178"/>
+    </row>
+    <row r="111" spans="1:11" ht="2.25" customHeight="1">
       <c r="B111" s="6"/>
       <c r="C111"/>
       <c r="D111"/>
       <c r="E111"/>
       <c r="F111"/>
-      <c r="G111" s="158"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
-      <c r="J111" s="1"/>
-    </row>
-    <row r="112" spans="1:10" ht="17.25" customHeight="1">
-      <c r="B112" s="138" t="s">
+      <c r="G111" s="126"/>
+      <c r="H111" s="178"/>
+      <c r="I111" s="178"/>
+      <c r="J111" s="178"/>
+      <c r="K111" s="178"/>
+    </row>
+    <row r="112" spans="1:11" ht="17.25" customHeight="1">
+      <c r="B112" s="148" t="s">
         <v>52</v>
       </c>
-      <c r="C112" s="138"/>
-      <c r="D112" s="138"/>
-      <c r="E112" s="138"/>
-      <c r="F112" s="138"/>
-      <c r="G112" s="158"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
-    </row>
-    <row r="113" spans="1:23" ht="9.9499999999999993" customHeight="1">
+      <c r="C112" s="148"/>
+      <c r="D112" s="148"/>
+      <c r="E112" s="148"/>
+      <c r="F112" s="148"/>
+      <c r="G112" s="126"/>
+      <c r="H112" s="178"/>
+      <c r="I112" s="178"/>
+      <c r="J112" s="178"/>
+      <c r="K112" s="178"/>
+    </row>
+    <row r="113" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="B113" s="6"/>
       <c r="C113"/>
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113"/>
-      <c r="G113" s="158"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" spans="1:23" ht="18.75" customHeight="1">
+      <c r="G113" s="126"/>
+      <c r="H113" s="178"/>
+      <c r="I113" s="178"/>
+      <c r="J113" s="178"/>
+      <c r="K113" s="178"/>
+    </row>
+    <row r="114" spans="1:11" ht="18.75" customHeight="1">
       <c r="B114" s="6"/>
       <c r="C114"/>
       <c r="D114"/>
       <c r="E114"/>
       <c r="F114"/>
-      <c r="G114" s="158"/>
+      <c r="G114" s="126"/>
       <c r="H114" s="178"/>
       <c r="I114" s="178"/>
       <c r="J114" s="178"/>
       <c r="K114" s="178"/>
-      <c r="L114" s="178"/>
-      <c r="M114" s="178"/>
-      <c r="N114" s="178"/>
-      <c r="O114" s="178"/>
-      <c r="P114" s="178"/>
-      <c r="Q114" s="178"/>
-      <c r="R114" s="178"/>
-      <c r="S114" s="178"/>
-      <c r="T114" s="178"/>
-      <c r="U114" s="178"/>
-      <c r="V114" s="178"/>
-      <c r="W114" s="178"/>
-    </row>
-    <row r="115" spans="1:23" ht="15" customHeight="1">
-      <c r="B115" s="50" t="s">
+    </row>
+    <row r="115" spans="1:11" ht="15" customHeight="1">
+      <c r="B115" s="49" t="s">
         <v>34</v>
       </c>
       <c r="C115"/>
       <c r="D115"/>
       <c r="E115"/>
       <c r="F115"/>
-      <c r="G115" s="158"/>
+      <c r="G115" s="126"/>
       <c r="H115" s="178"/>
       <c r="I115" s="178"/>
       <c r="J115" s="178"/>
       <c r="K115" s="178"/>
-      <c r="L115" s="178"/>
-      <c r="M115" s="178"/>
-      <c r="N115" s="178"/>
-      <c r="O115" s="178"/>
-      <c r="P115" s="178"/>
-      <c r="Q115" s="178"/>
-      <c r="R115" s="178"/>
-      <c r="S115" s="178"/>
-      <c r="T115" s="178"/>
-      <c r="U115" s="178"/>
-      <c r="V115" s="178"/>
-      <c r="W115" s="178"/>
-    </row>
-    <row r="116" spans="1:23" ht="0.75" customHeight="1">
+    </row>
+    <row r="116" spans="1:11" ht="0.75" customHeight="1">
       <c r="B116" s="6"/>
       <c r="C116"/>
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116"/>
-      <c r="G116" s="158"/>
+      <c r="G116" s="126"/>
       <c r="H116" s="178"/>
       <c r="I116" s="178"/>
       <c r="J116" s="178"/>
       <c r="K116" s="178"/>
-      <c r="L116" s="178"/>
-      <c r="M116" s="178"/>
-      <c r="N116" s="178"/>
-      <c r="O116" s="178"/>
-      <c r="P116" s="178"/>
-      <c r="Q116" s="178"/>
-      <c r="R116" s="178"/>
-      <c r="S116" s="178"/>
-      <c r="T116" s="178"/>
-      <c r="U116" s="178"/>
-      <c r="V116" s="178"/>
-      <c r="W116" s="178"/>
-    </row>
-    <row r="117" spans="1:23" ht="16.5" customHeight="1">
+    </row>
+    <row r="117" spans="1:11" ht="16.5" customHeight="1">
       <c r="B117" s="6"/>
       <c r="C117"/>
       <c r="D117"/>
@@ -4023,1215 +4150,1166 @@
         <v>73</v>
       </c>
       <c r="F117" s="3"/>
-      <c r="G117" s="158"/>
+      <c r="G117" s="126"/>
       <c r="H117" s="178"/>
       <c r="I117" s="178"/>
       <c r="J117" s="178"/>
       <c r="K117" s="178"/>
-      <c r="L117" s="178"/>
-      <c r="M117" s="178"/>
-      <c r="N117" s="178"/>
-      <c r="O117" s="178"/>
-      <c r="P117" s="178"/>
-      <c r="Q117" s="178"/>
-      <c r="R117" s="178"/>
-      <c r="S117" s="178"/>
-      <c r="T117" s="178"/>
-      <c r="U117" s="178"/>
-      <c r="V117" s="178"/>
-      <c r="W117" s="178"/>
-    </row>
-    <row r="118" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    </row>
+    <row r="118" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="35"/>
-      <c r="G118" s="179"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="34"/>
+      <c r="G118" s="126"/>
       <c r="H118" s="178"/>
       <c r="I118" s="178"/>
       <c r="J118" s="178"/>
       <c r="K118" s="178"/>
-      <c r="L118" s="178"/>
-      <c r="M118" s="178"/>
-      <c r="N118" s="178"/>
-      <c r="O118" s="178"/>
-      <c r="P118" s="178"/>
-      <c r="Q118" s="178"/>
-      <c r="R118" s="178"/>
-      <c r="S118" s="178"/>
-      <c r="T118" s="178"/>
-      <c r="U118" s="178"/>
-      <c r="V118" s="178"/>
-      <c r="W118" s="178"/>
-    </row>
-    <row r="119" spans="1:23" ht="9.9499999999999993" customHeight="1">
-      <c r="A119" s="180"/>
-      <c r="B119" s="181"/>
-      <c r="C119" s="180"/>
-      <c r="D119" s="180"/>
-      <c r="E119" s="180"/>
-      <c r="F119" s="180"/>
-      <c r="G119" s="179"/>
+    </row>
+    <row r="119" spans="1:11" ht="9.9499999999999993" customHeight="1">
+      <c r="A119" s="146"/>
+      <c r="B119" s="147"/>
+      <c r="C119" s="146"/>
+      <c r="D119" s="146"/>
+      <c r="E119" s="146"/>
+      <c r="F119" s="146"/>
+      <c r="G119" s="126"/>
       <c r="H119" s="178"/>
       <c r="I119" s="178"/>
       <c r="J119" s="178"/>
       <c r="K119" s="178"/>
-      <c r="L119" s="178"/>
-      <c r="M119" s="178"/>
-      <c r="N119" s="178"/>
-      <c r="O119" s="178"/>
-      <c r="P119" s="178"/>
-      <c r="Q119" s="178"/>
-      <c r="R119" s="178"/>
-      <c r="S119" s="178"/>
-      <c r="T119" s="178"/>
-      <c r="U119" s="178"/>
-      <c r="V119" s="178"/>
-      <c r="W119" s="178"/>
-    </row>
-    <row r="120" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    </row>
+    <row r="120" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A120" s="1"/>
-      <c r="B120" s="20"/>
-      <c r="G120" s="178"/>
-      <c r="H120" s="178"/>
-      <c r="I120" s="178"/>
-      <c r="J120" s="178"/>
-      <c r="K120" s="178"/>
-      <c r="L120" s="178"/>
-      <c r="M120" s="178"/>
-      <c r="N120" s="178"/>
-      <c r="O120" s="178"/>
-      <c r="P120" s="178"/>
-      <c r="Q120" s="178"/>
-      <c r="R120" s="178"/>
-      <c r="S120" s="178"/>
-      <c r="T120" s="178"/>
-      <c r="U120" s="178"/>
-      <c r="V120" s="178"/>
-      <c r="W120" s="178"/>
-    </row>
-    <row r="121" spans="1:23" ht="9.9499999999999993" customHeight="1">
+      <c r="B120" s="19"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="20"/>
+      <c r="B121" s="19"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="122" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="20"/>
+      <c r="B122" s="19"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="123" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="20"/>
+      <c r="B123" s="19"/>
       <c r="G123" s="1"/>
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="124" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A124" s="1"/>
-      <c r="B124" s="20"/>
+      <c r="B124" s="19"/>
       <c r="G124" s="1"/>
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="125" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="20"/>
+      <c r="B125" s="19"/>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="126" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="20"/>
+      <c r="B126" s="19"/>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="127" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="20"/>
+      <c r="B127" s="19"/>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:23" ht="9.9499999999999993" customHeight="1">
+    <row r="128" spans="1:11" ht="9.9499999999999993" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="20"/>
+      <c r="B128" s="19"/>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
     </row>
     <row r="129" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
-      <c r="B129" s="20"/>
+      <c r="B129" s="19"/>
     </row>
     <row r="130" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
-      <c r="B130" s="20"/>
+      <c r="B130" s="19"/>
     </row>
     <row r="131" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
-      <c r="B131" s="20"/>
+      <c r="B131" s="19"/>
     </row>
     <row r="132" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
-      <c r="B132" s="20"/>
+      <c r="B132" s="19"/>
     </row>
     <row r="133" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
-      <c r="B133" s="20"/>
+      <c r="B133" s="19"/>
     </row>
     <row r="134" spans="2:2" s="1" customFormat="1" ht="126" customHeight="1">
-      <c r="B134" s="20"/>
+      <c r="B134" s="19"/>
     </row>
     <row r="135" spans="2:2" s="1" customFormat="1" ht="96" customHeight="1">
-      <c r="B135" s="20"/>
+      <c r="B135" s="19"/>
     </row>
     <row r="136" spans="2:2" s="1" customFormat="1" ht="93" customHeight="1">
-      <c r="B136" s="20"/>
+      <c r="B136" s="19"/>
     </row>
     <row r="137" spans="2:2" s="1" customFormat="1" ht="42" customHeight="1">
-      <c r="B137" s="20"/>
+      <c r="B137" s="19"/>
     </row>
     <row r="138" spans="2:2" s="1" customFormat="1" ht="42.75" customHeight="1">
-      <c r="B138" s="20"/>
+      <c r="B138" s="19"/>
     </row>
     <row r="139" spans="2:2" s="1" customFormat="1" ht="103.5" customHeight="1">
-      <c r="B139" s="20"/>
+      <c r="B139" s="19"/>
     </row>
     <row r="140" spans="2:2" s="1" customFormat="1">
-      <c r="B140" s="20"/>
+      <c r="B140" s="19"/>
     </row>
     <row r="141" spans="2:2" s="1" customFormat="1">
-      <c r="B141" s="20"/>
+      <c r="B141" s="19"/>
     </row>
     <row r="142" spans="2:2" s="1" customFormat="1">
-      <c r="B142" s="20"/>
+      <c r="B142" s="19"/>
     </row>
     <row r="143" spans="2:2" s="1" customFormat="1">
-      <c r="B143" s="20"/>
+      <c r="B143" s="19"/>
     </row>
     <row r="144" spans="2:2" s="1" customFormat="1">
-      <c r="B144" s="20"/>
+      <c r="B144" s="19"/>
     </row>
     <row r="145" spans="2:2" s="1" customFormat="1">
-      <c r="B145" s="20"/>
+      <c r="B145" s="19"/>
     </row>
     <row r="146" spans="2:2" s="1" customFormat="1">
-      <c r="B146" s="20"/>
+      <c r="B146" s="19"/>
     </row>
     <row r="147" spans="2:2" s="1" customFormat="1">
-      <c r="B147" s="20"/>
+      <c r="B147" s="19"/>
     </row>
     <row r="148" spans="2:2" s="1" customFormat="1">
-      <c r="B148" s="20"/>
+      <c r="B148" s="19"/>
     </row>
     <row r="149" spans="2:2" s="1" customFormat="1">
-      <c r="B149" s="20"/>
+      <c r="B149" s="19"/>
     </row>
     <row r="150" spans="2:2" s="1" customFormat="1">
-      <c r="B150" s="20"/>
+      <c r="B150" s="19"/>
     </row>
     <row r="151" spans="2:2" s="1" customFormat="1">
-      <c r="B151" s="20"/>
+      <c r="B151" s="19"/>
     </row>
     <row r="152" spans="2:2" s="1" customFormat="1">
-      <c r="B152" s="20"/>
+      <c r="B152" s="19"/>
     </row>
     <row r="153" spans="2:2" s="1" customFormat="1">
-      <c r="B153" s="20"/>
+      <c r="B153" s="19"/>
     </row>
     <row r="154" spans="2:2" s="1" customFormat="1">
-      <c r="B154" s="20"/>
+      <c r="B154" s="19"/>
     </row>
     <row r="155" spans="2:2" s="1" customFormat="1">
-      <c r="B155" s="20"/>
+      <c r="B155" s="19"/>
     </row>
     <row r="156" spans="2:2" s="1" customFormat="1">
-      <c r="B156" s="20"/>
+      <c r="B156" s="19"/>
     </row>
     <row r="157" spans="2:2" s="1" customFormat="1">
-      <c r="B157" s="20"/>
+      <c r="B157" s="19"/>
     </row>
     <row r="158" spans="2:2" s="1" customFormat="1">
-      <c r="B158" s="20"/>
+      <c r="B158" s="19"/>
     </row>
     <row r="159" spans="2:2" s="1" customFormat="1">
-      <c r="B159" s="20"/>
+      <c r="B159" s="19"/>
     </row>
     <row r="160" spans="2:2" s="1" customFormat="1">
-      <c r="B160" s="20"/>
+      <c r="B160" s="19"/>
     </row>
     <row r="161" spans="2:2" s="1" customFormat="1">
-      <c r="B161" s="20"/>
+      <c r="B161" s="19"/>
     </row>
     <row r="162" spans="2:2" s="1" customFormat="1">
-      <c r="B162" s="20"/>
+      <c r="B162" s="19"/>
     </row>
     <row r="163" spans="2:2" s="1" customFormat="1">
-      <c r="B163" s="20"/>
+      <c r="B163" s="19"/>
     </row>
     <row r="164" spans="2:2" s="1" customFormat="1">
-      <c r="B164" s="20"/>
+      <c r="B164" s="19"/>
     </row>
     <row r="165" spans="2:2" s="1" customFormat="1">
-      <c r="B165" s="20"/>
+      <c r="B165" s="19"/>
     </row>
     <row r="166" spans="2:2" s="1" customFormat="1">
-      <c r="B166" s="20"/>
+      <c r="B166" s="19"/>
     </row>
     <row r="167" spans="2:2" s="1" customFormat="1">
-      <c r="B167" s="20"/>
+      <c r="B167" s="19"/>
     </row>
     <row r="168" spans="2:2" s="1" customFormat="1">
-      <c r="B168" s="20"/>
+      <c r="B168" s="19"/>
     </row>
     <row r="169" spans="2:2" s="1" customFormat="1">
-      <c r="B169" s="20"/>
+      <c r="B169" s="19"/>
     </row>
     <row r="170" spans="2:2" s="1" customFormat="1">
-      <c r="B170" s="20"/>
+      <c r="B170" s="19"/>
     </row>
     <row r="171" spans="2:2" s="1" customFormat="1">
-      <c r="B171" s="20"/>
+      <c r="B171" s="19"/>
     </row>
     <row r="172" spans="2:2" s="1" customFormat="1">
-      <c r="B172" s="20"/>
+      <c r="B172" s="19"/>
     </row>
     <row r="173" spans="2:2" s="1" customFormat="1">
-      <c r="B173" s="20"/>
+      <c r="B173" s="19"/>
     </row>
     <row r="174" spans="2:2" s="1" customFormat="1">
-      <c r="B174" s="20"/>
+      <c r="B174" s="19"/>
     </row>
     <row r="175" spans="2:2" s="1" customFormat="1">
-      <c r="B175" s="20"/>
+      <c r="B175" s="19"/>
     </row>
     <row r="176" spans="2:2" s="1" customFormat="1">
-      <c r="B176" s="20"/>
+      <c r="B176" s="19"/>
     </row>
     <row r="177" spans="2:2" s="1" customFormat="1">
-      <c r="B177" s="20"/>
+      <c r="B177" s="19"/>
     </row>
     <row r="178" spans="2:2" s="1" customFormat="1">
-      <c r="B178" s="20"/>
+      <c r="B178" s="19"/>
     </row>
     <row r="179" spans="2:2" s="1" customFormat="1">
-      <c r="B179" s="20"/>
+      <c r="B179" s="19"/>
     </row>
     <row r="180" spans="2:2" s="1" customFormat="1">
-      <c r="B180" s="20"/>
+      <c r="B180" s="19"/>
     </row>
     <row r="181" spans="2:2" s="1" customFormat="1">
-      <c r="B181" s="20"/>
+      <c r="B181" s="19"/>
     </row>
     <row r="182" spans="2:2" s="1" customFormat="1">
-      <c r="B182" s="20"/>
+      <c r="B182" s="19"/>
     </row>
     <row r="183" spans="2:2" s="1" customFormat="1">
-      <c r="B183" s="20"/>
+      <c r="B183" s="19"/>
     </row>
     <row r="184" spans="2:2" s="1" customFormat="1">
-      <c r="B184" s="20"/>
+      <c r="B184" s="19"/>
     </row>
     <row r="185" spans="2:2" s="1" customFormat="1">
-      <c r="B185" s="20"/>
+      <c r="B185" s="19"/>
     </row>
     <row r="186" spans="2:2" s="1" customFormat="1">
-      <c r="B186" s="20"/>
+      <c r="B186" s="19"/>
     </row>
     <row r="187" spans="2:2" s="1" customFormat="1">
-      <c r="B187" s="20"/>
+      <c r="B187" s="19"/>
     </row>
     <row r="188" spans="2:2" s="1" customFormat="1">
-      <c r="B188" s="20"/>
+      <c r="B188" s="19"/>
     </row>
     <row r="189" spans="2:2" s="1" customFormat="1">
-      <c r="B189" s="20"/>
+      <c r="B189" s="19"/>
     </row>
     <row r="190" spans="2:2" s="1" customFormat="1">
-      <c r="B190" s="20"/>
+      <c r="B190" s="19"/>
     </row>
     <row r="191" spans="2:2" s="1" customFormat="1">
-      <c r="B191" s="20"/>
+      <c r="B191" s="19"/>
     </row>
     <row r="192" spans="2:2" s="1" customFormat="1">
-      <c r="B192" s="20"/>
+      <c r="B192" s="19"/>
     </row>
     <row r="193" spans="2:2" s="1" customFormat="1">
-      <c r="B193" s="20"/>
+      <c r="B193" s="19"/>
     </row>
     <row r="194" spans="2:2" s="1" customFormat="1">
-      <c r="B194" s="20"/>
+      <c r="B194" s="19"/>
     </row>
     <row r="195" spans="2:2" s="1" customFormat="1">
-      <c r="B195" s="20"/>
+      <c r="B195" s="19"/>
     </row>
     <row r="196" spans="2:2" s="1" customFormat="1">
-      <c r="B196" s="20"/>
+      <c r="B196" s="19"/>
     </row>
     <row r="197" spans="2:2" s="1" customFormat="1">
-      <c r="B197" s="20"/>
+      <c r="B197" s="19"/>
     </row>
     <row r="198" spans="2:2" s="1" customFormat="1">
-      <c r="B198" s="20"/>
+      <c r="B198" s="19"/>
     </row>
     <row r="199" spans="2:2" s="1" customFormat="1">
-      <c r="B199" s="20"/>
+      <c r="B199" s="19"/>
     </row>
     <row r="200" spans="2:2" s="1" customFormat="1">
-      <c r="B200" s="20"/>
+      <c r="B200" s="19"/>
     </row>
     <row r="201" spans="2:2" s="1" customFormat="1">
-      <c r="B201" s="20"/>
+      <c r="B201" s="19"/>
     </row>
     <row r="202" spans="2:2" s="1" customFormat="1">
-      <c r="B202" s="20"/>
+      <c r="B202" s="19"/>
     </row>
     <row r="203" spans="2:2" s="1" customFormat="1">
-      <c r="B203" s="20"/>
+      <c r="B203" s="19"/>
     </row>
     <row r="204" spans="2:2" s="1" customFormat="1">
-      <c r="B204" s="20"/>
+      <c r="B204" s="19"/>
     </row>
     <row r="205" spans="2:2" s="1" customFormat="1">
-      <c r="B205" s="20"/>
+      <c r="B205" s="19"/>
     </row>
     <row r="206" spans="2:2" s="1" customFormat="1">
-      <c r="B206" s="20"/>
+      <c r="B206" s="19"/>
     </row>
     <row r="207" spans="2:2" s="1" customFormat="1">
-      <c r="B207" s="20"/>
+      <c r="B207" s="19"/>
     </row>
     <row r="208" spans="2:2" s="1" customFormat="1">
-      <c r="B208" s="20"/>
+      <c r="B208" s="19"/>
     </row>
     <row r="209" spans="2:2" s="1" customFormat="1">
-      <c r="B209" s="20"/>
+      <c r="B209" s="19"/>
     </row>
     <row r="210" spans="2:2" s="1" customFormat="1">
-      <c r="B210" s="20"/>
+      <c r="B210" s="19"/>
     </row>
     <row r="211" spans="2:2" s="1" customFormat="1">
-      <c r="B211" s="20"/>
+      <c r="B211" s="19"/>
     </row>
     <row r="212" spans="2:2" s="1" customFormat="1">
-      <c r="B212" s="20"/>
+      <c r="B212" s="19"/>
     </row>
     <row r="213" spans="2:2" s="1" customFormat="1">
-      <c r="B213" s="20"/>
+      <c r="B213" s="19"/>
     </row>
     <row r="214" spans="2:2" s="1" customFormat="1">
-      <c r="B214" s="20"/>
+      <c r="B214" s="19"/>
     </row>
     <row r="215" spans="2:2" s="1" customFormat="1">
-      <c r="B215" s="20"/>
+      <c r="B215" s="19"/>
     </row>
     <row r="216" spans="2:2" s="1" customFormat="1">
-      <c r="B216" s="20"/>
+      <c r="B216" s="19"/>
     </row>
     <row r="217" spans="2:2" s="1" customFormat="1">
-      <c r="B217" s="20"/>
+      <c r="B217" s="19"/>
     </row>
     <row r="218" spans="2:2" s="1" customFormat="1">
-      <c r="B218" s="20"/>
+      <c r="B218" s="19"/>
     </row>
     <row r="219" spans="2:2" s="1" customFormat="1">
-      <c r="B219" s="20"/>
+      <c r="B219" s="19"/>
     </row>
     <row r="220" spans="2:2" s="1" customFormat="1">
-      <c r="B220" s="20"/>
+      <c r="B220" s="19"/>
     </row>
     <row r="221" spans="2:2" s="1" customFormat="1">
-      <c r="B221" s="20"/>
+      <c r="B221" s="19"/>
     </row>
     <row r="222" spans="2:2" s="1" customFormat="1">
-      <c r="B222" s="20"/>
+      <c r="B222" s="19"/>
     </row>
     <row r="223" spans="2:2" s="1" customFormat="1">
-      <c r="B223" s="20"/>
+      <c r="B223" s="19"/>
     </row>
     <row r="224" spans="2:2" s="1" customFormat="1">
-      <c r="B224" s="20"/>
+      <c r="B224" s="19"/>
     </row>
     <row r="225" spans="2:2" s="1" customFormat="1">
-      <c r="B225" s="20"/>
+      <c r="B225" s="19"/>
     </row>
     <row r="226" spans="2:2" s="1" customFormat="1">
-      <c r="B226" s="20"/>
+      <c r="B226" s="19"/>
     </row>
     <row r="227" spans="2:2" s="1" customFormat="1">
-      <c r="B227" s="20"/>
+      <c r="B227" s="19"/>
     </row>
     <row r="228" spans="2:2" s="1" customFormat="1">
-      <c r="B228" s="20"/>
+      <c r="B228" s="19"/>
     </row>
     <row r="229" spans="2:2" s="1" customFormat="1">
-      <c r="B229" s="20"/>
+      <c r="B229" s="19"/>
     </row>
     <row r="230" spans="2:2" s="1" customFormat="1">
-      <c r="B230" s="20"/>
+      <c r="B230" s="19"/>
     </row>
     <row r="231" spans="2:2" s="1" customFormat="1">
-      <c r="B231" s="20"/>
+      <c r="B231" s="19"/>
     </row>
     <row r="232" spans="2:2" s="1" customFormat="1">
-      <c r="B232" s="20"/>
+      <c r="B232" s="19"/>
     </row>
     <row r="233" spans="2:2" s="1" customFormat="1">
-      <c r="B233" s="20"/>
+      <c r="B233" s="19"/>
     </row>
     <row r="234" spans="2:2" s="1" customFormat="1">
-      <c r="B234" s="20"/>
+      <c r="B234" s="19"/>
     </row>
     <row r="235" spans="2:2" s="1" customFormat="1">
-      <c r="B235" s="20"/>
+      <c r="B235" s="19"/>
     </row>
     <row r="236" spans="2:2" s="1" customFormat="1">
-      <c r="B236" s="20"/>
+      <c r="B236" s="19"/>
     </row>
     <row r="237" spans="2:2" s="1" customFormat="1">
-      <c r="B237" s="20"/>
+      <c r="B237" s="19"/>
     </row>
     <row r="238" spans="2:2" s="1" customFormat="1">
-      <c r="B238" s="20"/>
+      <c r="B238" s="19"/>
     </row>
     <row r="239" spans="2:2" s="1" customFormat="1">
-      <c r="B239" s="20"/>
+      <c r="B239" s="19"/>
     </row>
     <row r="240" spans="2:2" s="1" customFormat="1">
-      <c r="B240" s="20"/>
+      <c r="B240" s="19"/>
     </row>
     <row r="241" spans="2:2" s="1" customFormat="1">
-      <c r="B241" s="20"/>
+      <c r="B241" s="19"/>
     </row>
     <row r="242" spans="2:2" s="1" customFormat="1">
-      <c r="B242" s="20"/>
+      <c r="B242" s="19"/>
     </row>
     <row r="243" spans="2:2" s="1" customFormat="1">
-      <c r="B243" s="20"/>
+      <c r="B243" s="19"/>
     </row>
     <row r="244" spans="2:2" s="1" customFormat="1">
-      <c r="B244" s="20"/>
+      <c r="B244" s="19"/>
     </row>
     <row r="245" spans="2:2" s="1" customFormat="1">
-      <c r="B245" s="20"/>
+      <c r="B245" s="19"/>
     </row>
     <row r="246" spans="2:2" s="1" customFormat="1">
-      <c r="B246" s="20"/>
+      <c r="B246" s="19"/>
     </row>
     <row r="247" spans="2:2" s="1" customFormat="1">
-      <c r="B247" s="20"/>
+      <c r="B247" s="19"/>
     </row>
     <row r="248" spans="2:2" s="1" customFormat="1">
-      <c r="B248" s="20"/>
+      <c r="B248" s="19"/>
     </row>
     <row r="249" spans="2:2" s="1" customFormat="1">
-      <c r="B249" s="20"/>
+      <c r="B249" s="19"/>
     </row>
     <row r="250" spans="2:2" s="1" customFormat="1">
-      <c r="B250" s="20"/>
+      <c r="B250" s="19"/>
     </row>
     <row r="251" spans="2:2" s="1" customFormat="1">
-      <c r="B251" s="20"/>
+      <c r="B251" s="19"/>
     </row>
     <row r="252" spans="2:2" s="1" customFormat="1">
-      <c r="B252" s="20"/>
+      <c r="B252" s="19"/>
     </row>
     <row r="253" spans="2:2" s="1" customFormat="1">
-      <c r="B253" s="20"/>
+      <c r="B253" s="19"/>
     </row>
     <row r="254" spans="2:2" s="1" customFormat="1">
-      <c r="B254" s="20"/>
+      <c r="B254" s="19"/>
     </row>
     <row r="255" spans="2:2" s="1" customFormat="1">
-      <c r="B255" s="20"/>
+      <c r="B255" s="19"/>
     </row>
     <row r="256" spans="2:2" s="1" customFormat="1">
-      <c r="B256" s="20"/>
+      <c r="B256" s="19"/>
     </row>
     <row r="257" spans="2:2" s="1" customFormat="1">
-      <c r="B257" s="20"/>
+      <c r="B257" s="19"/>
     </row>
     <row r="258" spans="2:2" s="1" customFormat="1">
-      <c r="B258" s="20"/>
+      <c r="B258" s="19"/>
     </row>
     <row r="259" spans="2:2" s="1" customFormat="1">
-      <c r="B259" s="20"/>
+      <c r="B259" s="19"/>
     </row>
     <row r="260" spans="2:2" s="1" customFormat="1">
-      <c r="B260" s="20"/>
+      <c r="B260" s="19"/>
     </row>
     <row r="261" spans="2:2" s="1" customFormat="1">
-      <c r="B261" s="20"/>
+      <c r="B261" s="19"/>
     </row>
     <row r="262" spans="2:2" s="1" customFormat="1">
-      <c r="B262" s="20"/>
+      <c r="B262" s="19"/>
     </row>
     <row r="263" spans="2:2" s="1" customFormat="1">
-      <c r="B263" s="20"/>
+      <c r="B263" s="19"/>
     </row>
     <row r="264" spans="2:2" s="1" customFormat="1">
-      <c r="B264" s="20"/>
+      <c r="B264" s="19"/>
     </row>
     <row r="265" spans="2:2" s="1" customFormat="1">
-      <c r="B265" s="20"/>
+      <c r="B265" s="19"/>
     </row>
     <row r="266" spans="2:2" s="1" customFormat="1">
-      <c r="B266" s="20"/>
+      <c r="B266" s="19"/>
     </row>
     <row r="267" spans="2:2" s="1" customFormat="1">
-      <c r="B267" s="20"/>
+      <c r="B267" s="19"/>
     </row>
     <row r="268" spans="2:2" s="1" customFormat="1">
-      <c r="B268" s="20"/>
+      <c r="B268" s="19"/>
     </row>
     <row r="269" spans="2:2" s="1" customFormat="1">
-      <c r="B269" s="20"/>
+      <c r="B269" s="19"/>
     </row>
     <row r="270" spans="2:2" s="1" customFormat="1">
-      <c r="B270" s="20"/>
+      <c r="B270" s="19"/>
     </row>
     <row r="271" spans="2:2" s="1" customFormat="1">
-      <c r="B271" s="20"/>
+      <c r="B271" s="19"/>
     </row>
     <row r="272" spans="2:2" s="1" customFormat="1">
-      <c r="B272" s="20"/>
+      <c r="B272" s="19"/>
     </row>
     <row r="273" spans="2:2" s="1" customFormat="1">
-      <c r="B273" s="20"/>
+      <c r="B273" s="19"/>
     </row>
     <row r="274" spans="2:2" s="1" customFormat="1">
-      <c r="B274" s="20"/>
+      <c r="B274" s="19"/>
     </row>
     <row r="275" spans="2:2" s="1" customFormat="1">
-      <c r="B275" s="20"/>
+      <c r="B275" s="19"/>
     </row>
     <row r="276" spans="2:2" s="1" customFormat="1">
-      <c r="B276" s="20"/>
+      <c r="B276" s="19"/>
     </row>
     <row r="277" spans="2:2" s="1" customFormat="1">
-      <c r="B277" s="20"/>
+      <c r="B277" s="19"/>
     </row>
     <row r="278" spans="2:2" s="1" customFormat="1">
-      <c r="B278" s="20"/>
+      <c r="B278" s="19"/>
     </row>
     <row r="279" spans="2:2" s="1" customFormat="1">
-      <c r="B279" s="20"/>
+      <c r="B279" s="19"/>
     </row>
     <row r="280" spans="2:2" s="1" customFormat="1">
-      <c r="B280" s="20"/>
+      <c r="B280" s="19"/>
     </row>
     <row r="281" spans="2:2" s="1" customFormat="1">
-      <c r="B281" s="20"/>
+      <c r="B281" s="19"/>
     </row>
     <row r="282" spans="2:2" s="1" customFormat="1">
-      <c r="B282" s="20"/>
+      <c r="B282" s="19"/>
     </row>
     <row r="283" spans="2:2" s="1" customFormat="1">
-      <c r="B283" s="20"/>
+      <c r="B283" s="19"/>
     </row>
     <row r="284" spans="2:2" s="1" customFormat="1">
-      <c r="B284" s="20"/>
+      <c r="B284" s="19"/>
     </row>
     <row r="285" spans="2:2" s="1" customFormat="1">
-      <c r="B285" s="20"/>
+      <c r="B285" s="19"/>
     </row>
     <row r="286" spans="2:2" s="1" customFormat="1">
-      <c r="B286" s="20"/>
+      <c r="B286" s="19"/>
     </row>
     <row r="287" spans="2:2" s="1" customFormat="1">
-      <c r="B287" s="20"/>
+      <c r="B287" s="19"/>
     </row>
     <row r="288" spans="2:2" s="1" customFormat="1">
-      <c r="B288" s="20"/>
+      <c r="B288" s="19"/>
     </row>
     <row r="289" spans="2:2" s="1" customFormat="1">
-      <c r="B289" s="20"/>
+      <c r="B289" s="19"/>
     </row>
     <row r="290" spans="2:2" s="1" customFormat="1">
-      <c r="B290" s="20"/>
+      <c r="B290" s="19"/>
     </row>
     <row r="291" spans="2:2" s="1" customFormat="1">
-      <c r="B291" s="20"/>
+      <c r="B291" s="19"/>
     </row>
     <row r="292" spans="2:2" s="1" customFormat="1">
-      <c r="B292" s="20"/>
+      <c r="B292" s="19"/>
     </row>
     <row r="293" spans="2:2" s="1" customFormat="1">
-      <c r="B293" s="20"/>
+      <c r="B293" s="19"/>
     </row>
     <row r="294" spans="2:2" s="1" customFormat="1">
-      <c r="B294" s="20"/>
+      <c r="B294" s="19"/>
     </row>
     <row r="295" spans="2:2" s="1" customFormat="1">
-      <c r="B295" s="20"/>
+      <c r="B295" s="19"/>
     </row>
     <row r="296" spans="2:2" s="1" customFormat="1">
-      <c r="B296" s="20"/>
+      <c r="B296" s="19"/>
     </row>
     <row r="297" spans="2:2" s="1" customFormat="1">
-      <c r="B297" s="20"/>
+      <c r="B297" s="19"/>
     </row>
     <row r="298" spans="2:2" s="1" customFormat="1">
-      <c r="B298" s="20"/>
+      <c r="B298" s="19"/>
     </row>
     <row r="299" spans="2:2" s="1" customFormat="1">
-      <c r="B299" s="20"/>
+      <c r="B299" s="19"/>
     </row>
     <row r="300" spans="2:2" s="1" customFormat="1">
-      <c r="B300" s="20"/>
+      <c r="B300" s="19"/>
     </row>
     <row r="301" spans="2:2" s="1" customFormat="1">
-      <c r="B301" s="20"/>
+      <c r="B301" s="19"/>
     </row>
     <row r="302" spans="2:2" s="1" customFormat="1">
-      <c r="B302" s="20"/>
+      <c r="B302" s="19"/>
     </row>
     <row r="303" spans="2:2" s="1" customFormat="1">
-      <c r="B303" s="20"/>
+      <c r="B303" s="19"/>
     </row>
     <row r="304" spans="2:2" s="1" customFormat="1">
-      <c r="B304" s="20"/>
+      <c r="B304" s="19"/>
     </row>
     <row r="305" spans="2:2" s="1" customFormat="1">
-      <c r="B305" s="20"/>
+      <c r="B305" s="19"/>
     </row>
     <row r="306" spans="2:2" s="1" customFormat="1">
-      <c r="B306" s="20"/>
+      <c r="B306" s="19"/>
     </row>
     <row r="307" spans="2:2" s="1" customFormat="1">
-      <c r="B307" s="20"/>
+      <c r="B307" s="19"/>
     </row>
     <row r="308" spans="2:2" s="1" customFormat="1">
-      <c r="B308" s="20"/>
+      <c r="B308" s="19"/>
     </row>
     <row r="309" spans="2:2" s="1" customFormat="1">
-      <c r="B309" s="20"/>
+      <c r="B309" s="19"/>
     </row>
     <row r="310" spans="2:2" s="1" customFormat="1">
-      <c r="B310" s="20"/>
+      <c r="B310" s="19"/>
     </row>
     <row r="311" spans="2:2" s="1" customFormat="1">
-      <c r="B311" s="20"/>
+      <c r="B311" s="19"/>
     </row>
     <row r="312" spans="2:2" s="1" customFormat="1">
-      <c r="B312" s="20"/>
+      <c r="B312" s="19"/>
     </row>
     <row r="313" spans="2:2" s="1" customFormat="1">
-      <c r="B313" s="20"/>
+      <c r="B313" s="19"/>
     </row>
     <row r="314" spans="2:2" s="1" customFormat="1">
-      <c r="B314" s="20"/>
+      <c r="B314" s="19"/>
     </row>
     <row r="315" spans="2:2" s="1" customFormat="1">
-      <c r="B315" s="20"/>
+      <c r="B315" s="19"/>
     </row>
     <row r="316" spans="2:2" s="1" customFormat="1">
-      <c r="B316" s="20"/>
+      <c r="B316" s="19"/>
     </row>
     <row r="317" spans="2:2" s="1" customFormat="1">
-      <c r="B317" s="20"/>
+      <c r="B317" s="19"/>
     </row>
     <row r="318" spans="2:2" s="1" customFormat="1">
-      <c r="B318" s="20"/>
+      <c r="B318" s="19"/>
     </row>
     <row r="319" spans="2:2" s="1" customFormat="1">
-      <c r="B319" s="20"/>
+      <c r="B319" s="19"/>
     </row>
     <row r="320" spans="2:2" s="1" customFormat="1">
-      <c r="B320" s="20"/>
+      <c r="B320" s="19"/>
     </row>
     <row r="321" spans="2:2" s="1" customFormat="1">
-      <c r="B321" s="20"/>
+      <c r="B321" s="19"/>
     </row>
     <row r="322" spans="2:2" s="1" customFormat="1">
-      <c r="B322" s="20"/>
+      <c r="B322" s="19"/>
     </row>
     <row r="323" spans="2:2" s="1" customFormat="1">
-      <c r="B323" s="20"/>
+      <c r="B323" s="19"/>
     </row>
     <row r="324" spans="2:2" s="1" customFormat="1">
-      <c r="B324" s="20"/>
+      <c r="B324" s="19"/>
     </row>
     <row r="325" spans="2:2" s="1" customFormat="1">
-      <c r="B325" s="20"/>
+      <c r="B325" s="19"/>
     </row>
     <row r="326" spans="2:2" s="1" customFormat="1">
-      <c r="B326" s="20"/>
+      <c r="B326" s="19"/>
     </row>
     <row r="327" spans="2:2" s="1" customFormat="1">
-      <c r="B327" s="20"/>
+      <c r="B327" s="19"/>
     </row>
     <row r="328" spans="2:2" s="1" customFormat="1">
-      <c r="B328" s="20"/>
+      <c r="B328" s="19"/>
     </row>
     <row r="329" spans="2:2" s="1" customFormat="1">
-      <c r="B329" s="20"/>
+      <c r="B329" s="19"/>
     </row>
     <row r="330" spans="2:2" s="1" customFormat="1">
-      <c r="B330" s="20"/>
+      <c r="B330" s="19"/>
     </row>
     <row r="331" spans="2:2" s="1" customFormat="1">
-      <c r="B331" s="20"/>
+      <c r="B331" s="19"/>
     </row>
     <row r="332" spans="2:2" s="1" customFormat="1">
-      <c r="B332" s="20"/>
+      <c r="B332" s="19"/>
     </row>
     <row r="333" spans="2:2" s="1" customFormat="1">
-      <c r="B333" s="20"/>
+      <c r="B333" s="19"/>
     </row>
     <row r="334" spans="2:2" s="1" customFormat="1">
-      <c r="B334" s="20"/>
+      <c r="B334" s="19"/>
     </row>
     <row r="335" spans="2:2" s="1" customFormat="1">
-      <c r="B335" s="20"/>
+      <c r="B335" s="19"/>
     </row>
     <row r="336" spans="2:2" s="1" customFormat="1">
-      <c r="B336" s="20"/>
+      <c r="B336" s="19"/>
     </row>
     <row r="337" spans="2:2" s="1" customFormat="1">
-      <c r="B337" s="20"/>
+      <c r="B337" s="19"/>
     </row>
     <row r="338" spans="2:2" s="1" customFormat="1">
-      <c r="B338" s="20"/>
+      <c r="B338" s="19"/>
     </row>
     <row r="339" spans="2:2" s="1" customFormat="1">
-      <c r="B339" s="20"/>
+      <c r="B339" s="19"/>
     </row>
     <row r="340" spans="2:2" s="1" customFormat="1">
-      <c r="B340" s="20"/>
+      <c r="B340" s="19"/>
     </row>
     <row r="341" spans="2:2" s="1" customFormat="1">
-      <c r="B341" s="20"/>
+      <c r="B341" s="19"/>
     </row>
     <row r="342" spans="2:2" s="1" customFormat="1">
-      <c r="B342" s="20"/>
+      <c r="B342" s="19"/>
     </row>
     <row r="343" spans="2:2" s="1" customFormat="1">
-      <c r="B343" s="20"/>
+      <c r="B343" s="19"/>
     </row>
     <row r="344" spans="2:2" s="1" customFormat="1">
-      <c r="B344" s="20"/>
+      <c r="B344" s="19"/>
     </row>
     <row r="345" spans="2:2" s="1" customFormat="1">
-      <c r="B345" s="20"/>
+      <c r="B345" s="19"/>
     </row>
     <row r="346" spans="2:2" s="1" customFormat="1">
-      <c r="B346" s="20"/>
+      <c r="B346" s="19"/>
     </row>
     <row r="347" spans="2:2" s="1" customFormat="1">
-      <c r="B347" s="20"/>
+      <c r="B347" s="19"/>
     </row>
     <row r="348" spans="2:2" s="1" customFormat="1">
-      <c r="B348" s="20"/>
+      <c r="B348" s="19"/>
     </row>
     <row r="349" spans="2:2" s="1" customFormat="1">
-      <c r="B349" s="20"/>
+      <c r="B349" s="19"/>
     </row>
     <row r="350" spans="2:2" s="1" customFormat="1">
-      <c r="B350" s="20"/>
+      <c r="B350" s="19"/>
     </row>
     <row r="351" spans="2:2" s="1" customFormat="1">
-      <c r="B351" s="20"/>
+      <c r="B351" s="19"/>
     </row>
     <row r="352" spans="2:2" s="1" customFormat="1">
-      <c r="B352" s="20"/>
+      <c r="B352" s="19"/>
     </row>
     <row r="353" spans="2:2" s="1" customFormat="1">
-      <c r="B353" s="20"/>
+      <c r="B353" s="19"/>
     </row>
     <row r="354" spans="2:2" s="1" customFormat="1">
-      <c r="B354" s="20"/>
+      <c r="B354" s="19"/>
     </row>
     <row r="355" spans="2:2" s="1" customFormat="1">
-      <c r="B355" s="20"/>
+      <c r="B355" s="19"/>
     </row>
     <row r="356" spans="2:2" s="1" customFormat="1">
-      <c r="B356" s="20"/>
+      <c r="B356" s="19"/>
     </row>
     <row r="357" spans="2:2" s="1" customFormat="1">
-      <c r="B357" s="20"/>
+      <c r="B357" s="19"/>
     </row>
     <row r="358" spans="2:2" s="1" customFormat="1">
-      <c r="B358" s="20"/>
+      <c r="B358" s="19"/>
     </row>
     <row r="359" spans="2:2" s="1" customFormat="1">
-      <c r="B359" s="20"/>
+      <c r="B359" s="19"/>
     </row>
     <row r="360" spans="2:2" s="1" customFormat="1">
-      <c r="B360" s="20"/>
+      <c r="B360" s="19"/>
     </row>
     <row r="361" spans="2:2" s="1" customFormat="1">
-      <c r="B361" s="20"/>
+      <c r="B361" s="19"/>
     </row>
     <row r="362" spans="2:2" s="1" customFormat="1">
-      <c r="B362" s="20"/>
+      <c r="B362" s="19"/>
     </row>
     <row r="363" spans="2:2" s="1" customFormat="1">
-      <c r="B363" s="20"/>
+      <c r="B363" s="19"/>
     </row>
     <row r="364" spans="2:2" s="1" customFormat="1">
-      <c r="B364" s="20"/>
+      <c r="B364" s="19"/>
     </row>
     <row r="365" spans="2:2" s="1" customFormat="1">
-      <c r="B365" s="20"/>
+      <c r="B365" s="19"/>
     </row>
     <row r="366" spans="2:2" s="1" customFormat="1">
-      <c r="B366" s="20"/>
+      <c r="B366" s="19"/>
     </row>
     <row r="367" spans="2:2" s="1" customFormat="1">
-      <c r="B367" s="20"/>
+      <c r="B367" s="19"/>
     </row>
     <row r="368" spans="2:2" s="1" customFormat="1">
-      <c r="B368" s="20"/>
+      <c r="B368" s="19"/>
     </row>
     <row r="369" spans="2:2" s="1" customFormat="1">
-      <c r="B369" s="20"/>
+      <c r="B369" s="19"/>
     </row>
     <row r="370" spans="2:2" s="1" customFormat="1">
-      <c r="B370" s="20"/>
+      <c r="B370" s="19"/>
     </row>
     <row r="371" spans="2:2" s="1" customFormat="1">
-      <c r="B371" s="20"/>
+      <c r="B371" s="19"/>
     </row>
     <row r="372" spans="2:2" s="1" customFormat="1">
-      <c r="B372" s="20"/>
+      <c r="B372" s="19"/>
     </row>
     <row r="373" spans="2:2" s="1" customFormat="1">
-      <c r="B373" s="20"/>
+      <c r="B373" s="19"/>
     </row>
     <row r="374" spans="2:2" s="1" customFormat="1">
-      <c r="B374" s="20"/>
+      <c r="B374" s="19"/>
     </row>
     <row r="375" spans="2:2" s="1" customFormat="1">
-      <c r="B375" s="20"/>
+      <c r="B375" s="19"/>
     </row>
     <row r="376" spans="2:2" s="1" customFormat="1">
-      <c r="B376" s="20"/>
+      <c r="B376" s="19"/>
     </row>
     <row r="377" spans="2:2" s="1" customFormat="1">
-      <c r="B377" s="20"/>
+      <c r="B377" s="19"/>
     </row>
     <row r="378" spans="2:2" s="1" customFormat="1">
-      <c r="B378" s="20"/>
+      <c r="B378" s="19"/>
     </row>
     <row r="379" spans="2:2" s="1" customFormat="1">
-      <c r="B379" s="20"/>
+      <c r="B379" s="19"/>
     </row>
     <row r="380" spans="2:2" s="1" customFormat="1">
-      <c r="B380" s="20"/>
+      <c r="B380" s="19"/>
     </row>
     <row r="381" spans="2:2" s="1" customFormat="1">
-      <c r="B381" s="20"/>
+      <c r="B381" s="19"/>
     </row>
     <row r="382" spans="2:2" s="1" customFormat="1">
-      <c r="B382" s="20"/>
+      <c r="B382" s="19"/>
     </row>
     <row r="383" spans="2:2" s="1" customFormat="1">
-      <c r="B383" s="20"/>
+      <c r="B383" s="19"/>
     </row>
     <row r="384" spans="2:2" s="1" customFormat="1">
-      <c r="B384" s="20"/>
+      <c r="B384" s="19"/>
     </row>
     <row r="385" spans="2:2" s="1" customFormat="1">
-      <c r="B385" s="20"/>
+      <c r="B385" s="19"/>
     </row>
     <row r="386" spans="2:2" s="1" customFormat="1">
-      <c r="B386" s="20"/>
+      <c r="B386" s="19"/>
     </row>
     <row r="387" spans="2:2" s="1" customFormat="1">
-      <c r="B387" s="20"/>
+      <c r="B387" s="19"/>
     </row>
     <row r="388" spans="2:2" s="1" customFormat="1">
-      <c r="B388" s="20"/>
+      <c r="B388" s="19"/>
     </row>
     <row r="389" spans="2:2" s="1" customFormat="1">
-      <c r="B389" s="20"/>
+      <c r="B389" s="19"/>
     </row>
     <row r="390" spans="2:2" s="1" customFormat="1">
-      <c r="B390" s="20"/>
+      <c r="B390" s="19"/>
     </row>
     <row r="391" spans="2:2" s="1" customFormat="1">
-      <c r="B391" s="20"/>
+      <c r="B391" s="19"/>
     </row>
     <row r="392" spans="2:2" s="1" customFormat="1">
-      <c r="B392" s="20"/>
+      <c r="B392" s="19"/>
     </row>
     <row r="393" spans="2:2" s="1" customFormat="1">
-      <c r="B393" s="20"/>
+      <c r="B393" s="19"/>
     </row>
     <row r="394" spans="2:2" s="1" customFormat="1">
-      <c r="B394" s="20"/>
+      <c r="B394" s="19"/>
     </row>
     <row r="395" spans="2:2" s="1" customFormat="1">
-      <c r="B395" s="20"/>
+      <c r="B395" s="19"/>
     </row>
     <row r="396" spans="2:2" s="1" customFormat="1">
-      <c r="B396" s="20"/>
+      <c r="B396" s="19"/>
     </row>
     <row r="397" spans="2:2" s="1" customFormat="1">
-      <c r="B397" s="20"/>
+      <c r="B397" s="19"/>
     </row>
     <row r="398" spans="2:2" s="1" customFormat="1">
-      <c r="B398" s="20"/>
+      <c r="B398" s="19"/>
     </row>
     <row r="399" spans="2:2" s="1" customFormat="1">
-      <c r="B399" s="20"/>
+      <c r="B399" s="19"/>
     </row>
     <row r="400" spans="2:2" s="1" customFormat="1">
-      <c r="B400" s="20"/>
+      <c r="B400" s="19"/>
     </row>
     <row r="401" spans="2:2" s="1" customFormat="1">
-      <c r="B401" s="20"/>
+      <c r="B401" s="19"/>
     </row>
     <row r="402" spans="2:2" s="1" customFormat="1">
-      <c r="B402" s="20"/>
+      <c r="B402" s="19"/>
     </row>
     <row r="403" spans="2:2" s="1" customFormat="1">
-      <c r="B403" s="20"/>
+      <c r="B403" s="19"/>
     </row>
     <row r="404" spans="2:2" s="1" customFormat="1">
-      <c r="B404" s="20"/>
+      <c r="B404" s="19"/>
     </row>
     <row r="405" spans="2:2" s="1" customFormat="1">
-      <c r="B405" s="20"/>
+      <c r="B405" s="19"/>
     </row>
     <row r="406" spans="2:2" s="1" customFormat="1">
-      <c r="B406" s="20"/>
+      <c r="B406" s="19"/>
     </row>
     <row r="407" spans="2:2" s="1" customFormat="1">
-      <c r="B407" s="20"/>
+      <c r="B407" s="19"/>
     </row>
     <row r="408" spans="2:2" s="1" customFormat="1">
-      <c r="B408" s="20"/>
+      <c r="B408" s="19"/>
     </row>
     <row r="409" spans="2:2" s="1" customFormat="1">
-      <c r="B409" s="20"/>
+      <c r="B409" s="19"/>
     </row>
     <row r="410" spans="2:2" s="1" customFormat="1">
-      <c r="B410" s="20"/>
+      <c r="B410" s="19"/>
     </row>
     <row r="411" spans="2:2" s="1" customFormat="1">
-      <c r="B411" s="20"/>
+      <c r="B411" s="19"/>
     </row>
     <row r="412" spans="2:2" s="1" customFormat="1">
-      <c r="B412" s="20"/>
+      <c r="B412" s="19"/>
     </row>
     <row r="413" spans="2:2" s="1" customFormat="1">
-      <c r="B413" s="20"/>
+      <c r="B413" s="19"/>
     </row>
     <row r="414" spans="2:2" s="1" customFormat="1">
-      <c r="B414" s="20"/>
+      <c r="B414" s="19"/>
     </row>
     <row r="415" spans="2:2" s="1" customFormat="1">
-      <c r="B415" s="20"/>
+      <c r="B415" s="19"/>
     </row>
     <row r="416" spans="2:2" s="1" customFormat="1">
-      <c r="B416" s="20"/>
+      <c r="B416" s="19"/>
     </row>
     <row r="417" spans="2:2" s="1" customFormat="1">
-      <c r="B417" s="20"/>
+      <c r="B417" s="19"/>
     </row>
     <row r="418" spans="2:2" s="1" customFormat="1">
-      <c r="B418" s="20"/>
+      <c r="B418" s="19"/>
     </row>
     <row r="419" spans="2:2" s="1" customFormat="1">
-      <c r="B419" s="20"/>
+      <c r="B419" s="19"/>
     </row>
     <row r="420" spans="2:2" s="1" customFormat="1">
-      <c r="B420" s="20"/>
+      <c r="B420" s="19"/>
     </row>
     <row r="421" spans="2:2" s="1" customFormat="1">
-      <c r="B421" s="20"/>
+      <c r="B421" s="19"/>
     </row>
     <row r="422" spans="2:2" s="1" customFormat="1">
-      <c r="B422" s="20"/>
+      <c r="B422" s="19"/>
     </row>
     <row r="423" spans="2:2" s="1" customFormat="1">
-      <c r="B423" s="20"/>
+      <c r="B423" s="19"/>
     </row>
     <row r="424" spans="2:2" s="1" customFormat="1">
-      <c r="B424" s="20"/>
+      <c r="B424" s="19"/>
     </row>
     <row r="425" spans="2:2" s="1" customFormat="1">
-      <c r="B425" s="20"/>
+      <c r="B425" s="19"/>
     </row>
     <row r="426" spans="2:2" s="1" customFormat="1">
-      <c r="B426" s="20"/>
+      <c r="B426" s="19"/>
     </row>
     <row r="427" spans="2:2" s="1" customFormat="1">
-      <c r="B427" s="20"/>
+      <c r="B427" s="19"/>
     </row>
     <row r="428" spans="2:2" s="1" customFormat="1">
-      <c r="B428" s="20"/>
+      <c r="B428" s="19"/>
     </row>
     <row r="429" spans="2:2" s="1" customFormat="1">
-      <c r="B429" s="20"/>
+      <c r="B429" s="19"/>
     </row>
     <row r="430" spans="2:2" s="1" customFormat="1">
-      <c r="B430" s="20"/>
+      <c r="B430" s="19"/>
     </row>
     <row r="431" spans="2:2" s="1" customFormat="1">
-      <c r="B431" s="20"/>
+      <c r="B431" s="19"/>
     </row>
     <row r="432" spans="2:2" s="1" customFormat="1">
-      <c r="B432" s="20"/>
+      <c r="B432" s="19"/>
     </row>
     <row r="433" spans="2:2" s="1" customFormat="1">
-      <c r="B433" s="20"/>
+      <c r="B433" s="19"/>
     </row>
     <row r="434" spans="2:2" s="1" customFormat="1">
-      <c r="B434" s="20"/>
+      <c r="B434" s="19"/>
     </row>
     <row r="435" spans="2:2" s="1" customFormat="1">
-      <c r="B435" s="20"/>
+      <c r="B435" s="19"/>
     </row>
     <row r="436" spans="2:2" s="1" customFormat="1">
-      <c r="B436" s="20"/>
+      <c r="B436" s="19"/>
     </row>
     <row r="437" spans="2:2" s="1" customFormat="1">
-      <c r="B437" s="20"/>
+      <c r="B437" s="19"/>
     </row>
     <row r="438" spans="2:2" s="1" customFormat="1">
-      <c r="B438" s="20"/>
+      <c r="B438" s="19"/>
     </row>
     <row r="439" spans="2:2" s="1" customFormat="1">
-      <c r="B439" s="20"/>
+      <c r="B439" s="19"/>
     </row>
     <row r="440" spans="2:2" s="1" customFormat="1">
-      <c r="B440" s="20"/>
+      <c r="B440" s="19"/>
     </row>
     <row r="441" spans="2:2" s="1" customFormat="1">
-      <c r="B441" s="20"/>
+      <c r="B441" s="19"/>
     </row>
     <row r="442" spans="2:2" s="1" customFormat="1">
-      <c r="B442" s="20"/>
+      <c r="B442" s="19"/>
     </row>
     <row r="443" spans="2:2" s="1" customFormat="1">
-      <c r="B443" s="20"/>
+      <c r="B443" s="19"/>
     </row>
     <row r="444" spans="2:2" s="1" customFormat="1">
-      <c r="B444" s="20"/>
+      <c r="B444" s="19"/>
     </row>
     <row r="445" spans="2:2" s="1" customFormat="1">
-      <c r="B445" s="20"/>
+      <c r="B445" s="19"/>
     </row>
     <row r="446" spans="2:2" s="1" customFormat="1">
-      <c r="B446" s="20"/>
+      <c r="B446" s="19"/>
     </row>
     <row r="447" spans="2:2" s="1" customFormat="1">
-      <c r="B447" s="20"/>
+      <c r="B447" s="19"/>
     </row>
     <row r="448" spans="2:2" s="1" customFormat="1">
-      <c r="B448" s="20"/>
+      <c r="B448" s="19"/>
     </row>
     <row r="449" spans="2:2" s="1" customFormat="1">
-      <c r="B449" s="20"/>
+      <c r="B449" s="19"/>
     </row>
     <row r="450" spans="2:2" s="1" customFormat="1">
-      <c r="B450" s="20"/>
+      <c r="B450" s="19"/>
     </row>
     <row r="451" spans="2:2" s="1" customFormat="1">
-      <c r="B451" s="20"/>
+      <c r="B451" s="19"/>
     </row>
     <row r="452" spans="2:2" s="1" customFormat="1">
-      <c r="B452" s="20"/>
+      <c r="B452" s="19"/>
     </row>
     <row r="453" spans="2:2" s="1" customFormat="1">
-      <c r="B453" s="20"/>
+      <c r="B453" s="19"/>
     </row>
     <row r="454" spans="2:2" s="1" customFormat="1">
-      <c r="B454" s="20"/>
+      <c r="B454" s="19"/>
     </row>
     <row r="455" spans="2:2" s="1" customFormat="1">
-      <c r="B455" s="20"/>
+      <c r="B455" s="19"/>
     </row>
     <row r="456" spans="2:2" s="1" customFormat="1">
-      <c r="B456" s="20"/>
+      <c r="B456" s="19"/>
     </row>
     <row r="457" spans="2:2" s="1" customFormat="1">
-      <c r="B457" s="20"/>
+      <c r="B457" s="19"/>
     </row>
     <row r="458" spans="2:2" s="1" customFormat="1">
-      <c r="B458" s="20"/>
+      <c r="B458" s="19"/>
     </row>
     <row r="459" spans="2:2" s="1" customFormat="1">
-      <c r="B459" s="20"/>
+      <c r="B459" s="19"/>
     </row>
     <row r="460" spans="2:2" s="1" customFormat="1">
-      <c r="B460" s="20"/>
+      <c r="B460" s="19"/>
     </row>
     <row r="461" spans="2:2" s="1" customFormat="1">
-      <c r="B461" s="20"/>
+      <c r="B461" s="19"/>
     </row>
     <row r="462" spans="2:2" s="1" customFormat="1">
-      <c r="B462" s="20"/>
+      <c r="B462" s="19"/>
     </row>
     <row r="463" spans="2:2" s="1" customFormat="1">
-      <c r="B463" s="20"/>
+      <c r="B463" s="19"/>
     </row>
     <row r="464" spans="2:2" s="1" customFormat="1">
-      <c r="B464" s="20"/>
+      <c r="B464" s="19"/>
     </row>
     <row r="465" spans="2:2" s="1" customFormat="1">
-      <c r="B465" s="20"/>
+      <c r="B465" s="19"/>
     </row>
     <row r="466" spans="2:2" s="1" customFormat="1">
-      <c r="B466" s="20"/>
+      <c r="B466" s="19"/>
     </row>
     <row r="467" spans="2:2" s="1" customFormat="1">
-      <c r="B467" s="20"/>
+      <c r="B467" s="19"/>
     </row>
     <row r="468" spans="2:2" s="1" customFormat="1">
-      <c r="B468" s="20"/>
+      <c r="B468" s="19"/>
     </row>
     <row r="469" spans="2:2" s="1" customFormat="1">
-      <c r="B469" s="20"/>
+      <c r="B469" s="19"/>
     </row>
     <row r="470" spans="2:2" s="1" customFormat="1">
-      <c r="B470" s="20"/>
+      <c r="B470" s="19"/>
     </row>
     <row r="471" spans="2:2" s="1" customFormat="1">
-      <c r="B471" s="20"/>
+      <c r="B471" s="19"/>
     </row>
     <row r="472" spans="2:2" s="1" customFormat="1">
-      <c r="B472" s="20"/>
+      <c r="B472" s="19"/>
     </row>
     <row r="473" spans="2:2" s="1" customFormat="1">
-      <c r="B473" s="20"/>
+      <c r="B473" s="19"/>
     </row>
     <row r="474" spans="2:2" s="1" customFormat="1">
-      <c r="B474" s="20"/>
+      <c r="B474" s="19"/>
     </row>
     <row r="475" spans="2:2" s="1" customFormat="1">
-      <c r="B475" s="20"/>
+      <c r="B475" s="19"/>
     </row>
     <row r="476" spans="2:2" s="1" customFormat="1">
-      <c r="B476" s="20"/>
+      <c r="B476" s="19"/>
     </row>
     <row r="477" spans="2:2" s="1" customFormat="1">
-      <c r="B477" s="20"/>
+      <c r="B477" s="19"/>
     </row>
     <row r="478" spans="2:2" s="1" customFormat="1">
-      <c r="B478" s="20"/>
+      <c r="B478" s="19"/>
     </row>
     <row r="479" spans="2:2" s="1" customFormat="1">
-      <c r="B479" s="20"/>
+      <c r="B479" s="19"/>
     </row>
     <row r="480" spans="2:2" s="1" customFormat="1">
-      <c r="B480" s="20"/>
+      <c r="B480" s="19"/>
     </row>
     <row r="481" spans="1:10">
       <c r="A481" s="1"/>
-      <c r="B481" s="20"/>
+      <c r="B481" s="19"/>
       <c r="G481" s="1"/>
       <c r="H481" s="1"/>
       <c r="I481" s="1"/>
@@ -5239,7 +5317,7 @@
     </row>
     <row r="482" spans="1:10">
       <c r="A482" s="1"/>
-      <c r="B482" s="20"/>
+      <c r="B482" s="19"/>
       <c r="G482" s="1"/>
       <c r="H482" s="1"/>
       <c r="I482" s="1"/>
@@ -5247,7 +5325,7 @@
     </row>
     <row r="483" spans="1:10">
       <c r="A483" s="1"/>
-      <c r="B483" s="20"/>
+      <c r="B483" s="19"/>
       <c r="G483" s="1"/>
       <c r="H483" s="1"/>
       <c r="I483" s="1"/>
@@ -5255,7 +5333,7 @@
     </row>
     <row r="484" spans="1:10">
       <c r="A484" s="1"/>
-      <c r="B484" s="20"/>
+      <c r="B484" s="19"/>
       <c r="G484" s="1"/>
       <c r="H484" s="1"/>
       <c r="I484" s="1"/>
@@ -5263,7 +5341,7 @@
     </row>
     <row r="485" spans="1:10">
       <c r="A485" s="1"/>
-      <c r="B485" s="20"/>
+      <c r="B485" s="19"/>
       <c r="G485" s="1"/>
       <c r="H485" s="1"/>
       <c r="I485" s="1"/>
@@ -5271,7 +5349,7 @@
     </row>
     <row r="486" spans="1:10">
       <c r="A486" s="1"/>
-      <c r="B486" s="20"/>
+      <c r="B486" s="19"/>
       <c r="G486" s="1"/>
       <c r="H486" s="1"/>
       <c r="I486" s="1"/>
@@ -5279,7 +5357,7 @@
     </row>
     <row r="487" spans="1:10">
       <c r="A487" s="1"/>
-      <c r="B487" s="20"/>
+      <c r="B487" s="19"/>
       <c r="G487" s="1"/>
       <c r="H487" s="1"/>
       <c r="I487" s="1"/>
@@ -5287,7 +5365,7 @@
     </row>
     <row r="488" spans="1:10">
       <c r="A488" s="1"/>
-      <c r="B488" s="20"/>
+      <c r="B488" s="19"/>
       <c r="G488" s="1"/>
       <c r="H488" s="1"/>
       <c r="I488" s="1"/>
@@ -5295,7 +5373,7 @@
     </row>
     <row r="489" spans="1:10">
       <c r="A489" s="1"/>
-      <c r="B489" s="20"/>
+      <c r="B489" s="19"/>
       <c r="G489" s="1"/>
       <c r="H489" s="1"/>
       <c r="I489" s="1"/>
@@ -5303,7 +5381,7 @@
     </row>
     <row r="490" spans="1:10">
       <c r="A490" s="1"/>
-      <c r="B490" s="20"/>
+      <c r="B490" s="19"/>
       <c r="G490" s="1"/>
       <c r="H490" s="1"/>
       <c r="I490" s="1"/>
@@ -10089,6 +10167,43 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0"/>
   <dataConsolidate/>
   <mergeCells count="53">
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B89:F89"/>
@@ -10105,43 +10220,6 @@
     <mergeCell ref="B99:E99"/>
     <mergeCell ref="B101:E101"/>
     <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" display="www.BOYDSIGNSYSTEMS.com                                                                     " xr:uid="{00000000-0004-0000-0200-000000000000}"/>

--- a/templates/Blank.xlsx
+++ b/templates/Blank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\efinney\Desktop\Chat GPT\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A7DACF-0F5F-4796-BF95-AED63C8A24D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A6F779-2A81-4B54-BE38-BE9CC629D539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,130 +1705,6 @@
     <xf numFmtId="4" fontId="2" fillId="6" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="6" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="39" fillId="6" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1837,10 +1713,95 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1848,110 +1809,149 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="39" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="48" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -2367,61 +2367,61 @@
     <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A1" s="164" t="e" vm="1">
+    <row r="1" spans="1:11">
+      <c r="A1" s="117" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-    </row>
-    <row r="2" spans="1:11" ht="12.6" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="178"/>
-      <c r="I2" s="178"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="178"/>
-    </row>
-    <row r="3" spans="1:11" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="164"/>
-      <c r="C3" s="164"/>
-      <c r="D3" s="164"/>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="178"/>
-      <c r="J3" s="178"/>
-      <c r="K3" s="178"/>
-    </row>
-    <row r="4" spans="1:11" ht="12.2" customHeight="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="178"/>
-      <c r="I4" s="178"/>
-      <c r="J4" s="178"/>
-      <c r="K4" s="178"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1">
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="117"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="147"/>
+      <c r="I2" s="147"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="117"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="146"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="147"/>
+      <c r="K3" s="147"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="117"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="147"/>
+      <c r="K4" s="147"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5">
       <c r="B5" s="50" t="s">
         <v>31</v>
       </c>
@@ -2429,215 +2429,215 @@
       <c r="D5" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="165"/>
-      <c r="F5" s="165"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178"/>
-    </row>
-    <row r="6" spans="1:11" ht="11.45" customHeight="1">
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+    </row>
+    <row r="6" spans="1:11" ht="15">
       <c r="C6" s="57"/>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
       <c r="F6" s="52"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="178"/>
-      <c r="I6" s="178"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
-    </row>
-    <row r="7" spans="1:11" ht="12.2" customHeight="1">
+      <c r="G6" s="148"/>
+      <c r="H6" s="147"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="147"/>
+      <c r="K6" s="147"/>
+    </row>
+    <row r="7" spans="1:11" ht="15">
       <c r="B7" s="53"/>
       <c r="C7" s="63"/>
       <c r="D7" s="22"/>
       <c r="E7" s="35"/>
       <c r="F7" s="39"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="178"/>
-      <c r="I7" s="178"/>
-      <c r="J7" s="178"/>
-      <c r="K7" s="178"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1">
+      <c r="G7" s="146"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+    </row>
+    <row r="8" spans="1:11" ht="23.25">
       <c r="A8" s="64"/>
       <c r="B8" s="65" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="65"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="166"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
       <c r="F8" s="98"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="178"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="178"/>
-      <c r="K8" s="178"/>
-    </row>
-    <row r="9" spans="1:11" customFormat="1" ht="18.75" hidden="1" customHeight="1">
+      <c r="G8" s="149"/>
+      <c r="H8" s="147"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="147"/>
+      <c r="K8" s="147"/>
+    </row>
+    <row r="9" spans="1:11" customFormat="1" ht="23.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="100"/>
       <c r="E9" s="100"/>
       <c r="F9" s="99"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="178"/>
-      <c r="I9" s="179"/>
-      <c r="J9" s="179"/>
-      <c r="K9" s="179"/>
-    </row>
-    <row r="10" spans="1:11" s="8" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="172" t="s">
+      <c r="G9" s="150"/>
+      <c r="H9" s="147"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="151"/>
+      <c r="K9" s="151"/>
+    </row>
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="13.5">
+      <c r="A10" s="129" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="173"/>
+      <c r="B10" s="130"/>
       <c r="C10" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="167" t="s">
+      <c r="D10" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="180"/>
-      <c r="I10" s="180"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-    </row>
-    <row r="11" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A11" s="174"/>
-      <c r="B11" s="175"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+    </row>
+    <row r="11" spans="1:11" s="8" customFormat="1">
+      <c r="A11" s="131"/>
+      <c r="B11" s="132"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="170"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="180"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-    </row>
-    <row r="12" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A12" s="162"/>
-      <c r="B12" s="177"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="13.5">
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
       <c r="C12" s="93"/>
-      <c r="D12" s="157"/>
-      <c r="E12" s="158"/>
-      <c r="F12" s="158"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="180"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="180"/>
-    </row>
-    <row r="13" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A13" s="162"/>
-      <c r="B13" s="163"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="155"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+    </row>
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="13.5">
+      <c r="A13" s="134"/>
+      <c r="B13" s="136"/>
       <c r="C13" s="94"/>
-      <c r="D13" s="157"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="180"/>
-      <c r="J13" s="180"/>
-      <c r="K13" s="180"/>
-    </row>
-    <row r="14" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A14" s="162"/>
-      <c r="B14" s="163"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="155"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="153"/>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1">
+      <c r="A14" s="134"/>
+      <c r="B14" s="136"/>
       <c r="C14" s="94"/>
-      <c r="D14" s="159"/>
-      <c r="E14" s="160"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="180"/>
-      <c r="J14" s="180"/>
-      <c r="K14" s="180"/>
-    </row>
-    <row r="15" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A15" s="162"/>
-      <c r="B15" s="163"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="154"/>
+      <c r="H14" s="153"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="153"/>
+      <c r="K14" s="153"/>
+    </row>
+    <row r="15" spans="1:11" s="8" customFormat="1">
+      <c r="A15" s="134"/>
+      <c r="B15" s="136"/>
       <c r="C15" s="95"/>
-      <c r="D15" s="159"/>
-      <c r="E15" s="160"/>
-      <c r="F15" s="160"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="180"/>
-      <c r="J15" s="180"/>
-      <c r="K15" s="180"/>
-    </row>
-    <row r="16" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A16" s="162"/>
-      <c r="B16" s="163"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="153"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="153"/>
+      <c r="K15" s="153"/>
+    </row>
+    <row r="16" spans="1:11" s="8" customFormat="1">
+      <c r="A16" s="134"/>
+      <c r="B16" s="136"/>
       <c r="C16" s="93"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="158"/>
-      <c r="F16" s="158"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="180"/>
-      <c r="J16" s="180"/>
-      <c r="K16" s="180"/>
-    </row>
-    <row r="17" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A17" s="162"/>
-      <c r="B17" s="163"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="156"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="153"/>
+    </row>
+    <row r="17" spans="1:11" s="8" customFormat="1">
+      <c r="A17" s="134"/>
+      <c r="B17" s="136"/>
       <c r="C17" s="96"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="158"/>
-      <c r="F17" s="158"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="180"/>
-      <c r="J17" s="180"/>
-      <c r="K17" s="180"/>
-    </row>
-    <row r="18" spans="1:11" ht="12.75" hidden="1" customHeight="1">
+      <c r="D17" s="118"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="156"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="54"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
       <c r="F18" s="110"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="178"/>
-      <c r="I18" s="178"/>
-      <c r="J18" s="178"/>
-      <c r="K18" s="178"/>
-    </row>
-    <row r="19" spans="1:11" s="8" customFormat="1" ht="14.25" customHeight="1">
+      <c r="G18" s="157"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="147"/>
+    </row>
+    <row r="19" spans="1:11" s="8" customFormat="1">
       <c r="A19" s="56"/>
-      <c r="B19" s="171"/>
-      <c r="C19" s="171"/>
-      <c r="D19" s="171"/>
-      <c r="E19" s="171"/>
-      <c r="F19" s="171"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="180"/>
-      <c r="I19" s="180"/>
-      <c r="J19" s="180"/>
-      <c r="K19" s="180"/>
-    </row>
-    <row r="20" spans="1:11" ht="4.7" customHeight="1">
+      <c r="B19" s="128"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="153"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="26"/>
       <c r="B20" s="26"/>
       <c r="C20" s="26"/>
       <c r="D20" s="26"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="178"/>
-      <c r="I20" s="178"/>
-      <c r="J20" s="178"/>
-      <c r="K20" s="178"/>
-    </row>
-    <row r="21" spans="1:11" s="9" customFormat="1" ht="14.45" customHeight="1">
+      <c r="G20" s="159"/>
+      <c r="H20" s="147"/>
+      <c r="I20" s="147"/>
+      <c r="J20" s="147"/>
+      <c r="K20" s="147"/>
+    </row>
+    <row r="21" spans="1:11" s="9" customFormat="1">
       <c r="A21" s="67" t="s">
         <v>64</v>
       </c>
@@ -2646,66 +2646,66 @@
       <c r="D21" s="1"/>
       <c r="E21" s="68"/>
       <c r="F21" s="58"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="181"/>
-      <c r="I21" s="181"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="181"/>
-    </row>
-    <row r="22" spans="1:11" ht="11.45" customHeight="1">
-      <c r="A22" s="156" t="s">
+      <c r="G21" s="160"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="156"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="176"/>
-      <c r="E22" s="176"/>
-      <c r="F22" s="176"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="178"/>
-      <c r="I22" s="178"/>
-      <c r="J22" s="178"/>
-      <c r="K22" s="178"/>
-    </row>
-    <row r="23" spans="1:11" ht="11.45" customHeight="1">
-      <c r="A23" s="156" t="s">
+      <c r="B22" s="137"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="147"/>
+      <c r="I22" s="147"/>
+      <c r="J22" s="147"/>
+      <c r="K22" s="147"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="156"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="176"/>
-      <c r="E23" s="176"/>
-      <c r="F23" s="176"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="178"/>
-      <c r="I23" s="178"/>
-      <c r="J23" s="178"/>
-      <c r="K23" s="178"/>
-    </row>
-    <row r="24" spans="1:11" ht="9" customHeight="1">
+      <c r="B23" s="137"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="147"/>
+      <c r="I23" s="147"/>
+      <c r="J23" s="147"/>
+      <c r="K23" s="147"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="B24" s="27"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="178"/>
-      <c r="I24" s="178"/>
-      <c r="J24" s="178"/>
-      <c r="K24" s="178"/>
-    </row>
-    <row r="25" spans="1:11" ht="19.5" customHeight="1">
+      <c r="G24" s="162"/>
+      <c r="H24" s="147"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="147"/>
+      <c r="K24" s="147"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="69" t="s">
         <v>11</v>
       </c>
       <c r="B25" s="59"/>
-      <c r="C25" s="161"/>
-      <c r="D25" s="161"/>
-      <c r="E25" s="161"/>
-      <c r="F25" s="161"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="178"/>
-      <c r="I25" s="178"/>
-      <c r="J25" s="178"/>
-      <c r="K25" s="178"/>
-    </row>
-    <row r="26" spans="1:11" s="10" customFormat="1" ht="24.75" customHeight="1">
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="163"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="147"/>
+    </row>
+    <row r="26" spans="1:11" s="10" customFormat="1" ht="25.5">
       <c r="A26" s="29" t="s">
         <v>1</v>
       </c>
@@ -2724,13 +2724,13 @@
       <c r="F26" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="128"/>
-      <c r="H26" s="182"/>
-      <c r="I26" s="182"/>
-      <c r="J26" s="182"/>
-      <c r="K26" s="182"/>
-    </row>
-    <row r="27" spans="1:11" s="10" customFormat="1" ht="1.5" hidden="1" customHeight="1">
+      <c r="G26" s="164"/>
+      <c r="H26" s="165"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
+      <c r="K26" s="165"/>
+    </row>
+    <row r="27" spans="1:11" s="10" customFormat="1">
       <c r="A27" s="60">
         <v>0</v>
       </c>
@@ -2739,11 +2739,11 @@
       <c r="D27" s="62"/>
       <c r="E27" s="61"/>
       <c r="F27" s="112"/>
-      <c r="G27" s="128"/>
-      <c r="H27" s="182"/>
-      <c r="I27" s="182"/>
-      <c r="J27" s="182"/>
-      <c r="K27" s="182"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="165"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="165"/>
+      <c r="K27" s="165"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="87">
@@ -2758,11 +2758,11 @@
         <f>IF(D28&lt;&gt;"",D28*E28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G28" s="129"/>
-      <c r="H28" s="178"/>
-      <c r="I28" s="178"/>
-      <c r="J28" s="178"/>
-      <c r="K28" s="178"/>
+      <c r="G28" s="166"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="147"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="87">
@@ -2777,11 +2777,11 @@
         <f t="shared" ref="F29:F44" si="1">IF(D29&lt;&gt;"",D29*E29," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G29" s="129"/>
-      <c r="H29" s="178"/>
-      <c r="I29" s="178"/>
-      <c r="J29" s="178"/>
-      <c r="K29" s="178"/>
+      <c r="G29" s="166"/>
+      <c r="H29" s="147"/>
+      <c r="I29" s="147"/>
+      <c r="J29" s="147"/>
+      <c r="K29" s="147"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="87">
@@ -2796,11 +2796,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G30" s="129"/>
-      <c r="H30" s="178"/>
-      <c r="I30" s="178"/>
-      <c r="J30" s="178"/>
-      <c r="K30" s="178"/>
+      <c r="G30" s="166"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="147"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="87">
@@ -2815,11 +2815,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G31" s="129"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="178"/>
-      <c r="J31" s="178"/>
-      <c r="K31" s="178"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="147"/>
+      <c r="I31" s="147"/>
+      <c r="J31" s="147"/>
+      <c r="K31" s="147"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="87">
@@ -2834,11 +2834,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G32" s="129"/>
-      <c r="H32" s="178"/>
-      <c r="I32" s="178"/>
-      <c r="J32" s="178"/>
-      <c r="K32" s="178"/>
+      <c r="G32" s="166"/>
+      <c r="H32" s="147"/>
+      <c r="I32" s="147"/>
+      <c r="J32" s="147"/>
+      <c r="K32" s="147"/>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="87">
@@ -2853,11 +2853,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G33" s="129"/>
-      <c r="H33" s="178"/>
-      <c r="I33" s="178"/>
-      <c r="J33" s="178"/>
-      <c r="K33" s="178"/>
+      <c r="G33" s="166"/>
+      <c r="H33" s="147"/>
+      <c r="I33" s="147"/>
+      <c r="J33" s="147"/>
+      <c r="K33" s="147"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="87">
@@ -2872,11 +2872,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G34" s="129"/>
-      <c r="H34" s="178"/>
-      <c r="I34" s="178"/>
-      <c r="J34" s="178"/>
-      <c r="K34" s="178"/>
+      <c r="G34" s="166"/>
+      <c r="H34" s="147"/>
+      <c r="I34" s="147"/>
+      <c r="J34" s="147"/>
+      <c r="K34" s="147"/>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="87">
@@ -2891,11 +2891,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G35" s="129"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="178"/>
-      <c r="K35" s="178"/>
+      <c r="G35" s="166"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="147"/>
+      <c r="J35" s="147"/>
+      <c r="K35" s="147"/>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="87">
@@ -2910,11 +2910,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G36" s="129"/>
-      <c r="H36" s="178"/>
-      <c r="I36" s="178"/>
-      <c r="J36" s="178"/>
-      <c r="K36" s="178"/>
+      <c r="G36" s="166"/>
+      <c r="H36" s="147"/>
+      <c r="I36" s="147"/>
+      <c r="J36" s="147"/>
+      <c r="K36" s="147"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="87">
@@ -2929,11 +2929,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G37" s="129"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="178"/>
-      <c r="J37" s="178"/>
-      <c r="K37" s="178"/>
+      <c r="G37" s="166"/>
+      <c r="H37" s="147"/>
+      <c r="I37" s="147"/>
+      <c r="J37" s="147"/>
+      <c r="K37" s="147"/>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="87">
@@ -2948,11 +2948,11 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G38" s="130"/>
-      <c r="H38" s="178"/>
-      <c r="I38" s="178"/>
-      <c r="J38" s="178"/>
-      <c r="K38" s="178"/>
+      <c r="G38" s="167"/>
+      <c r="H38" s="147"/>
+      <c r="I38" s="147"/>
+      <c r="J38" s="147"/>
+      <c r="K38" s="147"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="87">
@@ -2967,13 +2967,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G39" s="130"/>
-      <c r="H39" s="178"/>
-      <c r="I39" s="178"/>
-      <c r="J39" s="178"/>
-      <c r="K39" s="178"/>
-    </row>
-    <row r="40" spans="1:11" ht="24.75" hidden="1" customHeight="1" thickBot="1">
+      <c r="G39" s="167"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="147"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="147"/>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="87">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2986,13 +2986,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G40" s="129"/>
-      <c r="H40" s="178"/>
-      <c r="I40" s="178"/>
-      <c r="J40" s="178"/>
-      <c r="K40" s="178"/>
-    </row>
-    <row r="41" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G40" s="166"/>
+      <c r="H40" s="147"/>
+      <c r="I40" s="147"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="147"/>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="87">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3005,13 +3005,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G41" s="131"/>
-      <c r="H41" s="178"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="178"/>
-      <c r="K41" s="178"/>
-    </row>
-    <row r="42" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G41" s="168"/>
+      <c r="H41" s="147"/>
+      <c r="I41" s="147"/>
+      <c r="J41" s="147"/>
+      <c r="K41" s="147"/>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="87">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3024,13 +3024,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G42" s="132"/>
-      <c r="H42" s="178"/>
-      <c r="I42" s="178"/>
-      <c r="J42" s="178"/>
-      <c r="K42" s="178"/>
-    </row>
-    <row r="43" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G42" s="169"/>
+      <c r="H42" s="147"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="147"/>
+      <c r="K42" s="147"/>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="87">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3043,13 +3043,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G43" s="132"/>
-      <c r="H43" s="178"/>
-      <c r="I43" s="178"/>
-      <c r="J43" s="178"/>
-      <c r="K43" s="178"/>
-    </row>
-    <row r="44" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G43" s="169"/>
+      <c r="H43" s="147"/>
+      <c r="I43" s="147"/>
+      <c r="J43" s="147"/>
+      <c r="K43" s="147"/>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="87">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3062,13 +3062,13 @@
         <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G44" s="133"/>
-      <c r="H44" s="183"/>
-      <c r="I44" s="183"/>
-      <c r="J44" s="178"/>
-      <c r="K44" s="178"/>
-    </row>
-    <row r="45" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G44" s="170"/>
+      <c r="H44" s="171"/>
+      <c r="I44" s="171"/>
+      <c r="J44" s="147"/>
+      <c r="K44" s="147"/>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="87">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3081,13 +3081,13 @@
         <f t="shared" ref="F45:F47" si="2">IF(D45&lt;&gt;"",D45*E45," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G45" s="132"/>
-      <c r="H45" s="178"/>
-      <c r="I45" s="178"/>
-      <c r="J45" s="178"/>
-      <c r="K45" s="178"/>
-    </row>
-    <row r="46" spans="1:11" ht="12.75" customHeight="1">
+      <c r="G45" s="169"/>
+      <c r="H45" s="147"/>
+      <c r="I45" s="147"/>
+      <c r="J45" s="147"/>
+      <c r="K45" s="147"/>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="87">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3100,13 +3100,13 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G46" s="132"/>
-      <c r="H46" s="178"/>
-      <c r="I46" s="178"/>
-      <c r="J46" s="178"/>
-      <c r="K46" s="178"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+      <c r="G46" s="169"/>
+      <c r="H46" s="147"/>
+      <c r="I46" s="147"/>
+      <c r="J46" s="147"/>
+      <c r="K46" s="147"/>
+    </row>
+    <row r="47" spans="1:11" ht="13.5" thickBot="1">
       <c r="A47" s="87">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3119,13 +3119,13 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="G47" s="134"/>
-      <c r="H47" s="178"/>
-      <c r="I47" s="178"/>
-      <c r="J47" s="178"/>
-      <c r="K47" s="178"/>
-    </row>
-    <row r="48" spans="1:11" ht="14.25" customHeight="1">
+      <c r="G47" s="172"/>
+      <c r="H47" s="147"/>
+      <c r="I47" s="147"/>
+      <c r="J47" s="147"/>
+      <c r="K47" s="147"/>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="92"/>
       <c r="B48" s="82"/>
       <c r="C48" s="83"/>
@@ -3137,13 +3137,13 @@
         <f>SUM(F28:F47)</f>
         <v>0</v>
       </c>
-      <c r="G48" s="135"/>
-      <c r="H48" s="178"/>
-      <c r="I48" s="178"/>
-      <c r="J48" s="178"/>
-      <c r="K48" s="178"/>
-    </row>
-    <row r="49" spans="1:11" ht="16.149999999999999" customHeight="1">
+      <c r="G48" s="173"/>
+      <c r="H48" s="147"/>
+      <c r="I48" s="147"/>
+      <c r="J48" s="147"/>
+      <c r="K48" s="147"/>
+    </row>
+    <row r="49" spans="1:11" ht="15">
       <c r="A49" s="40"/>
       <c r="B49" s="73"/>
       <c r="C49" s="74"/>
@@ -3151,13 +3151,13 @@
         <v>69</v>
       </c>
       <c r="F49" s="79"/>
-      <c r="G49" s="136"/>
-      <c r="H49" s="178"/>
-      <c r="I49" s="178"/>
-      <c r="J49" s="178"/>
-      <c r="K49" s="178"/>
-    </row>
-    <row r="50" spans="1:11" ht="12" customHeight="1">
+      <c r="G49" s="174"/>
+      <c r="H49" s="147"/>
+      <c r="I49" s="147"/>
+      <c r="J49" s="147"/>
+      <c r="K49" s="147"/>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="40"/>
       <c r="B50" s="73"/>
       <c r="C50" s="74"/>
@@ -3167,13 +3167,13 @@
       <c r="F50" s="79">
         <v>0</v>
       </c>
-      <c r="G50" s="126"/>
-      <c r="H50" s="178"/>
-      <c r="I50" s="178"/>
-      <c r="J50" s="178"/>
-      <c r="K50" s="178"/>
-    </row>
-    <row r="51" spans="1:11" s="18" customFormat="1" ht="12.75" customHeight="1">
+      <c r="G50" s="162"/>
+      <c r="H50" s="147"/>
+      <c r="I50" s="147"/>
+      <c r="J50" s="147"/>
+      <c r="K50" s="147"/>
+    </row>
+    <row r="51" spans="1:11" s="18" customFormat="1">
       <c r="A51" s="40"/>
       <c r="B51" s="73"/>
       <c r="C51" s="75"/>
@@ -3184,13 +3184,13 @@
       <c r="F51" s="102">
         <v>0</v>
       </c>
-      <c r="G51" s="137"/>
-      <c r="H51" s="184"/>
-      <c r="I51" s="184"/>
-      <c r="J51" s="184"/>
-      <c r="K51" s="184"/>
-    </row>
-    <row r="52" spans="1:11" ht="15" customHeight="1">
+      <c r="G51" s="175"/>
+      <c r="H51" s="176"/>
+      <c r="I51" s="176"/>
+      <c r="J51" s="176"/>
+      <c r="K51" s="176"/>
+    </row>
+    <row r="52" spans="1:11" ht="13.5">
       <c r="A52" s="38"/>
       <c r="B52" s="73"/>
       <c r="C52" s="76"/>
@@ -3201,13 +3201,13 @@
       <c r="F52" s="101">
         <v>0</v>
       </c>
-      <c r="G52" s="126"/>
-      <c r="H52" s="178"/>
-      <c r="I52" s="178"/>
-      <c r="J52" s="178"/>
-      <c r="K52" s="178"/>
-    </row>
-    <row r="53" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="G52" s="162"/>
+      <c r="H52" s="147"/>
+      <c r="I52" s="147"/>
+      <c r="J52" s="147"/>
+      <c r="K52" s="147"/>
+    </row>
+    <row r="53" spans="1:11" ht="14.25" thickBot="1">
       <c r="A53" s="4"/>
       <c r="B53" s="36"/>
       <c r="C53" s="37"/>
@@ -3216,13 +3216,13 @@
         <v>7</v>
       </c>
       <c r="F53" s="80"/>
-      <c r="G53" s="137"/>
-      <c r="H53" s="178"/>
-      <c r="I53" s="178"/>
-      <c r="J53" s="178"/>
-      <c r="K53" s="178"/>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1">
+      <c r="G53" s="175"/>
+      <c r="H53" s="147"/>
+      <c r="I53" s="147"/>
+      <c r="J53" s="147"/>
+      <c r="K53" s="147"/>
+    </row>
+    <row r="54" spans="1:11" ht="13.5">
       <c r="A54" s="40"/>
       <c r="B54" s="28"/>
       <c r="C54" s="15"/>
@@ -3234,24 +3234,24 @@
         <f>+F53+F52+F49+F48+F50</f>
         <v>0</v>
       </c>
-      <c r="G54" s="126"/>
-      <c r="H54" s="178"/>
-      <c r="I54" s="178"/>
-      <c r="J54" s="178"/>
-      <c r="K54" s="178"/>
-    </row>
-    <row r="55" spans="1:11" ht="5.25" customHeight="1">
+      <c r="G54" s="162"/>
+      <c r="H54" s="147"/>
+      <c r="I54" s="147"/>
+      <c r="J54" s="147"/>
+      <c r="K54" s="147"/>
+    </row>
+    <row r="55" spans="1:11" ht="14.25">
       <c r="A55" s="106"/>
       <c r="B55" s="107"/>
       <c r="C55" s="107"/>
       <c r="D55" s="107"/>
       <c r="E55" s="108"/>
       <c r="F55" s="109"/>
-      <c r="G55" s="138"/>
-      <c r="H55" s="178"/>
-      <c r="I55" s="178"/>
-      <c r="J55" s="178"/>
-      <c r="K55" s="178"/>
+      <c r="G55" s="177"/>
+      <c r="H55" s="147"/>
+      <c r="I55" s="147"/>
+      <c r="J55" s="147"/>
+      <c r="K55" s="147"/>
     </row>
     <row r="56" spans="1:11" ht="15">
       <c r="A56" s="97" t="s">
@@ -3262,93 +3262,93 @@
       <c r="D56" s="97"/>
       <c r="E56" s="97"/>
       <c r="F56" s="97"/>
-      <c r="G56" s="139"/>
-      <c r="H56" s="178"/>
-      <c r="I56" s="178"/>
-      <c r="J56" s="178"/>
-      <c r="K56" s="178"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1">
+      <c r="G56" s="178"/>
+      <c r="H56" s="147"/>
+      <c r="I56" s="147"/>
+      <c r="J56" s="147"/>
+      <c r="K56" s="147"/>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="4"/>
       <c r="B57"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
       <c r="F57"/>
-      <c r="G57" s="139"/>
-      <c r="H57" s="178"/>
-      <c r="I57" s="178"/>
-      <c r="J57" s="178"/>
-      <c r="K57" s="178"/>
-    </row>
-    <row r="58" spans="1:11" ht="28.5" customHeight="1">
+      <c r="G57" s="178"/>
+      <c r="H57" s="147"/>
+      <c r="I57" s="147"/>
+      <c r="J57" s="147"/>
+      <c r="K57" s="147"/>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B58" s="149" t="s">
+      <c r="B58" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="C58" s="149"/>
-      <c r="D58" s="149"/>
-      <c r="E58" s="149"/>
-      <c r="F58" s="149"/>
-      <c r="G58" s="126"/>
-      <c r="H58" s="178"/>
-      <c r="I58" s="178"/>
-      <c r="J58" s="178"/>
-      <c r="K58" s="178"/>
-    </row>
-    <row r="59" spans="1:11" ht="2.25" customHeight="1">
+      <c r="C58" s="116"/>
+      <c r="D58" s="116"/>
+      <c r="E58" s="116"/>
+      <c r="F58" s="116"/>
+      <c r="G58" s="162"/>
+      <c r="H58" s="147"/>
+      <c r="I58" s="147"/>
+      <c r="J58" s="147"/>
+      <c r="K58" s="147"/>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="42"/>
       <c r="B59" s="42"/>
       <c r="C59" s="70"/>
       <c r="D59" s="70"/>
       <c r="E59" s="70"/>
       <c r="F59"/>
-      <c r="G59" s="137"/>
-      <c r="H59" s="178"/>
-      <c r="I59" s="178"/>
-      <c r="J59" s="178"/>
-      <c r="K59" s="178"/>
-    </row>
-    <row r="60" spans="1:11" ht="31.5" customHeight="1">
+      <c r="G59" s="175"/>
+      <c r="H59" s="147"/>
+      <c r="I59" s="147"/>
+      <c r="J59" s="147"/>
+      <c r="K59" s="147"/>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B60" s="149" t="s">
+      <c r="B60" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="149"/>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
-      <c r="G60" s="126"/>
-      <c r="H60" s="178"/>
-      <c r="I60" s="178"/>
-      <c r="J60" s="178"/>
-      <c r="K60" s="178"/>
-    </row>
-    <row r="61" spans="1:11" ht="2.25" customHeight="1">
+      <c r="C60" s="116"/>
+      <c r="D60" s="116"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="116"/>
+      <c r="G60" s="162"/>
+      <c r="H60" s="147"/>
+      <c r="I60" s="147"/>
+      <c r="J60" s="147"/>
+      <c r="K60" s="147"/>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="42"/>
       <c r="B61" s="42"/>
       <c r="C61" s="70"/>
       <c r="D61" s="70"/>
       <c r="E61" s="70"/>
       <c r="F61"/>
-      <c r="G61" s="140"/>
-      <c r="H61" s="178"/>
-      <c r="I61" s="178"/>
-      <c r="J61" s="178"/>
-      <c r="K61" s="178"/>
-    </row>
-    <row r="62" spans="1:11" ht="13.5" customHeight="1">
+      <c r="G61" s="179"/>
+      <c r="H61" s="147"/>
+      <c r="I61" s="147"/>
+      <c r="J61" s="147"/>
+      <c r="K61" s="147"/>
+    </row>
+    <row r="62" spans="1:11" ht="14.25">
       <c r="A62" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="154" t="s">
+      <c r="B62" s="141" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="154"/>
+      <c r="C62" s="141"/>
       <c r="D62" s="81">
         <v>0.5</v>
       </c>
@@ -3359,590 +3359,590 @@
         <f>+F54*D62</f>
         <v>0</v>
       </c>
-      <c r="G62" s="140"/>
-      <c r="H62" s="178"/>
-      <c r="I62" s="178"/>
-      <c r="J62" s="178"/>
-      <c r="K62" s="178"/>
-    </row>
-    <row r="63" spans="1:11" ht="3" customHeight="1">
+      <c r="G62" s="179"/>
+      <c r="H62" s="147"/>
+      <c r="I62" s="147"/>
+      <c r="J62" s="147"/>
+      <c r="K62" s="147"/>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63" s="42"/>
       <c r="B63" s="42"/>
       <c r="C63" s="48"/>
       <c r="D63" s="45"/>
       <c r="E63" s="46"/>
       <c r="F63" s="47"/>
-      <c r="G63" s="126"/>
-      <c r="H63" s="178"/>
-      <c r="I63" s="178"/>
-      <c r="J63" s="178"/>
-      <c r="K63" s="178"/>
-    </row>
-    <row r="64" spans="1:11" ht="15" customHeight="1">
+      <c r="G63" s="162"/>
+      <c r="H63" s="147"/>
+      <c r="I63" s="147"/>
+      <c r="J63" s="147"/>
+      <c r="K63" s="147"/>
+    </row>
+    <row r="64" spans="1:11" ht="14.25">
       <c r="A64" s="42"/>
-      <c r="B64" s="153" t="s">
+      <c r="B64" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="153"/>
-      <c r="D64" s="153"/>
-      <c r="E64" s="153"/>
+      <c r="C64" s="140"/>
+      <c r="D64" s="140"/>
+      <c r="E64" s="140"/>
       <c r="F64" s="47"/>
-      <c r="G64" s="137"/>
-      <c r="H64" s="178"/>
-      <c r="I64" s="178"/>
-      <c r="J64" s="178"/>
-      <c r="K64" s="178"/>
-    </row>
-    <row r="65" spans="1:11" ht="8.4499999999999993" customHeight="1">
+      <c r="G64" s="175"/>
+      <c r="H64" s="147"/>
+      <c r="I64" s="147"/>
+      <c r="J64" s="147"/>
+      <c r="K64" s="147"/>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" s="42"/>
       <c r="B65" s="42"/>
       <c r="C65" s="70"/>
       <c r="D65" s="70"/>
       <c r="E65" s="70"/>
       <c r="F65"/>
-      <c r="G65" s="126"/>
-      <c r="H65" s="178"/>
-      <c r="I65" s="178"/>
-      <c r="J65" s="178"/>
-      <c r="K65" s="178"/>
-    </row>
-    <row r="66" spans="1:11" ht="15" customHeight="1">
+      <c r="G65" s="162"/>
+      <c r="H65" s="147"/>
+      <c r="I65" s="147"/>
+      <c r="J65" s="147"/>
+      <c r="K65" s="147"/>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B66" s="149" t="s">
+      <c r="B66" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="149"/>
-      <c r="D66" s="149"/>
-      <c r="E66" s="149"/>
-      <c r="F66" s="149"/>
-      <c r="G66" s="141"/>
-      <c r="H66" s="178"/>
-      <c r="I66" s="178"/>
-      <c r="J66" s="178"/>
-      <c r="K66" s="178"/>
-    </row>
-    <row r="67" spans="1:11" ht="8.4499999999999993" customHeight="1">
+      <c r="C66" s="116"/>
+      <c r="D66" s="116"/>
+      <c r="E66" s="116"/>
+      <c r="F66" s="116"/>
+      <c r="G66" s="180"/>
+      <c r="H66" s="147"/>
+      <c r="I66" s="147"/>
+      <c r="J66" s="147"/>
+      <c r="K66" s="147"/>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" s="42"/>
       <c r="B67" s="42"/>
       <c r="C67" s="70"/>
       <c r="D67" s="70"/>
       <c r="E67" s="70"/>
       <c r="F67"/>
-      <c r="G67" s="126"/>
-      <c r="H67" s="178"/>
-      <c r="I67" s="178"/>
-      <c r="J67" s="178"/>
-      <c r="K67" s="178"/>
-    </row>
-    <row r="68" spans="1:11" ht="70.5" customHeight="1">
+      <c r="G67" s="162"/>
+      <c r="H67" s="147"/>
+      <c r="I67" s="147"/>
+      <c r="J67" s="147"/>
+      <c r="K67" s="147"/>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="155" t="s">
+      <c r="B68" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="C68" s="155"/>
-      <c r="D68" s="155"/>
-      <c r="E68" s="155"/>
-      <c r="F68" s="155"/>
-      <c r="G68" s="137"/>
-      <c r="H68" s="178"/>
-      <c r="I68" s="178"/>
-      <c r="J68" s="178"/>
-      <c r="K68" s="178"/>
-    </row>
-    <row r="69" spans="1:11" ht="31.5" customHeight="1">
+      <c r="C68" s="142"/>
+      <c r="D68" s="142"/>
+      <c r="E68" s="142"/>
+      <c r="F68" s="142"/>
+      <c r="G68" s="175"/>
+      <c r="H68" s="147"/>
+      <c r="I68" s="147"/>
+      <c r="J68" s="147"/>
+      <c r="K68" s="147"/>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" s="42"/>
-      <c r="B69" s="155" t="s">
+      <c r="B69" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="155"/>
-      <c r="D69" s="155"/>
-      <c r="E69" s="155"/>
-      <c r="F69" s="155"/>
-      <c r="G69" s="126"/>
-      <c r="H69" s="178"/>
-      <c r="I69" s="178"/>
-      <c r="J69" s="178"/>
-      <c r="K69" s="178"/>
-    </row>
-    <row r="70" spans="1:11" ht="4.5" customHeight="1">
+      <c r="C69" s="142"/>
+      <c r="D69" s="142"/>
+      <c r="E69" s="142"/>
+      <c r="F69" s="142"/>
+      <c r="G69" s="162"/>
+      <c r="H69" s="147"/>
+      <c r="I69" s="147"/>
+      <c r="J69" s="147"/>
+      <c r="K69" s="147"/>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="42"/>
       <c r="B70" s="42"/>
       <c r="C70" s="48"/>
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70"/>
-      <c r="G70" s="137"/>
-      <c r="H70" s="178"/>
-      <c r="I70" s="178"/>
-      <c r="J70" s="178"/>
-      <c r="K70" s="178"/>
-    </row>
-    <row r="71" spans="1:11" ht="27" customHeight="1">
+      <c r="G70" s="175"/>
+      <c r="H70" s="147"/>
+      <c r="I70" s="147"/>
+      <c r="J70" s="147"/>
+      <c r="K70" s="147"/>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="149" t="s">
+      <c r="B71" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C71" s="149"/>
-      <c r="D71" s="149"/>
-      <c r="E71" s="149"/>
-      <c r="F71" s="149"/>
-      <c r="G71" s="126"/>
-      <c r="H71" s="178"/>
-      <c r="I71" s="178"/>
-      <c r="J71" s="178"/>
-      <c r="K71" s="178"/>
-    </row>
-    <row r="72" spans="1:11" ht="4.5" customHeight="1">
+      <c r="C71" s="116"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="116"/>
+      <c r="G71" s="162"/>
+      <c r="H71" s="147"/>
+      <c r="I71" s="147"/>
+      <c r="J71" s="147"/>
+      <c r="K71" s="147"/>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="42"/>
       <c r="B72" s="42"/>
       <c r="C72" s="70"/>
       <c r="D72" s="70"/>
       <c r="E72" s="70"/>
       <c r="F72"/>
-      <c r="G72" s="137"/>
-      <c r="H72" s="178"/>
-      <c r="I72" s="178"/>
-      <c r="J72" s="178"/>
-      <c r="K72" s="178"/>
-    </row>
-    <row r="73" spans="1:11" ht="39" customHeight="1">
+      <c r="G72" s="175"/>
+      <c r="H72" s="147"/>
+      <c r="I72" s="147"/>
+      <c r="J72" s="147"/>
+      <c r="K72" s="147"/>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B73" s="152" t="s">
+      <c r="B73" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="C73" s="152"/>
-      <c r="D73" s="152"/>
-      <c r="E73" s="152"/>
-      <c r="F73" s="152"/>
-      <c r="G73" s="126"/>
-      <c r="H73" s="178"/>
-      <c r="I73" s="178"/>
-      <c r="J73" s="178"/>
-      <c r="K73" s="178"/>
-    </row>
-    <row r="74" spans="1:11" ht="6" customHeight="1">
+      <c r="C73" s="139"/>
+      <c r="D73" s="139"/>
+      <c r="E73" s="139"/>
+      <c r="F73" s="139"/>
+      <c r="G73" s="162"/>
+      <c r="H73" s="147"/>
+      <c r="I73" s="147"/>
+      <c r="J73" s="147"/>
+      <c r="K73" s="147"/>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" s="42"/>
       <c r="B74" s="42"/>
       <c r="C74" s="71"/>
       <c r="D74" s="71"/>
       <c r="E74" s="71"/>
       <c r="F74"/>
-      <c r="G74" s="137"/>
-      <c r="H74" s="178"/>
-      <c r="I74" s="178"/>
-      <c r="J74" s="178"/>
-      <c r="K74" s="178"/>
-    </row>
-    <row r="75" spans="1:11" ht="30" customHeight="1">
+      <c r="G74" s="175"/>
+      <c r="H74" s="147"/>
+      <c r="I74" s="147"/>
+      <c r="J74" s="147"/>
+      <c r="K74" s="147"/>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B75" s="149" t="s">
+      <c r="B75" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C75" s="149"/>
-      <c r="D75" s="149"/>
-      <c r="E75" s="149"/>
-      <c r="F75" s="149"/>
-      <c r="G75" s="126"/>
-      <c r="H75" s="178"/>
-      <c r="I75" s="178"/>
-      <c r="J75" s="178"/>
-      <c r="K75" s="178"/>
-    </row>
-    <row r="76" spans="1:11" ht="3" customHeight="1">
+      <c r="C75" s="116"/>
+      <c r="D75" s="116"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="116"/>
+      <c r="G75" s="162"/>
+      <c r="H75" s="147"/>
+      <c r="I75" s="147"/>
+      <c r="J75" s="147"/>
+      <c r="K75" s="147"/>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="42"/>
       <c r="B76" s="42"/>
       <c r="C76" s="70"/>
       <c r="D76" s="70"/>
       <c r="E76" s="70"/>
       <c r="F76"/>
-      <c r="G76" s="137"/>
-      <c r="H76" s="178"/>
-      <c r="I76" s="178"/>
-      <c r="J76" s="178"/>
-      <c r="K76" s="178"/>
-    </row>
-    <row r="77" spans="1:11" ht="27" customHeight="1">
+      <c r="G76" s="175"/>
+      <c r="H76" s="147"/>
+      <c r="I76" s="147"/>
+      <c r="J76" s="147"/>
+      <c r="K76" s="147"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B77" s="149" t="s">
+      <c r="B77" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="149"/>
-      <c r="D77" s="149"/>
-      <c r="E77" s="149"/>
-      <c r="F77" s="149"/>
-      <c r="G77" s="126"/>
-      <c r="H77" s="178"/>
-      <c r="I77" s="178"/>
-      <c r="J77" s="178"/>
-      <c r="K77" s="178"/>
-    </row>
-    <row r="78" spans="1:11" ht="5.25" customHeight="1">
+      <c r="C77" s="116"/>
+      <c r="D77" s="116"/>
+      <c r="E77" s="116"/>
+      <c r="F77" s="116"/>
+      <c r="G77" s="162"/>
+      <c r="H77" s="147"/>
+      <c r="I77" s="147"/>
+      <c r="J77" s="147"/>
+      <c r="K77" s="147"/>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="42"/>
       <c r="B78" s="42"/>
       <c r="C78" s="70"/>
       <c r="D78" s="70"/>
       <c r="E78" s="70"/>
       <c r="F78"/>
-      <c r="G78" s="137"/>
-      <c r="H78" s="178"/>
-      <c r="I78" s="178"/>
-      <c r="J78" s="178"/>
-      <c r="K78" s="178"/>
-    </row>
-    <row r="79" spans="1:11" ht="40.5" customHeight="1">
+      <c r="G78" s="175"/>
+      <c r="H78" s="147"/>
+      <c r="I78" s="147"/>
+      <c r="J78" s="147"/>
+      <c r="K78" s="147"/>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B79" s="149" t="s">
+      <c r="B79" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="149"/>
-      <c r="D79" s="149"/>
-      <c r="E79" s="149"/>
-      <c r="F79" s="149"/>
-      <c r="G79" s="137"/>
-      <c r="H79" s="178"/>
-      <c r="I79" s="178"/>
-      <c r="J79" s="178"/>
-      <c r="K79" s="178"/>
-    </row>
-    <row r="80" spans="1:11" ht="3" customHeight="1">
+      <c r="C79" s="116"/>
+      <c r="D79" s="116"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="175"/>
+      <c r="H79" s="147"/>
+      <c r="I79" s="147"/>
+      <c r="J79" s="147"/>
+      <c r="K79" s="147"/>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" s="42"/>
       <c r="B80" s="42"/>
       <c r="C80" s="70"/>
       <c r="D80" s="70"/>
       <c r="E80" s="70"/>
       <c r="F80"/>
-      <c r="G80" s="126"/>
-      <c r="H80" s="178"/>
-      <c r="I80" s="178"/>
-      <c r="J80" s="178"/>
-      <c r="K80" s="178"/>
-    </row>
-    <row r="81" spans="1:11" ht="27.75" customHeight="1">
+      <c r="G80" s="162"/>
+      <c r="H80" s="147"/>
+      <c r="I80" s="147"/>
+      <c r="J80" s="147"/>
+      <c r="K80" s="147"/>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="149" t="s">
+      <c r="B81" s="116" t="s">
         <v>40</v>
       </c>
-      <c r="C81" s="149"/>
-      <c r="D81" s="149"/>
-      <c r="E81" s="149"/>
-      <c r="F81" s="149"/>
-      <c r="G81" s="126"/>
-      <c r="H81" s="178"/>
-      <c r="I81" s="178"/>
-      <c r="J81" s="178"/>
-      <c r="K81" s="178"/>
-    </row>
-    <row r="82" spans="1:11" ht="6" customHeight="1">
+      <c r="C81" s="116"/>
+      <c r="D81" s="116"/>
+      <c r="E81" s="116"/>
+      <c r="F81" s="116"/>
+      <c r="G81" s="162"/>
+      <c r="H81" s="147"/>
+      <c r="I81" s="147"/>
+      <c r="J81" s="147"/>
+      <c r="K81" s="147"/>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" s="42"/>
       <c r="B82" s="42"/>
       <c r="C82" s="70"/>
       <c r="D82" s="70"/>
       <c r="E82" s="70"/>
       <c r="F82"/>
-      <c r="G82" s="137"/>
-      <c r="H82" s="178"/>
-      <c r="I82" s="178"/>
-      <c r="J82" s="178"/>
-      <c r="K82" s="178"/>
-    </row>
-    <row r="83" spans="1:11" ht="42.75" customHeight="1">
+      <c r="G82" s="175"/>
+      <c r="H82" s="147"/>
+      <c r="I82" s="147"/>
+      <c r="J82" s="147"/>
+      <c r="K82" s="147"/>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="149" t="s">
+      <c r="B83" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="149"/>
-      <c r="D83" s="149"/>
-      <c r="E83" s="149"/>
-      <c r="F83" s="149"/>
-      <c r="G83" s="126"/>
-      <c r="H83" s="178"/>
-      <c r="I83" s="178"/>
-      <c r="J83" s="178"/>
-      <c r="K83" s="178"/>
-    </row>
-    <row r="84" spans="1:11" ht="6.75" customHeight="1">
+      <c r="C83" s="116"/>
+      <c r="D83" s="116"/>
+      <c r="E83" s="116"/>
+      <c r="F83" s="116"/>
+      <c r="G83" s="162"/>
+      <c r="H83" s="147"/>
+      <c r="I83" s="147"/>
+      <c r="J83" s="147"/>
+      <c r="K83" s="147"/>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84" s="42"/>
       <c r="B84" s="42"/>
       <c r="C84" s="70"/>
       <c r="D84" s="70"/>
       <c r="E84" s="70"/>
       <c r="F84"/>
-      <c r="G84" s="126"/>
-      <c r="H84" s="178"/>
-      <c r="I84" s="178"/>
-      <c r="J84" s="178"/>
-      <c r="K84" s="178"/>
-    </row>
-    <row r="85" spans="1:11" ht="81" customHeight="1">
+      <c r="G84" s="162"/>
+      <c r="H84" s="147"/>
+      <c r="I84" s="147"/>
+      <c r="J84" s="147"/>
+      <c r="K84" s="147"/>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B85" s="149" t="s">
+      <c r="B85" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="149"/>
-      <c r="D85" s="149"/>
-      <c r="E85" s="149"/>
-      <c r="F85" s="149"/>
-      <c r="G85" s="126"/>
-      <c r="H85" s="178"/>
-      <c r="I85" s="178"/>
-      <c r="J85" s="178"/>
-      <c r="K85" s="178"/>
-    </row>
-    <row r="86" spans="1:11" ht="6.75" customHeight="1">
+      <c r="C85" s="116"/>
+      <c r="D85" s="116"/>
+      <c r="E85" s="116"/>
+      <c r="F85" s="116"/>
+      <c r="G85" s="162"/>
+      <c r="H85" s="147"/>
+      <c r="I85" s="147"/>
+      <c r="J85" s="147"/>
+      <c r="K85" s="147"/>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86" s="42"/>
       <c r="B86" s="70"/>
       <c r="C86" s="70"/>
       <c r="D86" s="70"/>
       <c r="E86" s="70"/>
       <c r="F86" s="70"/>
-      <c r="G86" s="126"/>
-      <c r="H86" s="178"/>
-      <c r="I86" s="178"/>
-      <c r="J86" s="178"/>
-      <c r="K86" s="178"/>
-    </row>
-    <row r="87" spans="1:11" ht="88.5" customHeight="1">
+      <c r="G86" s="162"/>
+      <c r="H86" s="147"/>
+      <c r="I86" s="147"/>
+      <c r="J86" s="147"/>
+      <c r="K86" s="147"/>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B87" s="150" t="s">
+      <c r="B87" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="C87" s="150"/>
-      <c r="D87" s="150"/>
-      <c r="E87" s="150"/>
+      <c r="C87" s="144"/>
+      <c r="D87" s="144"/>
+      <c r="E87" s="144"/>
       <c r="F87"/>
-      <c r="G87" s="126"/>
-      <c r="H87" s="178"/>
-      <c r="I87" s="178"/>
-      <c r="J87" s="178"/>
-      <c r="K87" s="178"/>
-    </row>
-    <row r="88" spans="1:11" ht="6" customHeight="1">
+      <c r="G87" s="162"/>
+      <c r="H87" s="147"/>
+      <c r="I87" s="147"/>
+      <c r="J87" s="147"/>
+      <c r="K87" s="147"/>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88" s="42"/>
-      <c r="B88" s="150"/>
-      <c r="C88" s="150"/>
-      <c r="D88" s="150"/>
-      <c r="E88" s="150"/>
+      <c r="B88" s="144"/>
+      <c r="C88" s="144"/>
+      <c r="D88" s="144"/>
+      <c r="E88" s="144"/>
       <c r="F88"/>
-      <c r="G88" s="137"/>
-      <c r="H88" s="178"/>
-      <c r="I88" s="178"/>
-      <c r="J88" s="178"/>
-      <c r="K88" s="178"/>
-    </row>
-    <row r="89" spans="1:11" ht="18" customHeight="1">
+      <c r="G88" s="175"/>
+      <c r="H88" s="147"/>
+      <c r="I88" s="147"/>
+      <c r="J88" s="147"/>
+      <c r="K88" s="147"/>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="149" t="s">
+      <c r="B89" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="C89" s="149"/>
-      <c r="D89" s="149"/>
-      <c r="E89" s="149"/>
-      <c r="F89" s="149"/>
-      <c r="G89" s="137"/>
-      <c r="H89" s="178"/>
-      <c r="I89" s="178"/>
-      <c r="J89" s="178"/>
-      <c r="K89" s="178"/>
-    </row>
-    <row r="90" spans="1:11" ht="6.75" customHeight="1">
+      <c r="C89" s="116"/>
+      <c r="D89" s="116"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="175"/>
+      <c r="H89" s="147"/>
+      <c r="I89" s="147"/>
+      <c r="J89" s="147"/>
+      <c r="K89" s="147"/>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90" s="42"/>
       <c r="B90" s="42"/>
       <c r="C90" s="70"/>
       <c r="D90" s="70"/>
       <c r="E90" s="70"/>
       <c r="F90"/>
-      <c r="G90" s="137"/>
-      <c r="H90" s="178"/>
-      <c r="I90" s="178"/>
-      <c r="J90" s="178"/>
-      <c r="K90" s="178"/>
-    </row>
-    <row r="91" spans="1:11" ht="67.5" customHeight="1">
+      <c r="G90" s="175"/>
+      <c r="H90" s="147"/>
+      <c r="I90" s="147"/>
+      <c r="J90" s="147"/>
+      <c r="K90" s="147"/>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B91" s="149" t="s">
+      <c r="B91" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="149"/>
-      <c r="D91" s="149"/>
-      <c r="E91" s="149"/>
+      <c r="C91" s="116"/>
+      <c r="D91" s="116"/>
+      <c r="E91" s="116"/>
       <c r="F91"/>
-      <c r="G91" s="142"/>
-      <c r="H91" s="178"/>
-      <c r="I91" s="178"/>
-      <c r="J91" s="178"/>
-      <c r="K91" s="178"/>
-    </row>
-    <row r="92" spans="1:11" ht="9.75" customHeight="1">
+      <c r="G91" s="181"/>
+      <c r="H91" s="147"/>
+      <c r="I91" s="147"/>
+      <c r="J91" s="147"/>
+      <c r="K91" s="147"/>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92" s="42"/>
       <c r="B92" s="78"/>
       <c r="C92" s="78"/>
       <c r="D92" s="78"/>
       <c r="E92" s="78"/>
       <c r="F92"/>
-      <c r="G92" s="137"/>
-      <c r="H92" s="178"/>
-      <c r="I92" s="178"/>
-      <c r="J92" s="178"/>
-      <c r="K92" s="178"/>
-    </row>
-    <row r="93" spans="1:11" ht="54.75" customHeight="1">
+      <c r="G92" s="175"/>
+      <c r="H92" s="147"/>
+      <c r="I92" s="147"/>
+      <c r="J92" s="147"/>
+      <c r="K92" s="147"/>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B93" s="149" t="s">
+      <c r="B93" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="149"/>
-      <c r="D93" s="149"/>
-      <c r="E93" s="149"/>
+      <c r="C93" s="116"/>
+      <c r="D93" s="116"/>
+      <c r="E93" s="116"/>
       <c r="F93"/>
-      <c r="G93" s="137"/>
-      <c r="H93" s="178"/>
-      <c r="I93" s="178"/>
-      <c r="J93" s="178"/>
-      <c r="K93" s="178"/>
-    </row>
-    <row r="94" spans="1:11" ht="7.5" customHeight="1">
+      <c r="G93" s="175"/>
+      <c r="H93" s="147"/>
+      <c r="I93" s="147"/>
+      <c r="J93" s="147"/>
+      <c r="K93" s="147"/>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94" s="42"/>
       <c r="B94" s="78"/>
       <c r="C94" s="78"/>
       <c r="D94" s="78"/>
       <c r="E94" s="78"/>
       <c r="F94"/>
-      <c r="G94" s="137"/>
-      <c r="H94" s="178"/>
-      <c r="I94" s="178"/>
-      <c r="J94" s="178"/>
-      <c r="K94" s="178"/>
-    </row>
-    <row r="95" spans="1:11" ht="41.25" customHeight="1">
+      <c r="G94" s="175"/>
+      <c r="H94" s="147"/>
+      <c r="I94" s="147"/>
+      <c r="J94" s="147"/>
+      <c r="K94" s="147"/>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B95" s="149" t="s">
+      <c r="B95" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="C95" s="149"/>
-      <c r="D95" s="149"/>
-      <c r="E95" s="149"/>
-      <c r="F95" s="149"/>
-      <c r="G95" s="137"/>
-      <c r="H95" s="178"/>
-      <c r="I95" s="178"/>
-      <c r="J95" s="178"/>
-      <c r="K95" s="178"/>
-    </row>
-    <row r="96" spans="1:11" ht="10.5" customHeight="1">
+      <c r="C95" s="116"/>
+      <c r="D95" s="116"/>
+      <c r="E95" s="116"/>
+      <c r="F95" s="116"/>
+      <c r="G95" s="175"/>
+      <c r="H95" s="147"/>
+      <c r="I95" s="147"/>
+      <c r="J95" s="147"/>
+      <c r="K95" s="147"/>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96" s="42"/>
       <c r="B96" s="70"/>
       <c r="C96" s="70"/>
       <c r="D96" s="70"/>
       <c r="E96" s="70"/>
       <c r="F96" s="70"/>
-      <c r="G96" s="137"/>
-      <c r="H96" s="178"/>
-      <c r="I96" s="178"/>
-      <c r="J96" s="178"/>
-      <c r="K96" s="178"/>
-    </row>
-    <row r="97" spans="1:11" ht="132.75" customHeight="1">
+      <c r="G96" s="175"/>
+      <c r="H96" s="147"/>
+      <c r="I96" s="147"/>
+      <c r="J96" s="147"/>
+      <c r="K96" s="147"/>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="B97" s="149" t="s">
+      <c r="B97" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="C97" s="149"/>
-      <c r="D97" s="149"/>
-      <c r="E97" s="149"/>
-      <c r="F97" s="149"/>
-      <c r="G97" s="143"/>
-      <c r="H97" s="178"/>
-      <c r="I97" s="178"/>
-      <c r="J97" s="178"/>
-      <c r="K97" s="178"/>
-    </row>
-    <row r="98" spans="1:11" ht="12.75" customHeight="1">
+      <c r="C97" s="116"/>
+      <c r="D97" s="116"/>
+      <c r="E97" s="116"/>
+      <c r="F97" s="116"/>
+      <c r="G97" s="182"/>
+      <c r="H97" s="147"/>
+      <c r="I97" s="147"/>
+      <c r="J97" s="147"/>
+      <c r="K97" s="147"/>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98" s="4"/>
       <c r="B98" s="42"/>
       <c r="C98" s="70"/>
       <c r="D98" s="70"/>
       <c r="E98" s="70"/>
       <c r="F98" s="6"/>
-      <c r="G98" s="144"/>
-      <c r="H98" s="178"/>
-      <c r="I98" s="178"/>
-      <c r="J98" s="178"/>
-      <c r="K98" s="178"/>
-    </row>
-    <row r="99" spans="1:11" ht="41.25" customHeight="1">
+      <c r="G98" s="183"/>
+      <c r="H98" s="147"/>
+      <c r="I98" s="147"/>
+      <c r="J98" s="147"/>
+      <c r="K98" s="147"/>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99" s="4"/>
-      <c r="B99" s="151" t="s">
+      <c r="B99" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="C99" s="151"/>
-      <c r="D99" s="151"/>
-      <c r="E99" s="151"/>
+      <c r="C99" s="145"/>
+      <c r="D99" s="145"/>
+      <c r="E99" s="145"/>
       <c r="F99" s="70"/>
-      <c r="G99" s="143"/>
-      <c r="H99" s="178"/>
-      <c r="I99" s="178"/>
-      <c r="J99" s="178"/>
-      <c r="K99" s="178"/>
-    </row>
-    <row r="100" spans="1:11" ht="9" customHeight="1">
+      <c r="G99" s="182"/>
+      <c r="H99" s="147"/>
+      <c r="I99" s="147"/>
+      <c r="J99" s="147"/>
+      <c r="K99" s="147"/>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100" s="4"/>
       <c r="B100" s="70"/>
       <c r="C100" s="70"/>
       <c r="D100" s="70"/>
       <c r="E100" s="70"/>
       <c r="F100" s="70"/>
-      <c r="G100" s="143"/>
-      <c r="H100" s="178"/>
-      <c r="I100" s="178"/>
-      <c r="J100" s="178"/>
-      <c r="K100" s="178"/>
-    </row>
-    <row r="101" spans="1:11" ht="39.75" customHeight="1">
+      <c r="G100" s="182"/>
+      <c r="H100" s="147"/>
+      <c r="I100" s="147"/>
+      <c r="J100" s="147"/>
+      <c r="K100" s="147"/>
+    </row>
+    <row r="101" spans="1:11" ht="15.75">
       <c r="A101" s="4"/>
-      <c r="B101" s="151" t="s">
+      <c r="B101" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="C101" s="151"/>
-      <c r="D101" s="151"/>
-      <c r="E101" s="151"/>
+      <c r="C101" s="145"/>
+      <c r="D101" s="145"/>
+      <c r="E101" s="145"/>
       <c r="F101" s="70"/>
-      <c r="G101" s="145"/>
-      <c r="H101" s="178"/>
-      <c r="I101" s="178"/>
-      <c r="J101" s="178"/>
-      <c r="K101" s="178"/>
+      <c r="G101" s="184"/>
+      <c r="H101" s="147"/>
+      <c r="I101" s="147"/>
+      <c r="J101" s="147"/>
+      <c r="K101" s="147"/>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="4"/>
@@ -3951,54 +3951,54 @@
       <c r="D102" s="70"/>
       <c r="E102" s="70"/>
       <c r="F102" s="70"/>
-      <c r="G102" s="143"/>
-      <c r="H102" s="178"/>
-      <c r="I102" s="178"/>
-      <c r="J102" s="178"/>
-      <c r="K102" s="178"/>
-    </row>
-    <row r="103" spans="1:11" ht="29.25" customHeight="1">
+      <c r="G102" s="182"/>
+      <c r="H102" s="147"/>
+      <c r="I102" s="147"/>
+      <c r="J102" s="147"/>
+      <c r="K102" s="147"/>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103" s="4"/>
-      <c r="B103" s="151" t="s">
+      <c r="B103" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="C103" s="151"/>
-      <c r="D103" s="151"/>
-      <c r="E103" s="151"/>
+      <c r="C103" s="145"/>
+      <c r="D103" s="145"/>
+      <c r="E103" s="145"/>
       <c r="F103" s="70"/>
-      <c r="G103" s="143"/>
-      <c r="H103" s="178"/>
-      <c r="I103" s="178"/>
-      <c r="J103" s="178"/>
-      <c r="K103" s="178"/>
-    </row>
-    <row r="104" spans="1:11" ht="6.75" customHeight="1">
+      <c r="G103" s="182"/>
+      <c r="H103" s="147"/>
+      <c r="I103" s="147"/>
+      <c r="J103" s="147"/>
+      <c r="K103" s="147"/>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104" s="4"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24"/>
       <c r="D104" s="24"/>
       <c r="E104" s="24"/>
       <c r="F104" s="24"/>
-      <c r="G104" s="126"/>
-      <c r="H104" s="178"/>
-      <c r="I104" s="178"/>
-      <c r="J104" s="178"/>
-      <c r="K104" s="178"/>
-    </row>
-    <row r="105" spans="1:11" ht="15.75" customHeight="1">
+      <c r="G104" s="162"/>
+      <c r="H104" s="147"/>
+      <c r="I104" s="147"/>
+      <c r="J104" s="147"/>
+      <c r="K104" s="147"/>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105" s="4"/>
-      <c r="B105" s="151" t="s">
+      <c r="B105" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="151"/>
-      <c r="D105" s="151"/>
-      <c r="E105" s="151"/>
-      <c r="F105" s="151"/>
-      <c r="G105" s="143"/>
-      <c r="H105" s="178"/>
-      <c r="I105" s="178"/>
-      <c r="J105" s="178"/>
-      <c r="K105" s="178"/>
+      <c r="C105" s="145"/>
+      <c r="D105" s="145"/>
+      <c r="E105" s="145"/>
+      <c r="F105" s="145"/>
+      <c r="G105" s="182"/>
+      <c r="H105" s="147"/>
+      <c r="I105" s="147"/>
+      <c r="J105" s="147"/>
+      <c r="K105" s="147"/>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="4"/>
@@ -4007,11 +4007,11 @@
       <c r="D106" s="24"/>
       <c r="E106" s="24"/>
       <c r="F106" s="24"/>
-      <c r="G106" s="126"/>
-      <c r="H106" s="178"/>
-      <c r="I106" s="178"/>
-      <c r="J106" s="178"/>
-      <c r="K106" s="178"/>
+      <c r="G106" s="162"/>
+      <c r="H106" s="147"/>
+      <c r="I106" s="147"/>
+      <c r="J106" s="147"/>
+      <c r="K106" s="147"/>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="4"/>
@@ -4020,11 +4020,11 @@
       <c r="D107" s="24"/>
       <c r="E107" s="24"/>
       <c r="F107" s="24"/>
-      <c r="G107" s="126"/>
-      <c r="H107" s="178"/>
-      <c r="I107" s="178"/>
-      <c r="J107" s="178"/>
-      <c r="K107" s="178"/>
+      <c r="G107" s="162"/>
+      <c r="H107" s="147"/>
+      <c r="I107" s="147"/>
+      <c r="J107" s="147"/>
+      <c r="K107" s="147"/>
     </row>
     <row r="108" spans="1:11" ht="31.5">
       <c r="B108" s="72" t="s">
@@ -4034,11 +4034,11 @@
       <c r="D108" s="72"/>
       <c r="E108" s="72"/>
       <c r="F108" s="72"/>
-      <c r="G108" s="126"/>
-      <c r="H108" s="178"/>
-      <c r="I108" s="178"/>
-      <c r="J108" s="178"/>
-      <c r="K108" s="178"/>
+      <c r="G108" s="162"/>
+      <c r="H108" s="147"/>
+      <c r="I108" s="147"/>
+      <c r="J108" s="147"/>
+      <c r="K108" s="147"/>
     </row>
     <row r="109" spans="1:11">
       <c r="B109" s="24"/>
@@ -4046,77 +4046,77 @@
       <c r="D109" s="24"/>
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
-      <c r="G109" s="126"/>
-      <c r="H109" s="178"/>
-      <c r="I109" s="178"/>
-      <c r="J109" s="178"/>
-      <c r="K109" s="178"/>
-    </row>
-    <row r="110" spans="1:11" ht="12.75" customHeight="1">
-      <c r="B110" s="148" t="s">
+      <c r="G109" s="162"/>
+      <c r="H109" s="147"/>
+      <c r="I109" s="147"/>
+      <c r="J109" s="147"/>
+      <c r="K109" s="147"/>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="B110" s="143" t="s">
         <v>51</v>
       </c>
-      <c r="C110" s="148"/>
-      <c r="D110" s="148"/>
-      <c r="E110" s="148"/>
-      <c r="F110" s="148"/>
-      <c r="G110" s="126"/>
-      <c r="H110" s="178"/>
-      <c r="I110" s="178"/>
-      <c r="J110" s="178"/>
-      <c r="K110" s="178"/>
-    </row>
-    <row r="111" spans="1:11" ht="2.25" customHeight="1">
+      <c r="C110" s="143"/>
+      <c r="D110" s="143"/>
+      <c r="E110" s="143"/>
+      <c r="F110" s="143"/>
+      <c r="G110" s="162"/>
+      <c r="H110" s="147"/>
+      <c r="I110" s="147"/>
+      <c r="J110" s="147"/>
+      <c r="K110" s="147"/>
+    </row>
+    <row r="111" spans="1:11">
       <c r="B111" s="6"/>
       <c r="C111"/>
       <c r="D111"/>
       <c r="E111"/>
       <c r="F111"/>
-      <c r="G111" s="126"/>
-      <c r="H111" s="178"/>
-      <c r="I111" s="178"/>
-      <c r="J111" s="178"/>
-      <c r="K111" s="178"/>
-    </row>
-    <row r="112" spans="1:11" ht="17.25" customHeight="1">
-      <c r="B112" s="148" t="s">
+      <c r="G111" s="162"/>
+      <c r="H111" s="147"/>
+      <c r="I111" s="147"/>
+      <c r="J111" s="147"/>
+      <c r="K111" s="147"/>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="B112" s="143" t="s">
         <v>52</v>
       </c>
-      <c r="C112" s="148"/>
-      <c r="D112" s="148"/>
-      <c r="E112" s="148"/>
-      <c r="F112" s="148"/>
-      <c r="G112" s="126"/>
-      <c r="H112" s="178"/>
-      <c r="I112" s="178"/>
-      <c r="J112" s="178"/>
-      <c r="K112" s="178"/>
-    </row>
-    <row r="113" spans="1:11" ht="9.9499999999999993" customHeight="1">
+      <c r="C112" s="143"/>
+      <c r="D112" s="143"/>
+      <c r="E112" s="143"/>
+      <c r="F112" s="143"/>
+      <c r="G112" s="162"/>
+      <c r="H112" s="147"/>
+      <c r="I112" s="147"/>
+      <c r="J112" s="147"/>
+      <c r="K112" s="147"/>
+    </row>
+    <row r="113" spans="1:11">
       <c r="B113" s="6"/>
       <c r="C113"/>
       <c r="D113"/>
       <c r="E113"/>
       <c r="F113"/>
-      <c r="G113" s="126"/>
-      <c r="H113" s="178"/>
-      <c r="I113" s="178"/>
-      <c r="J113" s="178"/>
-      <c r="K113" s="178"/>
-    </row>
-    <row r="114" spans="1:11" ht="18.75" customHeight="1">
+      <c r="G113" s="162"/>
+      <c r="H113" s="147"/>
+      <c r="I113" s="147"/>
+      <c r="J113" s="147"/>
+      <c r="K113" s="147"/>
+    </row>
+    <row r="114" spans="1:11">
       <c r="B114" s="6"/>
       <c r="C114"/>
       <c r="D114"/>
       <c r="E114"/>
       <c r="F114"/>
-      <c r="G114" s="126"/>
-      <c r="H114" s="178"/>
-      <c r="I114" s="178"/>
-      <c r="J114" s="178"/>
-      <c r="K114" s="178"/>
-    </row>
-    <row r="115" spans="1:11" ht="15" customHeight="1">
+      <c r="G114" s="162"/>
+      <c r="H114" s="147"/>
+      <c r="I114" s="147"/>
+      <c r="J114" s="147"/>
+      <c r="K114" s="147"/>
+    </row>
+    <row r="115" spans="1:11" ht="15.75">
       <c r="B115" s="49" t="s">
         <v>34</v>
       </c>
@@ -4124,25 +4124,25 @@
       <c r="D115"/>
       <c r="E115"/>
       <c r="F115"/>
-      <c r="G115" s="126"/>
-      <c r="H115" s="178"/>
-      <c r="I115" s="178"/>
-      <c r="J115" s="178"/>
-      <c r="K115" s="178"/>
-    </row>
-    <row r="116" spans="1:11" ht="0.75" customHeight="1">
+      <c r="G115" s="162"/>
+      <c r="H115" s="147"/>
+      <c r="I115" s="147"/>
+      <c r="J115" s="147"/>
+      <c r="K115" s="147"/>
+    </row>
+    <row r="116" spans="1:11">
       <c r="B116" s="6"/>
       <c r="C116"/>
       <c r="D116"/>
       <c r="E116"/>
       <c r="F116"/>
-      <c r="G116" s="126"/>
-      <c r="H116" s="178"/>
-      <c r="I116" s="178"/>
-      <c r="J116" s="178"/>
-      <c r="K116" s="178"/>
-    </row>
-    <row r="117" spans="1:11" ht="16.5" customHeight="1">
+      <c r="G116" s="162"/>
+      <c r="H116" s="147"/>
+      <c r="I116" s="147"/>
+      <c r="J116" s="147"/>
+      <c r="K116" s="147"/>
+    </row>
+    <row r="117" spans="1:11">
       <c r="B117" s="6"/>
       <c r="C117"/>
       <c r="D117"/>
@@ -4150,36 +4150,36 @@
         <v>73</v>
       </c>
       <c r="F117" s="3"/>
-      <c r="G117" s="126"/>
-      <c r="H117" s="178"/>
-      <c r="I117" s="178"/>
-      <c r="J117" s="178"/>
-      <c r="K117" s="178"/>
-    </row>
-    <row r="118" spans="1:11" ht="9.9499999999999993" customHeight="1">
+      <c r="G117" s="162"/>
+      <c r="H117" s="147"/>
+      <c r="I117" s="147"/>
+      <c r="J117" s="147"/>
+      <c r="K117" s="147"/>
+    </row>
+    <row r="118" spans="1:11" ht="20.25">
       <c r="A118" s="1"/>
       <c r="B118" s="19"/>
       <c r="C118" s="34"/>
-      <c r="G118" s="126"/>
-      <c r="H118" s="178"/>
-      <c r="I118" s="178"/>
-      <c r="J118" s="178"/>
-      <c r="K118" s="178"/>
-    </row>
-    <row r="119" spans="1:11" ht="9.9499999999999993" customHeight="1">
-      <c r="A119" s="146"/>
-      <c r="B119" s="147"/>
-      <c r="C119" s="146"/>
-      <c r="D119" s="146"/>
-      <c r="E119" s="146"/>
-      <c r="F119" s="146"/>
-      <c r="G119" s="126"/>
-      <c r="H119" s="178"/>
-      <c r="I119" s="178"/>
-      <c r="J119" s="178"/>
-      <c r="K119" s="178"/>
-    </row>
-    <row r="120" spans="1:11" ht="9.9499999999999993" customHeight="1">
+      <c r="G118" s="162"/>
+      <c r="H118" s="147"/>
+      <c r="I118" s="147"/>
+      <c r="J118" s="147"/>
+      <c r="K118" s="147"/>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" s="114"/>
+      <c r="B119" s="115"/>
+      <c r="C119" s="114"/>
+      <c r="D119" s="114"/>
+      <c r="E119" s="114"/>
+      <c r="F119" s="114"/>
+      <c r="G119" s="162"/>
+      <c r="H119" s="147"/>
+      <c r="I119" s="147"/>
+      <c r="J119" s="147"/>
+      <c r="K119" s="147"/>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120" s="1"/>
       <c r="B120" s="19"/>
       <c r="G120" s="1"/>
@@ -4187,7 +4187,7 @@
       <c r="I120" s="1"/>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="121" spans="1:11">
       <c r="A121" s="1"/>
       <c r="B121" s="19"/>
       <c r="G121" s="1"/>
@@ -4195,7 +4195,7 @@
       <c r="I121" s="1"/>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="122" spans="1:11">
       <c r="A122" s="1"/>
       <c r="B122" s="19"/>
       <c r="G122" s="1"/>
@@ -4203,7 +4203,7 @@
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="123" spans="1:11">
       <c r="A123" s="1"/>
       <c r="B123" s="19"/>
       <c r="G123" s="1"/>
@@ -4211,7 +4211,7 @@
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="124" spans="1:11">
       <c r="A124" s="1"/>
       <c r="B124" s="19"/>
       <c r="G124" s="1"/>
@@ -4219,7 +4219,7 @@
       <c r="I124" s="1"/>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="125" spans="1:11">
       <c r="A125" s="1"/>
       <c r="B125" s="19"/>
       <c r="G125" s="1"/>
@@ -4227,7 +4227,7 @@
       <c r="I125" s="1"/>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="126" spans="1:11">
       <c r="A126" s="1"/>
       <c r="B126" s="19"/>
       <c r="G126" s="1"/>
@@ -4235,7 +4235,7 @@
       <c r="I126" s="1"/>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="127" spans="1:11">
       <c r="A127" s="1"/>
       <c r="B127" s="19"/>
       <c r="G127" s="1"/>
@@ -4243,7 +4243,7 @@
       <c r="I127" s="1"/>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:11" ht="9.9499999999999993" customHeight="1">
+    <row r="128" spans="1:11">
       <c r="A128" s="1"/>
       <c r="B128" s="19"/>
       <c r="G128" s="1"/>
@@ -4251,37 +4251,37 @@
       <c r="I128" s="1"/>
       <c r="J128" s="1"/>
     </row>
-    <row r="129" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="129" spans="2:2" s="1" customFormat="1">
       <c r="B129" s="19"/>
     </row>
-    <row r="130" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="130" spans="2:2" s="1" customFormat="1">
       <c r="B130" s="19"/>
     </row>
-    <row r="131" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="131" spans="2:2" s="1" customFormat="1">
       <c r="B131" s="19"/>
     </row>
-    <row r="132" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="132" spans="2:2" s="1" customFormat="1">
       <c r="B132" s="19"/>
     </row>
-    <row r="133" spans="2:2" s="1" customFormat="1" ht="9.9499999999999993" customHeight="1">
+    <row r="133" spans="2:2" s="1" customFormat="1">
       <c r="B133" s="19"/>
     </row>
-    <row r="134" spans="2:2" s="1" customFormat="1" ht="126" customHeight="1">
+    <row r="134" spans="2:2" s="1" customFormat="1">
       <c r="B134" s="19"/>
     </row>
-    <row r="135" spans="2:2" s="1" customFormat="1" ht="96" customHeight="1">
+    <row r="135" spans="2:2" s="1" customFormat="1">
       <c r="B135" s="19"/>
     </row>
-    <row r="136" spans="2:2" s="1" customFormat="1" ht="93" customHeight="1">
+    <row r="136" spans="2:2" s="1" customFormat="1">
       <c r="B136" s="19"/>
     </row>
-    <row r="137" spans="2:2" s="1" customFormat="1" ht="42" customHeight="1">
+    <row r="137" spans="2:2" s="1" customFormat="1">
       <c r="B137" s="19"/>
     </row>
-    <row r="138" spans="2:2" s="1" customFormat="1" ht="42.75" customHeight="1">
+    <row r="138" spans="2:2" s="1" customFormat="1">
       <c r="B138" s="19"/>
     </row>
-    <row r="139" spans="2:2" s="1" customFormat="1" ht="103.5" customHeight="1">
+    <row r="139" spans="2:2" s="1" customFormat="1">
       <c r="B139" s="19"/>
     </row>
     <row r="140" spans="2:2" s="1" customFormat="1">
@@ -10167,6 +10167,43 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0"/>
   <dataConsolidate/>
   <mergeCells count="53">
+    <mergeCell ref="B112:F112"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="B95:F95"/>
     <mergeCell ref="A1:F4"/>
     <mergeCell ref="D17:F17"/>
@@ -10183,43 +10220,6 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B105:F105"/>
-    <mergeCell ref="B103:E103"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B97:F97"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" display="www.BOYDSIGNSYSTEMS.com                                                                     " xr:uid="{00000000-0004-0000-0200-000000000000}"/>
